--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -6956,22 +6956,22 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>GP0824_03</t>
+          <t>GG1024_01</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>P050072</t>
+          <t>P050092</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="N79" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050072|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050092|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O79" s="6" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>P050072|R</t>
+          <t>P050092|R</t>
         </is>
       </c>
       <c r="Q79" s="8" t="inlineStr">
@@ -7038,22 +7038,22 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>GG1024_01</t>
+          <t>GP052501</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>P050092</t>
+          <t>P050152</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
         </is>
       </c>
       <c r="N80" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050092|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050152|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O80" s="6" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>P050092|R</t>
+          <t>P050152|R</t>
         </is>
       </c>
       <c r="Q80" s="8" t="inlineStr">
@@ -7120,22 +7120,22 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>GP052501</t>
+          <t>CJ052501/01</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>P050152</t>
+          <t>P050162</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Cup Junky</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="N81" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050152|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050162|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O81" s="6" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>P050152|R</t>
+          <t>P050162|R</t>
         </is>
       </c>
       <c r="Q81" s="8" t="inlineStr">
@@ -7202,22 +7202,22 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>CJ052501/01</t>
+          <t>GP082501/2</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>P050162</t>
+          <t>P050322</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="N82" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050162|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050322|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O82" s="6" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>P050162|R</t>
+          <t>P050322|R</t>
         </is>
       </c>
       <c r="Q82" s="8" t="inlineStr">
@@ -7284,22 +7284,22 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>GP082501/2</t>
+          <t>CJ062501/2</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>P050322</t>
+          <t>P050212</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
         </is>
       </c>
       <c r="N83" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050322|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050212|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O83" s="6" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>P050322|R</t>
+          <t>P050212|R</t>
         </is>
       </c>
       <c r="Q83" s="8" t="inlineStr">
@@ -7366,22 +7366,22 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>CJ062501/2</t>
+          <t>CJ082501/2</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>P050212</t>
+          <t>P060032</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="N84" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050212|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060032|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O84" s="6" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>P050212|R</t>
+          <t>P060032|R</t>
         </is>
       </c>
       <c r="Q84" s="8" t="inlineStr">
@@ -7448,22 +7448,22 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>CJ082501/2</t>
+          <t>PM092501</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>P060032</t>
+          <t>P060062</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Permanent Market</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -7477,7 +7477,7 @@
         </is>
       </c>
       <c r="N85" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060032|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060062|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O85" s="6" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>P060032|R</t>
+          <t>P060062|R</t>
         </is>
       </c>
       <c r="Q85" s="8" t="inlineStr">
@@ -7530,22 +7530,22 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>PM092501</t>
+          <t>J31102501</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>P060062</t>
+          <t>P060152</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
         </is>
       </c>
       <c r="N86" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060062|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060152|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O86" s="6" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>P060062|R</t>
+          <t>P060152|R</t>
         </is>
       </c>
       <c r="Q86" s="8" t="inlineStr">
@@ -7612,22 +7612,22 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>J31102501</t>
+          <t>JD112501</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>P060152</t>
+          <t>P060212</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
         </is>
       </c>
       <c r="N87" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060152|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060212|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O87" s="6" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>P060152|R</t>
+          <t>P060212|R</t>
         </is>
       </c>
       <c r="Q87" s="8" t="inlineStr">
@@ -7689,27 +7689,27 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>JD112501</t>
+          <t>J31122501</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>P060212</t>
+          <t>P060262</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="N88" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060212|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060262|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O88" s="6" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>P060212|R</t>
+          <t>P060262|R</t>
         </is>
       </c>
       <c r="Q88" s="8" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -7940,24 +7940,20 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>GG012603</t>
+          <t>JD012603</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>P060402</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>GorillaGlue</t>
-        </is>
-      </c>
+          <t>P060362</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -7969,7 +7965,7 @@
         </is>
       </c>
       <c r="N91" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060402|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060362|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O91" s="6" t="inlineStr">
@@ -7979,7 +7975,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>P060402|R</t>
+          <t>P060362|R</t>
         </is>
       </c>
       <c r="Q91" s="8" t="inlineStr">
@@ -8022,24 +8018,20 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>SCR012603</t>
+          <t>JD012603</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>P060382</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
+          <t>P060422</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -8051,7 +8043,7 @@
         </is>
       </c>
       <c r="N92" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060382|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060422|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O92" s="6" t="inlineStr">
@@ -8061,7 +8053,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>P060382|R</t>
+          <t>P060422|R</t>
         </is>
       </c>
       <c r="Q92" s="8" t="inlineStr">
@@ -8099,27 +8091,27 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>CJ1024</t>
+          <t>GG012603</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
+          <t>P060402</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>GorillaGlue</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -8133,7 +8125,7 @@
         </is>
       </c>
       <c r="N93" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("CJ1024|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060402|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O93" s="6" t="inlineStr">
@@ -8143,12 +8135,12 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>CJ1024|R</t>
+          <t>P060402|R</t>
         </is>
       </c>
       <c r="Q93" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — retest assay not yet on file</t>
+          <t>not yet issuable — retest assay on file; identification A, B and foreign matter to test at the retest sampling</t>
         </is>
       </c>
     </row>
@@ -8181,29 +8173,25 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>GG1024</t>
+          <t>JD012603</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>Gorilla Glue</t>
-        </is>
-      </c>
+          <t>P060412</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -8215,7 +8203,7 @@
         </is>
       </c>
       <c r="N94" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("GG1024|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060412|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O94" s="6" t="inlineStr">
@@ -8225,12 +8213,12 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>GG1024|R</t>
+          <t>P060412|R</t>
         </is>
       </c>
       <c r="Q94" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — retest assay not yet on file</t>
+          <t>not yet issuable — retest assay on file; identification A, B and foreign matter to test at the retest sampling</t>
         </is>
       </c>
     </row>
@@ -8263,27 +8251,27 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>GP0824_01</t>
+          <t>SCR012603</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>P050102</t>
+          <t>P060382</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -8297,7 +8285,7 @@
         </is>
       </c>
       <c r="N95" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050102|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060382|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O95" s="6" t="inlineStr">
@@ -8307,12 +8295,12 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>P050102|R</t>
+          <t>P060382|R</t>
         </is>
       </c>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — retest assay not yet on file</t>
+          <t>not yet issuable — retest assay on file; identification A, B and foreign matter to test at the retest sampling</t>
         </is>
       </c>
     </row>
@@ -8350,22 +8338,22 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>MB0824_04</t>
+          <t>CJ1024</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>P050032</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -8379,7 +8367,7 @@
         </is>
       </c>
       <c r="N96" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050032|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("CJ1024|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O96" s="6" t="inlineStr">
@@ -8389,7 +8377,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>P050032|R</t>
+          <t>CJ1024|R</t>
         </is>
       </c>
       <c r="Q96" s="8" t="inlineStr">
@@ -8432,17 +8420,17 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>GG1024_02</t>
+          <t>GG1024</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>P050012</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -8461,7 +8449,7 @@
         </is>
       </c>
       <c r="N97" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050012|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("GG1024|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O97" s="6" t="inlineStr">
@@ -8471,7 +8459,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>P050012|R</t>
+          <t>GG1024|R</t>
         </is>
       </c>
       <c r="Q97" s="8" t="inlineStr">
@@ -8514,22 +8502,22 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
         <is>
-          <t>OMP1024_01</t>
+          <t>GP0824_01</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>P050042</t>
+          <t>P050102</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -8543,7 +8531,7 @@
         </is>
       </c>
       <c r="N98" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050042|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050102|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O98" s="6" t="inlineStr">
@@ -8553,7 +8541,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>P050042|R</t>
+          <t>P050102|R</t>
         </is>
       </c>
       <c r="Q98" s="8" t="inlineStr">
@@ -8596,22 +8584,22 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>OPM1024_03</t>
+          <t>MB0824_04</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>P050082</t>
+          <t>P050032</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -8625,7 +8613,7 @@
         </is>
       </c>
       <c r="N99" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050082|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050032|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O99" s="6" t="inlineStr">
@@ -8635,7 +8623,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>P050082|R</t>
+          <t>P050032|R</t>
         </is>
       </c>
       <c r="Q99" s="8" t="inlineStr">
@@ -8678,22 +8666,22 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>MB0824_05</t>
+          <t>GG1024_02</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>P050112</t>
+          <t>P050012</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -8707,7 +8695,7 @@
         </is>
       </c>
       <c r="N100" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050112|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050012|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O100" s="6" t="inlineStr">
@@ -8717,7 +8705,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>P050112|R</t>
+          <t>P050012|R</t>
         </is>
       </c>
       <c r="Q100" s="8" t="inlineStr">
@@ -8760,17 +8748,17 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>OPM052501</t>
+          <t>OMP1024_01</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>P050132</t>
+          <t>P050042</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -8789,7 +8777,7 @@
         </is>
       </c>
       <c r="N101" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050132|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050042|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O101" s="6" t="inlineStr">
@@ -8799,7 +8787,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>P050132|R</t>
+          <t>P050042|R</t>
         </is>
       </c>
       <c r="Q101" s="8" t="inlineStr">
@@ -8842,22 +8830,22 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>CJ052501/02</t>
+          <t>GP0824_03</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>P050172</t>
+          <t>P050072</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -8871,7 +8859,7 @@
         </is>
       </c>
       <c r="N102" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050172|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050072|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O102" s="6" t="inlineStr">
@@ -8881,7 +8869,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>P050172|R</t>
+          <t>P050072|R</t>
         </is>
       </c>
       <c r="Q102" s="8" t="inlineStr">
@@ -8924,22 +8912,22 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>HPA052501</t>
+          <t>OPM1024_03</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>P050182</t>
+          <t>P050082</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -8953,7 +8941,7 @@
         </is>
       </c>
       <c r="N103" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050182|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050082|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O103" s="6" t="inlineStr">
@@ -8963,7 +8951,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>P050182|R</t>
+          <t>P050082|R</t>
         </is>
       </c>
       <c r="Q103" s="8" t="inlineStr">
@@ -9006,22 +8994,22 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>BSS052501</t>
+          <t>MB0824_05</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>P050192</t>
+          <t>P050112</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -9035,7 +9023,7 @@
         </is>
       </c>
       <c r="N104" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050192|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050112|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O104" s="6" t="inlineStr">
@@ -9045,7 +9033,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>P050192|R</t>
+          <t>P050112|R</t>
         </is>
       </c>
       <c r="Q104" s="8" t="inlineStr">
@@ -9088,22 +9076,22 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>CJ062501/1</t>
+          <t>OPM052501</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>P050222</t>
+          <t>P050132</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
@@ -9117,7 +9105,7 @@
         </is>
       </c>
       <c r="N105" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050222|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050132|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O105" s="6" t="inlineStr">
@@ -9127,7 +9115,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>P050222|R</t>
+          <t>P050132|R</t>
         </is>
       </c>
       <c r="Q105" s="8" t="inlineStr">
@@ -9170,17 +9158,17 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>CJ072501</t>
+          <t>CJ052501/02</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>P050252</t>
+          <t>P050172</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -9199,7 +9187,7 @@
         </is>
       </c>
       <c r="N106" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050252|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050172|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O106" s="6" t="inlineStr">
@@ -9209,7 +9197,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>P050252|R</t>
+          <t>P050172|R</t>
         </is>
       </c>
       <c r="Q106" s="8" t="inlineStr">
@@ -9252,22 +9240,22 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>WC072501</t>
+          <t>HPA052501</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>P050262</t>
+          <t>P050182</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>Wedding Crusher</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
@@ -9281,7 +9269,7 @@
         </is>
       </c>
       <c r="N107" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050262|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050182|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O107" s="6" t="inlineStr">
@@ -9291,7 +9279,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>P050262|R</t>
+          <t>P050182|R</t>
         </is>
       </c>
       <c r="Q107" s="8" t="inlineStr">
@@ -9334,22 +9322,22 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>CLE072501</t>
+          <t>BSS052501</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>P050282</t>
+          <t>P050192</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Clemosa a bud</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -9363,7 +9351,7 @@
         </is>
       </c>
       <c r="N108" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050282|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050192|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O108" s="6" t="inlineStr">
@@ -9373,7 +9361,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>P050282|R</t>
+          <t>P050192|R</t>
         </is>
       </c>
       <c r="Q108" s="8" t="inlineStr">
@@ -9416,22 +9404,22 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>GP072501/2</t>
+          <t>CJ062501/1</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>P050302</t>
+          <t>P050222</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
@@ -9445,7 +9433,7 @@
         </is>
       </c>
       <c r="N109" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050302|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050222|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O109" s="6" t="inlineStr">
@@ -9455,7 +9443,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>P050302|R</t>
+          <t>P050222|R</t>
         </is>
       </c>
       <c r="Q109" s="8" t="inlineStr">
@@ -9498,22 +9486,22 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>GP082501/1</t>
+          <t>CJ072501</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>P050312</t>
+          <t>P050252</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -9527,7 +9515,7 @@
         </is>
       </c>
       <c r="N110" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050312|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050252|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O110" s="6" t="inlineStr">
@@ -9537,7 +9525,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>P050312|R</t>
+          <t>P050252|R</t>
         </is>
       </c>
       <c r="Q110" s="8" t="inlineStr">
@@ -9580,22 +9568,22 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>WC082501</t>
+          <t>WC072501</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>P060012</t>
+          <t>P050262</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
@@ -9609,7 +9597,7 @@
         </is>
       </c>
       <c r="N111" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060012|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050262|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O111" s="6" t="inlineStr">
@@ -9619,7 +9607,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>P060012|R</t>
+          <t>P050262|R</t>
         </is>
       </c>
       <c r="Q111" s="8" t="inlineStr">
@@ -9662,22 +9650,22 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>CJ082501/1</t>
+          <t>CLE072501</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>P060022</t>
+          <t>P050282</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Clemosa a bud</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -9691,7 +9679,7 @@
         </is>
       </c>
       <c r="N112" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060022|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050282|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O112" s="6" t="inlineStr">
@@ -9701,7 +9689,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>P060022|R</t>
+          <t>P050282|R</t>
         </is>
       </c>
       <c r="Q112" s="8" t="inlineStr">
@@ -9744,17 +9732,17 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>GP072501/1</t>
+          <t>GP072501/2</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>P050292</t>
+          <t>P050302</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -9773,7 +9761,7 @@
         </is>
       </c>
       <c r="N113" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050292|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050302|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O113" s="6" t="inlineStr">
@@ -9783,7 +9771,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>P050292|R</t>
+          <t>P050302|R</t>
         </is>
       </c>
       <c r="Q113" s="8" t="inlineStr">
@@ -9826,22 +9814,22 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>PM072501</t>
+          <t>GP082501/1</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>P050272</t>
+          <t>P050312</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -9855,7 +9843,7 @@
         </is>
       </c>
       <c r="N114" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050272|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050312|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O114" s="6" t="inlineStr">
@@ -9865,7 +9853,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>P050272|R</t>
+          <t>P050312|R</t>
         </is>
       </c>
       <c r="Q114" s="8" t="inlineStr">
@@ -9908,22 +9896,22 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>OPM092501</t>
+          <t>WC082501</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>P060042</t>
+          <t>P060012</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Wedding Crasher</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
@@ -9937,7 +9925,7 @@
         </is>
       </c>
       <c r="N115" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060042|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060012|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O115" s="6" t="inlineStr">
@@ -9947,7 +9935,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>P060042|R</t>
+          <t>P060012|R</t>
         </is>
       </c>
       <c r="Q115" s="8" t="inlineStr">
@@ -9990,17 +9978,17 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>CJ092501</t>
+          <t>CJ082501/1</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>P060072</t>
+          <t>P060022</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -10019,7 +10007,7 @@
         </is>
       </c>
       <c r="N116" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060072|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060022|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O116" s="6" t="inlineStr">
@@ -10029,7 +10017,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>P060072|R</t>
+          <t>P060022|R</t>
         </is>
       </c>
       <c r="Q116" s="8" t="inlineStr">
@@ -10072,20 +10060,24 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>SJ0925021</t>
+          <t>GP072501/1</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>P060082</t>
-        </is>
-      </c>
-      <c r="K117" s="2" t="inlineStr"/>
+          <t>P050292</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -10097,7 +10089,7 @@
         </is>
       </c>
       <c r="N117" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060082|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050292|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O117" s="6" t="inlineStr">
@@ -10107,7 +10099,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>P060082|R</t>
+          <t>P050292|R</t>
         </is>
       </c>
       <c r="Q117" s="8" t="inlineStr">
@@ -10150,22 +10142,22 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>GP092501</t>
+          <t>PM072501</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>P060092</t>
+          <t>P050272</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -10179,7 +10171,7 @@
         </is>
       </c>
       <c r="N118" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060092|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050272|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O118" s="6" t="inlineStr">
@@ -10189,7 +10181,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>P060092|R</t>
+          <t>P050272|R</t>
         </is>
       </c>
       <c r="Q118" s="8" t="inlineStr">
@@ -10232,22 +10224,22 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>AB092501</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>P060052</t>
+          <t>P060042</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>Apple and Banana</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
@@ -10261,7 +10253,7 @@
         </is>
       </c>
       <c r="N119" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060052|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060042|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O119" s="6" t="inlineStr">
@@ -10271,7 +10263,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>P060052|R</t>
+          <t>P060042|R</t>
         </is>
       </c>
       <c r="Q119" s="8" t="inlineStr">
@@ -10314,22 +10306,22 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>SJ102501</t>
+          <t>CJ092501</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>P060162</t>
+          <t>P060072</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -10343,7 +10335,7 @@
         </is>
       </c>
       <c r="N120" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060162|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060072|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O120" s="6" t="inlineStr">
@@ -10353,7 +10345,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>P060162|R</t>
+          <t>P060072|R</t>
         </is>
       </c>
       <c r="Q120" s="8" t="inlineStr">
@@ -10396,24 +10388,20 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>SJ112501</t>
+          <t>SJ0925021</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>P060192</t>
-        </is>
-      </c>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>Sleepy Joy</t>
-        </is>
-      </c>
+          <t>P060082</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -10425,7 +10413,7 @@
         </is>
       </c>
       <c r="N121" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060192|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060082|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O121" s="6" t="inlineStr">
@@ -10435,7 +10423,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>P060192|R</t>
+          <t>P060082|R</t>
         </is>
       </c>
       <c r="Q121" s="8" t="inlineStr">
@@ -10478,22 +10466,22 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>OPM112501</t>
+          <t>GP092501</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>P060222</t>
+          <t>P060092</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -10507,7 +10495,7 @@
         </is>
       </c>
       <c r="N122" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060222|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060092|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O122" s="6" t="inlineStr">
@@ -10517,7 +10505,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>P060222|R</t>
+          <t>P060092|R</t>
         </is>
       </c>
       <c r="Q122" s="8" t="inlineStr">
@@ -10560,22 +10548,22 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>KC102501</t>
+          <t>AB092501</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>P060172</t>
+          <t>P060052</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Apple and Banana</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
@@ -10589,7 +10577,7 @@
         </is>
       </c>
       <c r="N123" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060172|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060052|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O123" s="6" t="inlineStr">
@@ -10599,7 +10587,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>P060172|R</t>
+          <t>P060052|R</t>
         </is>
       </c>
       <c r="Q123" s="8" t="inlineStr">
@@ -10642,22 +10630,22 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>GRC102501</t>
+          <t>SJ102501</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>P060182</t>
+          <t>P060162</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -10671,7 +10659,7 @@
         </is>
       </c>
       <c r="N124" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060182|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060162|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O124" s="6" t="inlineStr">
@@ -10681,7 +10669,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>P060182|R</t>
+          <t>P060162|R</t>
         </is>
       </c>
       <c r="Q124" s="8" t="inlineStr">
@@ -10724,22 +10712,22 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>J31112501</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>P060202</t>
+          <t>P060192</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -10753,7 +10741,7 @@
         </is>
       </c>
       <c r="N125" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060202|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060192|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O125" s="6" t="inlineStr">
@@ -10763,7 +10751,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>P060202|R</t>
+          <t>P060192|R</t>
         </is>
       </c>
       <c r="Q125" s="8" t="inlineStr">
@@ -10806,22 +10794,22 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>JD112501＊</t>
+          <t>OPM112501</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>P060212</t>
+          <t>P060222</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -10835,7 +10823,7 @@
         </is>
       </c>
       <c r="N126" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("JD112501|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060222|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O126" s="6" t="inlineStr">
@@ -10845,7 +10833,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>JD112501|R</t>
+          <t>P060222|R</t>
         </is>
       </c>
       <c r="Q126" s="8" t="inlineStr">
@@ -10883,27 +10871,27 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>P060262</t>
+          <t>P060172</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
@@ -10917,7 +10905,7 @@
         </is>
       </c>
       <c r="N127" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060262|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060172|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O127" s="6" t="inlineStr">
@@ -10927,7 +10915,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>P060262|R</t>
+          <t>P060172|R</t>
         </is>
       </c>
       <c r="Q127" s="8" t="inlineStr">
@@ -10970,22 +10958,22 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>PM112501</t>
+          <t>GRC102501</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>P060232</t>
+          <t>P060182</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Graps &amp; Creme</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -10999,7 +10987,7 @@
         </is>
       </c>
       <c r="N128" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060232|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060182|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O128" s="6" t="inlineStr">
@@ -11009,7 +10997,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>P060232|R</t>
+          <t>P060182|R</t>
         </is>
       </c>
       <c r="Q128" s="8" t="inlineStr">
@@ -11047,27 +11035,27 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>CC112501</t>
+          <t>J31112501</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>P060272</t>
+          <t>P060202</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
@@ -11081,7 +11069,7 @@
         </is>
       </c>
       <c r="N129" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060272|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060202|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O129" s="6" t="inlineStr">
@@ -11091,7 +11079,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>P060272|R</t>
+          <t>P060202|R</t>
         </is>
       </c>
       <c r="Q129" s="8" t="inlineStr">
@@ -11129,27 +11117,27 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>JD112501＊</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>P060292</t>
+          <t>P060212</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -11163,7 +11151,7 @@
         </is>
       </c>
       <c r="N130" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060292|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("JD112501|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O130" s="6" t="inlineStr">
@@ -11173,7 +11161,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>P060292|R</t>
+          <t>JD112501|R</t>
         </is>
       </c>
       <c r="Q130" s="8" t="inlineStr">
@@ -11211,27 +11199,27 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>GG012601＊</t>
+          <t>PM112501</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>P060302</t>
+          <t>P060232</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Permanent Market</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
@@ -11245,7 +11233,7 @@
         </is>
       </c>
       <c r="N131" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060302|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060232|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O131" s="6" t="inlineStr">
@@ -11255,7 +11243,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>P060302|R</t>
+          <t>P060232|R</t>
         </is>
       </c>
       <c r="Q131" s="8" t="inlineStr">
@@ -11293,27 +11281,27 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>GG112501</t>
+          <t>CC112501</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>P060252</t>
+          <t>P060272</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -11327,7 +11315,7 @@
         </is>
       </c>
       <c r="N132" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060252|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060272|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O132" s="6" t="inlineStr">
@@ -11337,7 +11325,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>P060252|R</t>
+          <t>P060272|R</t>
         </is>
       </c>
       <c r="Q132" s="8" t="inlineStr">
@@ -11375,27 +11363,27 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>GP062501</t>
+          <t>FB112501</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>P050202</t>
+          <t>P060292</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
@@ -11409,7 +11397,7 @@
         </is>
       </c>
       <c r="N133" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050202|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060292|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O133" s="6" t="inlineStr">
@@ -11419,7 +11407,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>P050202|R</t>
+          <t>P060292|R</t>
         </is>
       </c>
       <c r="Q133" s="8" t="inlineStr">
@@ -11462,22 +11450,22 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>JD012601＊</t>
+          <t>GG012601＊</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>P060312</t>
+          <t>P060302</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -11491,7 +11479,7 @@
         </is>
       </c>
       <c r="N134" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060312|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060302|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O134" s="6" t="inlineStr">
@@ -11501,7 +11489,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>P060312|R</t>
+          <t>P060302|R</t>
         </is>
       </c>
       <c r="Q134" s="8" t="inlineStr">
@@ -11539,27 +11527,27 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>SCR112501</t>
+          <t>GG112501</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>P060282</t>
+          <t>P060252</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
@@ -11573,7 +11561,7 @@
         </is>
       </c>
       <c r="N135" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060282|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060252|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O135" s="6" t="inlineStr">
@@ -11583,7 +11571,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>P060282|R</t>
+          <t>P060252|R</t>
         </is>
       </c>
       <c r="Q135" s="8" t="inlineStr">
@@ -11621,27 +11609,27 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>FB012601_1</t>
+          <t>GP062501</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>P060322</t>
+          <t>P050202</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -11655,7 +11643,7 @@
         </is>
       </c>
       <c r="N136" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060322|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050202|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O136" s="6" t="inlineStr">
@@ -11665,7 +11653,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>P060322|R</t>
+          <t>P050202|R</t>
         </is>
       </c>
       <c r="Q136" s="8" t="inlineStr">
@@ -11708,20 +11696,24 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>JD012603</t>
+          <t>JD012601＊</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>P060362</t>
-        </is>
-      </c>
-      <c r="K137" s="2" t="inlineStr"/>
+          <t>P060312</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -11733,7 +11725,7 @@
         </is>
       </c>
       <c r="N137" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060362|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060312|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O137" s="6" t="inlineStr">
@@ -11743,7 +11735,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>P060362|R</t>
+          <t>P060312|R</t>
         </is>
       </c>
       <c r="Q137" s="8" t="inlineStr">
@@ -11786,20 +11778,24 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>JD012603</t>
+          <t>SCR112501</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>P060422</t>
-        </is>
-      </c>
-      <c r="K138" s="2" t="inlineStr"/>
+          <t>P060282</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -11811,7 +11807,7 @@
         </is>
       </c>
       <c r="N138" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060422|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060282|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O138" s="6" t="inlineStr">
@@ -11821,7 +11817,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>P060422|R</t>
+          <t>P060282|R</t>
         </is>
       </c>
       <c r="Q138" s="8" t="inlineStr">
@@ -11864,20 +11860,24 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>JD012603</t>
+          <t>FB012601_1</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>P060412</t>
-        </is>
-      </c>
-      <c r="K139" s="2" t="inlineStr"/>
+          <t>P060322</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="N139" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060412|R",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060322|R",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O139" s="6" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>P060412|R</t>
+          <t>P060322|R</t>
         </is>
       </c>
       <c r="Q139" s="8" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="O54" s="6" t="inlineStr">
         <is>
-          <t>— no cannabinoid certificate —</t>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="P54" s="6" t="inlineStr">
@@ -17553,12 +17553,14 @@
         <f>IF(ISNUMBER(F55),IF(AND(J55="legacy",F55&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F55+7)+CHOOSE(WEEKDAY(F55+7,2),0,0,0,0,0,2,1))),IF(J55="legacy",DATE(2026,5,27),""))</f>
         <v/>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>46244</v>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>197-13-M-26</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H55" s="2">
@@ -17594,9 +17596,9 @@
           <t>HighProAmnesia</t>
         </is>
       </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>197-13-K-26, (07.08.2026) [FHM-K]</t>
+      <c r="O55" s="6" t="inlineStr">
+        <is>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="P55" s="6" t="inlineStr">
@@ -17621,7 +17623,7 @@
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #9, #11, #12</t>
+          <t>not yet issuable — uncertified: #3, #4, #5, #6, #8, #9, #10, #11, #12</t>
         </is>
       </c>
     </row>
@@ -17647,12 +17649,14 @@
         <f>IF(ISNUMBER(F56),IF(AND(J56="legacy",F56&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F56+7)+CHOOSE(WEEKDAY(F56+7,2),0,0,0,0,0,2,1))),IF(J56="legacy",DATE(2026,5,27),""))</f>
         <v/>
       </c>
-      <c r="F56" s="5" t="n">
-        <v>46244</v>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>197-17-M-26</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H56" s="2">
@@ -17688,9 +17692,9 @@
           <t>OrangePunchMimosa</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>197-17-K-26, (07.08.2026) [FHM-K]</t>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
@@ -17715,7 +17719,7 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #9, #11, #12</t>
+          <t>not yet issuable — uncertified: #3, #4, #5, #6, #8, #9, #10, #11, #12</t>
         </is>
       </c>
     </row>
@@ -17741,12 +17745,14 @@
         <f>IF(ISNUMBER(F57),IF(AND(J57="legacy",F57&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F57+7)+CHOOSE(WEEKDAY(F57+7,2),0,0,0,0,0,2,1))),IF(J57="legacy",DATE(2026,5,27),""))</f>
         <v/>
       </c>
-      <c r="F57" s="5" t="n">
-        <v>46266</v>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>559-1090-26</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H57" s="2">
@@ -17784,7 +17790,7 @@
       </c>
       <c r="O57" s="6" t="inlineStr">
         <is>
-          <t>— no cannabinoid certificate —</t>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="P57" s="6" t="inlineStr">
@@ -17809,7 +17815,7 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #3, #4, #5, #6, #8, #10, #11, #12</t>
+          <t>not yet issuable — uncertified: #3, #4, #5, #6, #8, #9, #10, #11, #12</t>
         </is>
       </c>
     </row>
@@ -17835,12 +17841,14 @@
         <f>IF(ISNUMBER(F58),IF(AND(J58="legacy",F58&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F58+7)+CHOOSE(WEEKDAY(F58+7,2),0,0,0,0,0,2,1))),IF(J58="legacy",DATE(2026,5,27),""))</f>
         <v/>
       </c>
-      <c r="F58" s="5" t="n">
-        <v>46266</v>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>551-1082-26</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H58" s="2">
@@ -17878,7 +17886,7 @@
       </c>
       <c r="O58" s="6" t="inlineStr">
         <is>
-          <t>— no cannabinoid certificate —</t>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="P58" s="6" t="inlineStr">
@@ -17903,7 +17911,7 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #3, #4, #5, #6, #8, #10, #11, #12</t>
+          <t>not yet issuable — uncertified: #3, #4, #5, #6, #8, #9, #10, #11, #12</t>
         </is>
       </c>
     </row>
@@ -17930,11 +17938,11 @@
         <v/>
       </c>
       <c r="F59" s="5" t="n">
-        <v>46266</v>
+        <v>46083</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>550-1081-26</t>
+          <t>051-6-LoD-26</t>
         </is>
       </c>
       <c r="H59" s="2">
@@ -17997,7 +18005,7 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #10, #11, #12</t>
+          <t>not yet issuable — uncertified: #9, #10, #11, #12</t>
         </is>
       </c>
     </row>
@@ -18024,11 +18032,11 @@
         <v/>
       </c>
       <c r="F60" s="5" t="n">
-        <v>46244</v>
+        <v>46083</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>197-16-M-26</t>
+          <t>051-1-LoD-26</t>
         </is>
       </c>
       <c r="H60" s="2">
@@ -18091,7 +18099,7 @@
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #9, #11, #12</t>
+          <t>not yet issuable — uncertified: #9, #10, #11, #12</t>
         </is>
       </c>
     </row>
@@ -18118,11 +18126,11 @@
         <v/>
       </c>
       <c r="F61" s="5" t="n">
-        <v>46265</v>
+        <v>46083</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>549-1080-26</t>
+          <t>051-3-LoD-26</t>
         </is>
       </c>
       <c r="H61" s="2">
@@ -18185,7 +18193,7 @@
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #10, #11, #12</t>
+          <t>not yet issuable — uncertified: #9, #10, #11, #12</t>
         </is>
       </c>
     </row>
@@ -18306,11 +18314,11 @@
         <v/>
       </c>
       <c r="F63" s="5" t="n">
-        <v>46266</v>
+        <v>46083</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>550-1081-26</t>
+          <t>051-6-LoD-26</t>
         </is>
       </c>
       <c r="H63" s="2">
@@ -18373,7 +18381,7 @@
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #10, #11, #12</t>
+          <t>not yet issuable — uncertified: #9, #10, #11, #12</t>
         </is>
       </c>
     </row>
@@ -18494,11 +18502,11 @@
         <v/>
       </c>
       <c r="F65" s="5" t="n">
-        <v>46265</v>
+        <v>46083</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>547-1078-26</t>
+          <t>051-5-LoD-26</t>
         </is>
       </c>
       <c r="H65" s="2">
@@ -18561,7 +18569,7 @@
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #10, #11, #12</t>
+          <t>not yet issuable — uncertified: #9, #10, #11, #12</t>
         </is>
       </c>
     </row>
@@ -18588,11 +18596,11 @@
         <v/>
       </c>
       <c r="F66" s="5" t="n">
-        <v>46265</v>
+        <v>46086</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>546-1077-26</t>
+          <t>ППК26031</t>
         </is>
       </c>
       <c r="H66" s="2">
@@ -18655,7 +18663,7 @@
       </c>
       <c r="T66" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #10, #11, #12</t>
+          <t>not yet issuable — uncertified: #9, #10, #11, #12</t>
         </is>
       </c>
     </row>
@@ -18775,12 +18783,14 @@
         <f>IF(ISNUMBER(F68),IF(AND(J68="legacy",F68&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F68+7)+CHOOSE(WEEKDAY(F68+7,2),0,0,0,0,0,2,1))),IF(J68="legacy",DATE(2026,5,27),""))</f>
         <v/>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>46244</v>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>197-6-M-26</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H68" s="2">
@@ -18812,9 +18822,9 @@
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr"/>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>197-6-K-26, (07.08.2026) [FHM-K]</t>
+      <c r="O68" s="6" t="inlineStr">
+        <is>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="P68" s="6" t="inlineStr">
@@ -18839,7 +18849,7 @@
       </c>
       <c r="T68" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #9, #11, #12</t>
+          <t>not yet issuable — no certificate on file</t>
         </is>
       </c>
     </row>
@@ -18865,12 +18875,14 @@
         <f>IF(ISNUMBER(F69),IF(AND(J69="legacy",F69&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F69+7)+CHOOSE(WEEKDAY(F69+7,2),0,0,0,0,0,2,1))),IF(J69="legacy",DATE(2026,5,27),""))</f>
         <v/>
       </c>
-      <c r="F69" s="5" t="n">
-        <v>46244</v>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>197-7-M-26</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H69" s="2">
@@ -18906,9 +18918,9 @@
           <t>Fat Bastard</t>
         </is>
       </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>197-7-K-26, (07.08.2026) [FHM-K]</t>
+      <c r="O69" s="6" t="inlineStr">
+        <is>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="P69" s="6" t="inlineStr">
@@ -18933,7 +18945,7 @@
       </c>
       <c r="T69" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #9, #11, #12</t>
+          <t>not yet issuable — no certificate on file</t>
         </is>
       </c>
     </row>
@@ -19234,11 +19246,11 @@
         <v/>
       </c>
       <c r="F73" s="5" t="n">
-        <v>46244</v>
+        <v>46203</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>197-8-M-26</t>
+          <t>ППК26114</t>
         </is>
       </c>
       <c r="H73" s="2">
@@ -19301,7 +19313,7 @@
       </c>
       <c r="T73" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #9, #11, #12</t>
+          <t>not yet issuable — uncertified: #9, #10, #11, #12</t>
         </is>
       </c>
     </row>
@@ -19460,7 +19472,7 @@
       </c>
       <c r="O75" s="6" t="inlineStr">
         <is>
-          <t>— no cannabinoid certificate —</t>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="P75" s="6" t="inlineStr">
@@ -19511,12 +19523,14 @@
         <f>IF(ISNUMBER(F76),IF(AND(J76="legacy",F76&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F76+7)+CHOOSE(WEEKDAY(F76+7,2),0,0,0,0,0,2,1))),IF(J76="legacy",DATE(2026,5,27),""))</f>
         <v/>
       </c>
-      <c r="F76" s="5" t="n">
-        <v>46244</v>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>197-21-M-26</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H76" s="2">
@@ -19552,9 +19566,9 @@
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>197-21-K-26, (07.08.2026) [FHM-K]</t>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="P76" s="6" t="inlineStr">
@@ -19579,7 +19593,7 @@
       </c>
       <c r="T76" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — uncertified: #9, #11, #12</t>
+          <t>not yet issuable — no certificate on file</t>
         </is>
       </c>
     </row>
@@ -20341,19 +20355,16 @@
         <f>IF(A85="","",IF(ISNUMBER(I85),MAX(E85,I85),E85))</f>
         <v/>
       </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E85" s="5">
+        <f>IF(ISNUMBER(F85),MAX(DATE(2026,5,27),(F85+7)+CHOOSE(WEEKDAY(F85+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>565-1096-26</t>
         </is>
       </c>
       <c r="H85" s="2">
@@ -20371,7 +20382,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
@@ -20416,7 +20427,7 @@
       </c>
       <c r="T85" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -20438,19 +20449,16 @@
         <f>IF(A86="","",IF(ISNUMBER(I86),MAX(E86,I86),E86))</f>
         <v/>
       </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E86" s="5">
+        <f>IF(ISNUMBER(F86),MAX(DATE(2026,5,27),(F86+7)+CHOOSE(WEEKDAY(F86+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-2-M-26</t>
         </is>
       </c>
       <c r="H86" s="2">
@@ -20468,7 +20476,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
@@ -20513,7 +20521,7 @@
       </c>
       <c r="T86" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -20535,19 +20543,16 @@
         <f>IF(A87="","",IF(ISNUMBER(I87),MAX(E87,I87),E87))</f>
         <v/>
       </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E87" s="5">
+        <f>IF(ISNUMBER(F87),MAX(DATE(2026,5,27),(F87+7)+CHOOSE(WEEKDAY(F87+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-1-M-26</t>
         </is>
       </c>
       <c r="H87" s="2">
@@ -20565,7 +20570,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
@@ -20610,7 +20615,7 @@
       </c>
       <c r="T87" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -20632,14 +20637,13 @@
         <f>IF(A88="","",IF(ISNUMBER(I88),MAX(E88,I88),E88))</f>
         <v/>
       </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E88" s="5">
+        <f>IF(ISNUMBER(F88),MAX(DATE(2026,5,27),(F88+7)+CHOOSE(WEEKDAY(F88+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -20662,7 +20666,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
@@ -20707,7 +20711,7 @@
       </c>
       <c r="T88" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -20729,19 +20733,16 @@
         <f>IF(A89="","",IF(ISNUMBER(I89),MAX(E89,I89),E89))</f>
         <v/>
       </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E89" s="5">
+        <f>IF(ISNUMBER(F89),MAX(DATE(2026,5,27),(F89+7)+CHOOSE(WEEKDAY(F89+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-13-M-26</t>
         </is>
       </c>
       <c r="H89" s="2">
@@ -20759,7 +20760,7 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
@@ -20804,7 +20805,7 @@
       </c>
       <c r="T89" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -20826,19 +20827,16 @@
         <f>IF(A90="","",IF(ISNUMBER(I90),MAX(E90,I90),E90))</f>
         <v/>
       </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E90" s="5">
+        <f>IF(ISNUMBER(F90),MAX(DATE(2026,5,27),(F90+7)+CHOOSE(WEEKDAY(F90+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>562-1093-26</t>
         </is>
       </c>
       <c r="H90" s="2">
@@ -20856,7 +20854,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
@@ -20901,7 +20899,7 @@
       </c>
       <c r="T90" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -20923,19 +20921,16 @@
         <f>IF(A91="","",IF(ISNUMBER(I91),MAX(E91,I91),E91))</f>
         <v/>
       </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E91" s="5">
+        <f>IF(ISNUMBER(F91),MAX(DATE(2026,5,27),(F91+7)+CHOOSE(WEEKDAY(F91+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-17-M-26</t>
         </is>
       </c>
       <c r="H91" s="2">
@@ -20953,7 +20948,7 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
@@ -20998,7 +20993,7 @@
       </c>
       <c r="T91" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -21020,19 +21015,16 @@
         <f>IF(A92="","",IF(ISNUMBER(I92),MAX(E92,I92),E92))</f>
         <v/>
       </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E92" s="5">
+        <f>IF(ISNUMBER(F92),MAX(DATE(2026,5,27),(F92+7)+CHOOSE(WEEKDAY(F92+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>563-1094-26</t>
         </is>
       </c>
       <c r="H92" s="2">
@@ -21050,7 +21042,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
@@ -21095,7 +21087,7 @@
       </c>
       <c r="T92" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -21117,19 +21109,16 @@
         <f>IF(A93="","",IF(ISNUMBER(I93),MAX(E93,I93),E93))</f>
         <v/>
       </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E93" s="5">
+        <f>IF(ISNUMBER(F93),MAX(DATE(2026,5,27),(F93+7)+CHOOSE(WEEKDAY(F93+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>564-1095-26</t>
         </is>
       </c>
       <c r="H93" s="2">
@@ -21147,7 +21136,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
@@ -21192,7 +21181,7 @@
       </c>
       <c r="T93" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -21214,19 +21203,16 @@
         <f>IF(A94="","",IF(ISNUMBER(I94),MAX(E94,I94),E94))</f>
         <v/>
       </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E94" s="5">
+        <f>IF(ISNUMBER(F94),MAX(DATE(2026,5,27),(F94+7)+CHOOSE(WEEKDAY(F94+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-11-M-26</t>
         </is>
       </c>
       <c r="H94" s="2">
@@ -21244,7 +21230,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
@@ -21264,7 +21250,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ППК26032, (05.03.2026) [CNP]</t>
+          <t>197-11-K-26, (07.08.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P94" s="6" t="inlineStr">
@@ -21289,7 +21275,7 @@
       </c>
       <c r="T94" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -21311,14 +21297,13 @@
         <f>IF(A95="","",IF(ISNUMBER(I95),MAX(E95,I95),E95))</f>
         <v/>
       </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E95" s="5">
+        <f>IF(ISNUMBER(F95),MAX(DATE(2026,5,27),(F95+7)+CHOOSE(WEEKDAY(F95+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -21341,7 +21326,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L95" s="3" t="inlineStr">
@@ -21386,7 +21371,7 @@
       </c>
       <c r="T95" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -21408,19 +21393,16 @@
         <f>IF(A96="","",IF(ISNUMBER(I96),MAX(E96,I96),E96))</f>
         <v/>
       </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E96" s="5">
+        <f>IF(ISNUMBER(F96),MAX(DATE(2026,5,27),(F96+7)+CHOOSE(WEEKDAY(F96+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-14-M-26</t>
         </is>
       </c>
       <c r="H96" s="2">
@@ -21438,7 +21420,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
@@ -21483,7 +21465,7 @@
       </c>
       <c r="T96" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -21505,19 +21487,16 @@
         <f>IF(A97="","",IF(ISNUMBER(I97),MAX(E97,I97),E97))</f>
         <v/>
       </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E97" s="5">
+        <f>IF(ISNUMBER(F97),MAX(DATE(2026,5,27),(F97+7)+CHOOSE(WEEKDAY(F97+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-18-M-26</t>
         </is>
       </c>
       <c r="H97" s="2">
@@ -21535,7 +21514,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
@@ -21580,7 +21559,7 @@
       </c>
       <c r="T97" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -21602,14 +21581,13 @@
         <f>IF(A98="","",IF(ISNUMBER(I98),MAX(E98,I98),E98))</f>
         <v/>
       </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E98" s="5">
+        <f>IF(ISNUMBER(F98),MAX(DATE(2026,5,27),(F98+7)+CHOOSE(WEEKDAY(F98+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -21632,7 +21610,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
@@ -21650,9 +21628,9 @@
           <t>Grape Pie</t>
         </is>
       </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>ППК26034, (05.03.2026) [CNP]</t>
+      <c r="O98" s="6" t="inlineStr">
+        <is>
+          <t>— retest assay not yet on file —</t>
         </is>
       </c>
       <c r="P98" s="6" t="inlineStr">
@@ -21677,7 +21655,7 @@
       </c>
       <c r="T98" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay on file, mycotoxins pending · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -21699,14 +21677,13 @@
         <f>IF(A99="","",IF(ISNUMBER(I99),MAX(E99,I99),E99))</f>
         <v/>
       </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E99" s="5">
+        <f>IF(ISNUMBER(F99),MAX(DATE(2026,5,27),(F99+7)+CHOOSE(WEEKDAY(F99+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -21729,7 +21706,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
@@ -21774,7 +21751,7 @@
       </c>
       <c r="T99" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -21796,19 +21773,16 @@
         <f>IF(A100="","",IF(ISNUMBER(I100),MAX(E100,I100),E100))</f>
         <v/>
       </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E100" s="5">
+        <f>IF(ISNUMBER(F100),MAX(DATE(2026,5,27),(F100+7)+CHOOSE(WEEKDAY(F100+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-9-M-26</t>
         </is>
       </c>
       <c r="H100" s="2">
@@ -21826,7 +21800,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
@@ -21871,7 +21845,7 @@
       </c>
       <c r="T100" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -21893,14 +21867,13 @@
         <f>IF(A101="","",IF(ISNUMBER(I101),MAX(E101,I101),E101))</f>
         <v/>
       </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E101" s="5">
+        <f>IF(ISNUMBER(F101),MAX(DATE(2026,5,27),(F101+7)+CHOOSE(WEEKDAY(F101+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -21923,7 +21896,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L101" s="3" t="inlineStr">
@@ -21968,7 +21941,7 @@
       </c>
       <c r="T101" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -21990,19 +21963,16 @@
         <f>IF(A102="","",IF(ISNUMBER(I102),MAX(E102,I102),E102))</f>
         <v/>
       </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E102" s="5">
+        <f>IF(ISNUMBER(F102),MAX(DATE(2026,5,27),(F102+7)+CHOOSE(WEEKDAY(F102+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>560-1091-26</t>
         </is>
       </c>
       <c r="H102" s="2">
@@ -22020,7 +21990,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr">
@@ -22065,7 +22035,7 @@
       </c>
       <c r="T102" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -22087,19 +22057,16 @@
         <f>IF(A103="","",IF(ISNUMBER(I103),MAX(E103,I103),E103))</f>
         <v/>
       </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E103" s="5">
+        <f>IF(ISNUMBER(F103),MAX(DATE(2026,5,27),(F103+7)+CHOOSE(WEEKDAY(F103+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>558-1089-26</t>
         </is>
       </c>
       <c r="H103" s="2">
@@ -22117,7 +22084,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L103" s="3" t="inlineStr">
@@ -22162,7 +22129,7 @@
       </c>
       <c r="T103" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -22184,19 +22151,16 @@
         <f>IF(A104="","",IF(ISNUMBER(I104),MAX(E104,I104),E104))</f>
         <v/>
       </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E104" s="5">
+        <f>IF(ISNUMBER(F104),MAX(DATE(2026,5,27),(F104+7)+CHOOSE(WEEKDAY(F104+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-10-M-26</t>
         </is>
       </c>
       <c r="H104" s="2">
@@ -22214,7 +22178,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr">
@@ -22259,7 +22223,7 @@
       </c>
       <c r="T104" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -22281,19 +22245,16 @@
         <f>IF(A105="","",IF(ISNUMBER(I105),MAX(E105,I105),E105))</f>
         <v/>
       </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E105" s="5">
+        <f>IF(ISNUMBER(F105),MAX(DATE(2026,5,27),(F105+7)+CHOOSE(WEEKDAY(F105+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-3-M-26</t>
         </is>
       </c>
       <c r="H105" s="2">
@@ -22311,7 +22272,7 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L105" s="3" t="inlineStr">
@@ -22356,7 +22317,7 @@
       </c>
       <c r="T105" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -22378,14 +22339,13 @@
         <f>IF(A106="","",IF(ISNUMBER(I106),MAX(E106,I106),E106))</f>
         <v/>
       </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E106" s="5">
+        <f>IF(ISNUMBER(F106),MAX(DATE(2026,5,27),(F106+7)+CHOOSE(WEEKDAY(F106+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -22408,7 +22368,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr">
@@ -22453,7 +22413,7 @@
       </c>
       <c r="T106" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -22475,19 +22435,16 @@
         <f>IF(A107="","",IF(ISNUMBER(I107),MAX(E107,I107),E107))</f>
         <v/>
       </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E107" s="5">
+        <f>IF(ISNUMBER(F107),MAX(DATE(2026,5,27),(F107+7)+CHOOSE(WEEKDAY(F107+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>46265</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>548-1079-26</t>
         </is>
       </c>
       <c r="H107" s="2">
@@ -22505,7 +22462,7 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L107" s="3" t="inlineStr">
@@ -22550,7 +22507,7 @@
       </c>
       <c r="T107" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -22572,14 +22529,13 @@
         <f>IF(A108="","",IF(ISNUMBER(I108),MAX(E108,I108),E108))</f>
         <v/>
       </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E108" s="5">
+        <f>IF(ISNUMBER(F108),MAX(DATE(2026,5,27),(F108+7)+CHOOSE(WEEKDAY(F108+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -22602,7 +22558,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr">
@@ -22647,7 +22603,7 @@
       </c>
       <c r="T108" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -22669,19 +22625,16 @@
         <f>IF(A109="","",IF(ISNUMBER(I109),MAX(E109,I109),E109))</f>
         <v/>
       </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E109" s="5">
+        <f>IF(ISNUMBER(F109),MAX(DATE(2026,5,27),(F109+7)+CHOOSE(WEEKDAY(F109+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>556-1087-26</t>
         </is>
       </c>
       <c r="H109" s="2">
@@ -22699,7 +22652,7 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L109" s="3" t="inlineStr">
@@ -22744,7 +22697,7 @@
       </c>
       <c r="T109" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -22766,19 +22719,16 @@
         <f>IF(A110="","",IF(ISNUMBER(I110),MAX(E110,I110),E110))</f>
         <v/>
       </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E110" s="5">
+        <f>IF(ISNUMBER(F110),MAX(DATE(2026,5,27),(F110+7)+CHOOSE(WEEKDAY(F110+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>555-1086-26</t>
         </is>
       </c>
       <c r="H110" s="2">
@@ -22796,7 +22746,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr">
@@ -22841,7 +22791,7 @@
       </c>
       <c r="T110" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -22863,14 +22813,13 @@
         <f>IF(A111="","",IF(ISNUMBER(I111),MAX(E111,I111),E111))</f>
         <v/>
       </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E111" s="5">
+        <f>IF(ISNUMBER(F111),MAX(DATE(2026,5,27),(F111+7)+CHOOSE(WEEKDAY(F111+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -22893,7 +22842,7 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L111" s="3" t="inlineStr">
@@ -22938,7 +22887,7 @@
       </c>
       <c r="T111" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -22960,14 +22909,13 @@
         <f>IF(A112="","",IF(ISNUMBER(I112),MAX(E112,I112),E112))</f>
         <v/>
       </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E112" s="5">
+        <f>IF(ISNUMBER(F112),MAX(DATE(2026,5,27),(F112+7)+CHOOSE(WEEKDAY(F112+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -22990,7 +22938,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr">
@@ -23035,7 +22983,7 @@
       </c>
       <c r="T112" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -23057,14 +23005,13 @@
         <f>IF(A113="","",IF(ISNUMBER(I113),MAX(E113,I113),E113))</f>
         <v/>
       </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E113" s="5">
+        <f>IF(ISNUMBER(F113),MAX(DATE(2026,5,27),(F113+7)+CHOOSE(WEEKDAY(F113+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -23087,7 +23034,7 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L113" s="3" t="inlineStr">
@@ -23132,7 +23079,7 @@
       </c>
       <c r="T113" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -23154,19 +23101,16 @@
         <f>IF(A114="","",IF(ISNUMBER(I114),MAX(E114,I114),E114))</f>
         <v/>
       </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E114" s="5">
+        <f>IF(ISNUMBER(F114),MAX(DATE(2026,5,27),(F114+7)+CHOOSE(WEEKDAY(F114+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-12-M-26</t>
         </is>
       </c>
       <c r="H114" s="2">
@@ -23184,7 +23128,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr">
@@ -23229,7 +23173,7 @@
       </c>
       <c r="T114" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -23251,14 +23195,13 @@
         <f>IF(A115="","",IF(ISNUMBER(I115),MAX(E115,I115),E115))</f>
         <v/>
       </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E115" s="5">
+        <f>IF(ISNUMBER(F115),MAX(DATE(2026,5,27),(F115+7)+CHOOSE(WEEKDAY(F115+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -23281,7 +23224,7 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L115" s="3" t="inlineStr">
@@ -23326,7 +23269,7 @@
       </c>
       <c r="T115" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -23348,14 +23291,13 @@
         <f>IF(A116="","",IF(ISNUMBER(I116),MAX(E116,I116),E116))</f>
         <v/>
       </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E116" s="5">
+        <f>IF(ISNUMBER(F116),MAX(DATE(2026,5,27),(F116+7)+CHOOSE(WEEKDAY(F116+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -23378,7 +23320,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr">
@@ -23423,7 +23365,7 @@
       </c>
       <c r="T116" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -23445,19 +23387,16 @@
         <f>IF(A117="","",IF(ISNUMBER(I117),MAX(E117,I117),E117))</f>
         <v/>
       </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E117" s="5">
+        <f>IF(ISNUMBER(F117),MAX(DATE(2026,5,27),(F117+7)+CHOOSE(WEEKDAY(F117+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>553-1084-26</t>
         </is>
       </c>
       <c r="H117" s="2">
@@ -23475,7 +23414,7 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L117" s="3" t="inlineStr">
@@ -23520,7 +23459,7 @@
       </c>
       <c r="T117" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -23542,19 +23481,16 @@
         <f>IF(A118="","",IF(ISNUMBER(I118),MAX(E118,I118),E118))</f>
         <v/>
       </c>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E118" s="5">
+        <f>IF(ISNUMBER(F118),MAX(DATE(2026,5,27),(F118+7)+CHOOSE(WEEKDAY(F118+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>554-1085-26</t>
         </is>
       </c>
       <c r="H118" s="2">
@@ -23572,7 +23508,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr">
@@ -23617,7 +23553,7 @@
       </c>
       <c r="T118" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -23639,19 +23575,16 @@
         <f>IF(A119="","",IF(ISNUMBER(I119),MAX(E119,I119),E119))</f>
         <v/>
       </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E119" s="5">
+        <f>IF(ISNUMBER(F119),MAX(DATE(2026,5,27),(F119+7)+CHOOSE(WEEKDAY(F119+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-4-M-26</t>
         </is>
       </c>
       <c r="H119" s="2">
@@ -23669,7 +23602,7 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L119" s="3" t="inlineStr">
@@ -23714,7 +23647,7 @@
       </c>
       <c r="T119" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -23736,19 +23669,16 @@
         <f>IF(A120="","",IF(ISNUMBER(I120),MAX(E120,I120),E120))</f>
         <v/>
       </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E120" s="5">
+        <f>IF(ISNUMBER(F120),MAX(DATE(2026,5,27),(F120+7)+CHOOSE(WEEKDAY(F120+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-5-M-26</t>
         </is>
       </c>
       <c r="H120" s="2">
@@ -23766,7 +23696,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr">
@@ -23811,7 +23741,7 @@
       </c>
       <c r="T120" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -23833,14 +23763,13 @@
         <f>IF(A121="","",IF(ISNUMBER(I121),MAX(E121,I121),E121))</f>
         <v/>
       </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E121" s="5">
+        <f>IF(ISNUMBER(F121),MAX(DATE(2026,5,27),(F121+7)+CHOOSE(WEEKDAY(F121+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -23863,7 +23792,7 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L121" s="3" t="inlineStr">
@@ -23908,7 +23837,7 @@
       </c>
       <c r="T121" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -23930,19 +23859,16 @@
         <f>IF(A122="","",IF(ISNUMBER(I122),MAX(E122,I122),E122))</f>
         <v/>
       </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E122" s="5">
+        <f>IF(ISNUMBER(F122),MAX(DATE(2026,5,27),(F122+7)+CHOOSE(WEEKDAY(F122+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-20-M-26</t>
         </is>
       </c>
       <c r="H122" s="2">
@@ -23960,7 +23886,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr">
@@ -24005,7 +23931,7 @@
       </c>
       <c r="T122" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -24027,14 +23953,13 @@
         <f>IF(A123="","",IF(ISNUMBER(I123),MAX(E123,I123),E123))</f>
         <v/>
       </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E123" s="5">
+        <f>IF(ISNUMBER(F123),MAX(DATE(2026,5,27),(F123+7)+CHOOSE(WEEKDAY(F123+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -24057,7 +23982,7 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L123" s="3" t="inlineStr">
@@ -24102,7 +24027,7 @@
       </c>
       <c r="T123" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -24124,14 +24049,13 @@
         <f>IF(A124="","",IF(ISNUMBER(I124),MAX(E124,I124),E124))</f>
         <v/>
       </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E124" s="5">
+        <f>IF(ISNUMBER(F124),MAX(DATE(2026,5,27),(F124+7)+CHOOSE(WEEKDAY(F124+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -24154,7 +24078,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr">
@@ -24195,7 +24119,7 @@
       </c>
       <c r="T124" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -24217,14 +24141,13 @@
         <f>IF(A125="","",IF(ISNUMBER(I125),MAX(E125,I125),E125))</f>
         <v/>
       </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E125" s="5">
+        <f>IF(ISNUMBER(F125),MAX(DATE(2026,5,27),(F125+7)+CHOOSE(WEEKDAY(F125+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -24247,7 +24170,7 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L125" s="3" t="inlineStr">
@@ -24292,7 +24215,7 @@
       </c>
       <c r="T125" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -24314,19 +24237,16 @@
         <f>IF(A126="","",IF(ISNUMBER(I126),MAX(E126,I126),E126))</f>
         <v/>
       </c>
-      <c r="E126" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E126" s="5">
+        <f>IF(ISNUMBER(F126),MAX(DATE(2026,5,27),(F126+7)+CHOOSE(WEEKDAY(F126+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>552-1083-26</t>
         </is>
       </c>
       <c r="H126" s="2">
@@ -24344,7 +24264,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr">
@@ -24389,7 +24309,7 @@
       </c>
       <c r="T126" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -24411,19 +24331,16 @@
         <f>IF(A127="","",IF(ISNUMBER(I127),MAX(E127,I127),E127))</f>
         <v/>
       </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E127" s="5">
+        <f>IF(ISNUMBER(F127),MAX(DATE(2026,5,27),(F127+7)+CHOOSE(WEEKDAY(F127+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>46265</v>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>549-1080-26</t>
         </is>
       </c>
       <c r="H127" s="2">
@@ -24441,7 +24358,7 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L127" s="3" t="inlineStr">
@@ -24486,7 +24403,7 @@
       </c>
       <c r="T127" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -24508,14 +24425,13 @@
         <f>IF(A128="","",IF(ISNUMBER(I128),MAX(E128,I128),E128))</f>
         <v/>
       </c>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E128" s="5">
+        <f>IF(ISNUMBER(F128),MAX(DATE(2026,5,27),(F128+7)+CHOOSE(WEEKDAY(F128+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -24538,7 +24454,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr">
@@ -24583,7 +24499,7 @@
       </c>
       <c r="T128" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -24605,19 +24521,16 @@
         <f>IF(A129="","",IF(ISNUMBER(I129),MAX(E129,I129),E129))</f>
         <v/>
       </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E129" s="5">
+        <f>IF(ISNUMBER(F129),MAX(DATE(2026,5,27),(F129+7)+CHOOSE(WEEKDAY(F129+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-16-M-26</t>
         </is>
       </c>
       <c r="H129" s="2">
@@ -24635,7 +24548,7 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L129" s="3" t="inlineStr">
@@ -24680,7 +24593,7 @@
       </c>
       <c r="T129" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -24702,19 +24615,16 @@
         <f>IF(A130="","",IF(ISNUMBER(I130),MAX(E130,I130),E130))</f>
         <v/>
       </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E130" s="5">
+        <f>IF(ISNUMBER(F130),MAX(DATE(2026,5,27),(F130+7)+CHOOSE(WEEKDAY(F130+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>46265</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>546-1077-26</t>
         </is>
       </c>
       <c r="H130" s="2">
@@ -24732,7 +24642,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr">
@@ -24777,7 +24687,7 @@
       </c>
       <c r="T130" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -24799,14 +24709,13 @@
         <f>IF(A131="","",IF(ISNUMBER(I131),MAX(E131,I131),E131))</f>
         <v/>
       </c>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E131" s="5">
+        <f>IF(ISNUMBER(F131),MAX(DATE(2026,5,27),(F131+7)+CHOOSE(WEEKDAY(F131+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -24829,7 +24738,7 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L131" s="3" t="inlineStr">
@@ -24874,7 +24783,7 @@
       </c>
       <c r="T131" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -24896,19 +24805,16 @@
         <f>IF(A132="","",IF(ISNUMBER(I132),MAX(E132,I132),E132))</f>
         <v/>
       </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E132" s="5">
+        <f>IF(ISNUMBER(F132),MAX(DATE(2026,5,27),(F132+7)+CHOOSE(WEEKDAY(F132+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>550-1081-26</t>
         </is>
       </c>
       <c r="H132" s="2">
@@ -24926,7 +24832,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr">
@@ -24971,7 +24877,7 @@
       </c>
       <c r="T132" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -24993,19 +24899,16 @@
         <f>IF(A133="","",IF(ISNUMBER(I133),MAX(E133,I133),E133))</f>
         <v/>
       </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E133" s="5">
+        <f>IF(ISNUMBER(F133),MAX(DATE(2026,5,27),(F133+7)+CHOOSE(WEEKDAY(F133+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>46265</v>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>547-1078-26</t>
         </is>
       </c>
       <c r="H133" s="2">
@@ -25023,7 +24926,7 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L133" s="3" t="inlineStr">
@@ -25068,7 +24971,7 @@
       </c>
       <c r="T133" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -25090,19 +24993,16 @@
         <f>IF(A134="","",IF(ISNUMBER(I134),MAX(E134,I134),E134))</f>
         <v/>
       </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E134" s="5">
+        <f>IF(ISNUMBER(F134),MAX(DATE(2026,5,27),(F134+7)+CHOOSE(WEEKDAY(F134+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-15-M-26</t>
         </is>
       </c>
       <c r="H134" s="2">
@@ -25120,7 +25020,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr">
@@ -25165,7 +25065,7 @@
       </c>
       <c r="T134" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -25187,14 +25087,13 @@
         <f>IF(A135="","",IF(ISNUMBER(I135),MAX(E135,I135),E135))</f>
         <v/>
       </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E135" s="5">
+        <f>IF(ISNUMBER(F135),MAX(DATE(2026,5,27),(F135+7)+CHOOSE(WEEKDAY(F135+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -25217,7 +25116,7 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
@@ -25262,7 +25161,7 @@
       </c>
       <c r="T135" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -25284,19 +25183,16 @@
         <f>IF(A136="","",IF(ISNUMBER(I136),MAX(E136,I136),E136))</f>
         <v/>
       </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E136" s="5">
+        <f>IF(ISNUMBER(F136),MAX(DATE(2026,5,27),(F136+7)+CHOOSE(WEEKDAY(F136+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>46135</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1628-2026</t>
         </is>
       </c>
       <c r="H136" s="2">
@@ -25314,7 +25210,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr">
@@ -25332,9 +25228,9 @@
           <t>Jokerz 31</t>
         </is>
       </c>
-      <c r="O136" s="6" t="inlineStr">
-        <is>
-          <t>— retest assay not yet on file —</t>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>100-3-K-26, (09.04.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P136" s="6" t="inlineStr">
@@ -25359,7 +25255,7 @@
       </c>
       <c r="T136" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins and microbiology on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -25381,14 +25277,13 @@
         <f>IF(A137="","",IF(ISNUMBER(I137),MAX(E137,I137),E137))</f>
         <v/>
       </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E137" s="5">
+        <f>IF(ISNUMBER(F137),MAX(DATE(2026,5,27),(F137+7)+CHOOSE(WEEKDAY(F137+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -25411,7 +25306,7 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L137" s="3" t="inlineStr">
@@ -25456,7 +25351,7 @@
       </c>
       <c r="T137" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -25478,19 +25373,16 @@
         <f>IF(A138="","",IF(ISNUMBER(I138),MAX(E138,I138),E138))</f>
         <v/>
       </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F138" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E138" s="5">
+        <f>IF(ISNUMBER(F138),MAX(DATE(2026,5,27),(F138+7)+CHOOSE(WEEKDAY(F138+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-19-M-26</t>
         </is>
       </c>
       <c r="H138" s="2">
@@ -25508,7 +25400,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — Tranche 1 (sampled July 2026)</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr">
@@ -25553,7 +25445,7 @@
       </c>
       <c r="T138" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -25575,19 +25467,16 @@
         <f>IF(A139="","",IF(ISNUMBER(I139),MAX(E139,I139),E139))</f>
         <v/>
       </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E139" s="5">
+        <f>IF(ISNUMBER(F139),MAX(DATE(2026,5,27),(F139+7)+CHOOSE(WEEKDAY(F139+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>46265</v>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>543-1074-26</t>
         </is>
       </c>
       <c r="H139" s="2">
@@ -25605,7 +25494,7 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L139" s="3" t="inlineStr">
@@ -25650,7 +25539,7 @@
       </c>
       <c r="T139" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -25672,19 +25561,16 @@
         <f>IF(A140="","",IF(ISNUMBER(I140),MAX(E140,I140),E140))</f>
         <v/>
       </c>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E140" s="5">
+        <f>IF(ISNUMBER(F140),MAX(DATE(2026,5,27),(F140+7)+CHOOSE(WEEKDAY(F140+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>46265</v>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>542-1073-26</t>
         </is>
       </c>
       <c r="H140" s="2">
@@ -25702,7 +25588,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr">
@@ -25747,7 +25633,7 @@
       </c>
       <c r="T140" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -25769,19 +25655,16 @@
         <f>IF(A141="","",IF(ISNUMBER(I141),MAX(E141,I141),E141))</f>
         <v/>
       </c>
-      <c r="E141" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E141" s="5">
+        <f>IF(ISNUMBER(F141),MAX(DATE(2026,5,27),(F141+7)+CHOOSE(WEEKDAY(F141+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>46265</v>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541-1072-26</t>
         </is>
       </c>
       <c r="H141" s="2">
@@ -25799,7 +25682,7 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L141" s="3" t="inlineStr">
@@ -25844,7 +25727,7 @@
       </c>
       <c r="T141" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -25866,19 +25749,16 @@
         <f>IF(A142="","",IF(ISNUMBER(I142),MAX(E142,I142),E142))</f>
         <v/>
       </c>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E142" s="5">
+        <f>IF(ISNUMBER(F142),MAX(DATE(2026,5,27),(F142+7)+CHOOSE(WEEKDAY(F142+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>46265</v>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>545-1076-26</t>
         </is>
       </c>
       <c r="H142" s="2">
@@ -25896,7 +25776,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr">
@@ -25941,7 +25821,7 @@
       </c>
       <c r="T142" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -25963,19 +25843,16 @@
         <f>IF(A143="","",IF(ISNUMBER(I143),MAX(E143,I143),E143))</f>
         <v/>
       </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E143" s="5">
+        <f>IF(ISNUMBER(F143),MAX(DATE(2026,5,27),(F143+7)+CHOOSE(WEEKDAY(F143+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>46266</v>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>557-1088-26</t>
         </is>
       </c>
       <c r="H143" s="2">
@@ -25993,7 +25870,7 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L143" s="3" t="inlineStr">
@@ -26038,7 +25915,7 @@
       </c>
       <c r="T143" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -26060,19 +25937,16 @@
         <f>IF(A144="","",IF(ISNUMBER(I144),MAX(E144,I144),E144))</f>
         <v/>
       </c>
-      <c r="E144" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F144" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E144" s="5">
+        <f>IF(ISNUMBER(F144),MAX(DATE(2026,5,27),(F144+7)+CHOOSE(WEEKDAY(F144+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>46265</v>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540-1071-26</t>
         </is>
       </c>
       <c r="H144" s="2">
@@ -26090,7 +25964,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr">
@@ -26135,7 +26009,7 @@
       </c>
       <c r="T144" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -26157,14 +26031,13 @@
         <f>IF(A145="","",IF(ISNUMBER(I145),MAX(E145,I145),E145))</f>
         <v/>
       </c>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E145" s="5">
+        <f>IF(ISNUMBER(F145),MAX(DATE(2026,5,27),(F145+7)+CHOOSE(WEEKDAY(F145+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -26187,7 +26060,7 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L145" s="3" t="inlineStr">
@@ -26232,7 +26105,7 @@
       </c>
       <c r="T145" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -26254,14 +26127,13 @@
         <f>IF(A146="","",IF(ISNUMBER(I146),MAX(E146,I146),E146))</f>
         <v/>
       </c>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E146" s="5">
+        <f>IF(ISNUMBER(F146),MAX(DATE(2026,5,27),(F146+7)+CHOOSE(WEEKDAY(F146+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -26284,7 +26156,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr">
@@ -26329,7 +26201,7 @@
       </c>
       <c r="T146" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -26351,19 +26223,16 @@
         <f>IF(A147="","",IF(ISNUMBER(I147),MAX(E147,I147),E147))</f>
         <v/>
       </c>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E147" s="5">
+        <f>IF(ISNUMBER(F147),MAX(DATE(2026,5,27),(F147+7)+CHOOSE(WEEKDAY(F147+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-7-M-26</t>
         </is>
       </c>
       <c r="H147" s="2">
@@ -26381,7 +26250,7 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="L147" s="3" t="inlineStr">
@@ -26426,7 +26295,7 @@
       </c>
       <c r="T147" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -26448,19 +26317,16 @@
         <f>IF(A148="","",IF(ISNUMBER(I148),MAX(E148,I148),E148))</f>
         <v/>
       </c>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F148" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E148" s="5">
+        <f>IF(ISNUMBER(F148),MAX(DATE(2026,5,27),(F148+7)+CHOOSE(WEEKDAY(F148+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>46203</v>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ППК26113</t>
         </is>
       </c>
       <c r="H148" s="2">
@@ -26478,7 +26344,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr">
@@ -26492,9 +26358,9 @@
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr"/>
-      <c r="O148" s="6" t="inlineStr">
-        <is>
-          <t>— retest assay not yet on file —</t>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>ППК26113, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P148" s="6" t="inlineStr">
@@ -26519,7 +26385,7 @@
       </c>
       <c r="T148" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay on file, mycotoxins pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -26541,19 +26407,16 @@
         <f>IF(A149="","",IF(ISNUMBER(I149),MAX(E149,I149),E149))</f>
         <v/>
       </c>
-      <c r="E149" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E149" s="5">
+        <f>IF(ISNUMBER(F149),MAX(DATE(2026,5,27),(F149+7)+CHOOSE(WEEKDAY(F149+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>46203</v>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ППК26113</t>
         </is>
       </c>
       <c r="H149" s="2">
@@ -26571,7 +26434,7 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="L149" s="3" t="inlineStr">
@@ -26585,9 +26448,9 @@
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr"/>
-      <c r="O149" s="6" t="inlineStr">
-        <is>
-          <t>— retest assay not yet on file —</t>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>ППК26113, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P149" s="6" t="inlineStr">
@@ -26612,7 +26475,7 @@
       </c>
       <c r="T149" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay on file, mycotoxins pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -26634,19 +26497,16 @@
         <f>IF(A150="","",IF(ISNUMBER(I150),MAX(E150,I150),E150))</f>
         <v/>
       </c>
-      <c r="E150" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F150" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E150" s="5">
+        <f>IF(ISNUMBER(F150),MAX(DATE(2026,5,27),(F150+7)+CHOOSE(WEEKDAY(F150+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F150" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-8-M-26</t>
         </is>
       </c>
       <c r="H150" s="2">
@@ -26664,7 +26524,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr">
@@ -26709,7 +26569,7 @@
       </c>
       <c r="T150" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -26731,19 +26591,16 @@
         <f>IF(A151="","",IF(ISNUMBER(I151),MAX(E151,I151),E151))</f>
         <v/>
       </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E151" s="5">
+        <f>IF(ISNUMBER(F151),MAX(DATE(2026,5,27),(F151+7)+CHOOSE(WEEKDAY(F151+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>46203</v>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ППК26113</t>
         </is>
       </c>
       <c r="H151" s="2">
@@ -26761,7 +26618,7 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="L151" s="3" t="inlineStr">
@@ -26775,9 +26632,9 @@
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr"/>
-      <c r="O151" s="6" t="inlineStr">
-        <is>
-          <t>— retest assay not yet on file —</t>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>ППК26113, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P151" s="6" t="inlineStr">
@@ -26802,7 +26659,7 @@
       </c>
       <c r="T151" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay on file, mycotoxins pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -26824,19 +26681,16 @@
         <f>IF(A152="","",IF(ISNUMBER(I152),MAX(E152,I152),E152))</f>
         <v/>
       </c>
-      <c r="E152" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
-      </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>at retest</t>
-        </is>
+      <c r="E152" s="5">
+        <f>IF(ISNUMBER(F152),MAX(DATE(2026,5,27),(F152+7)+CHOOSE(WEEKDAY(F152+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>46244</v>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197-21-M-26</t>
         </is>
       </c>
       <c r="H152" s="2">
@@ -26854,7 +26708,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — re-analysed</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr">
@@ -26899,7 +26753,7 @@
       </c>
       <c r="T152" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — due — retest assay and mycotoxins on file · at retest sampling</t>
+          <t>not yet issuable — due — retest assay, mycotoxins on file; in-house iCoA to test · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -26921,14 +26775,13 @@
         <f>IF(A153="","",IF(ISNUMBER(I153),MAX(E153,I153),E153))</f>
         <v/>
       </c>
-      <c r="E153" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E153" s="5">
+        <f>IF(ISNUMBER(F153),MAX(DATE(2026,5,27),(F153+7)+CHOOSE(WEEKDAY(F153+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -26951,7 +26804,7 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L153" s="3" t="inlineStr">
@@ -26996,7 +26849,7 @@
       </c>
       <c r="T153" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -27018,14 +26871,13 @@
         <f>IF(A154="","",IF(ISNUMBER(I154),MAX(E154,I154),E154))</f>
         <v/>
       </c>
-      <c r="E154" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E154" s="5">
+        <f>IF(ISNUMBER(F154),MAX(DATE(2026,5,27),(F154+7)+CHOOSE(WEEKDAY(F154+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -27048,7 +26900,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr">
@@ -27093,7 +26945,7 @@
       </c>
       <c r="T154" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -27115,14 +26967,13 @@
         <f>IF(A155="","",IF(ISNUMBER(I155),MAX(E155,I155),E155))</f>
         <v/>
       </c>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E155" s="5">
+        <f>IF(ISNUMBER(F155),MAX(DATE(2026,5,27),(F155+7)+CHOOSE(WEEKDAY(F155+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -27145,7 +26996,7 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L155" s="3" t="inlineStr">
@@ -27190,7 +27041,7 @@
       </c>
       <c r="T155" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -27212,14 +27063,13 @@
         <f>IF(A156="","",IF(ISNUMBER(I156),MAX(E156,I156),E156))</f>
         <v/>
       </c>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E156" s="5">
+        <f>IF(ISNUMBER(F156),MAX(DATE(2026,5,27),(F156+7)+CHOOSE(WEEKDAY(F156+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -27242,7 +27092,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr">
@@ -27287,7 +27137,7 @@
       </c>
       <c r="T156" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -27309,14 +27159,13 @@
         <f>IF(A157="","",IF(ISNUMBER(I157),MAX(E157,I157),E157))</f>
         <v/>
       </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E157" s="5">
+        <f>IF(ISNUMBER(F157),MAX(DATE(2026,5,27),(F157+7)+CHOOSE(WEEKDAY(F157+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -27339,7 +27188,7 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L157" s="3" t="inlineStr">
@@ -27384,7 +27233,7 @@
       </c>
       <c r="T157" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -27406,14 +27255,13 @@
         <f>IF(A158="","",IF(ISNUMBER(I158),MAX(E158,I158),E158))</f>
         <v/>
       </c>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>at retest sampling</t>
-        </is>
+      <c r="E158" s="5">
+        <f>IF(ISNUMBER(F158),MAX(DATE(2026,5,27),(F158+7)+CHOOSE(WEEKDAY(F158+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <v/>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>at retest</t>
+          <t>— not yet sampled —</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -27436,7 +27284,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>retest — QP campaign</t>
+          <t>retest — not yet sampled</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr">
@@ -27481,14 +27329,14 @@
       </c>
       <c r="T158" s="8" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — retest assay not yet on file · at retest sampling</t>
+          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
     <row r="160" ht="150" customHeight="1">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; a CoQ with an uncertified determination is not issuable and carries no number (Status names the gaps); nothing is dated on a weekend. FORMULAS: No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the later of the rule date and the iCoA's date; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination, the retest assay and mycotoxins excluded), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060142: legacy CoQ cannot be dated 27.05.2026 — it cites 550-1081-26 of 01.09.2026; planned 08.09.2026 (first working day 7 days after) | P060182: legacy CoQ cannot be dated 27.05.2026 — it cites 550-1081-26 of 01.09.2026; planned 08.09.2026 (first working day 7 days after) | HPA1024: legacy CoQ cannot be dated 27.05.2026 — it cites 197-13-M-26 of 10.08.2026; planned 17.08.2026 (first working day 7 days after) | P060152: legacy CoQ cannot be dated 27.05.2026 — it cites 197-16-M-26 of 10.08.2026; planned 17.08.2026 (first working day 7 days after) | P060202: legacy CoQ cannot be dated 27.05.2026 — it cites 547-1078-26 of 31.08.2026; planned 07.09.2026 (first working day 7 days after) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | OPM1024: legacy CoQ cannot be dated 27.05.2026 — it cites 197-17-M-26 of 10.08.2026; planned 17.08.2026 (first working day 7 days after) | P060222: legacy CoQ cannot be dated 27.05.2026 — it cites 546-1077-26 of 31.08.2026; planned 07.09.2026 (first working day 7 days after) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: legacy CoQ cannot be dated 27.05.2026 — it cites 549-1080-26 of 31.08.2026; planned 07.09.2026 (first working day 7 days after) | P050142: legacy CoQ cannot be dated 27.05.2026 — it cites 559-1090-26 of 01.09.2026; planned 08.09.2026 (first working day 7 days after) | P060102: legacy CoQ cannot be dated 27.05.2026 — it cites 551-1082-26 of 01.09.2026; planned 08.09.2026 (first working day 7 days after)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; a CoQ with an uncertified determination is not issuable and carries no number (Status names the gaps); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins, microbiology by IJZ-MB) and the initial certificates for the rest; its rule date is the first working day 7 days after the latest retest certificate, and it is issued once the in-house retest iCoA exists. FORMULAS: No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the later of the rule date and the iCoA's date; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #9 — only the retest 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
@@ -30873,7 +30721,7 @@
     <row r="3" ht="190" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; a CoQ with an uncertified determination is not issuable and carries no number (Status names the gaps); nothing is dated on a weekend. FORMULAS: No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the later of the rule date and the iCoA's date; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination, the retest assay and mycotoxins excluded), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060142: legacy CoQ cannot be dated 27.05.2026 — it cites 550-1081-26 of 01.09.2026; planned 08.09.2026 (first working day 7 days after) | P060182: legacy CoQ cannot be dated 27.05.2026 — it cites 550-1081-26 of 01.09.2026; planned 08.09.2026 (first working day 7 days after) | HPA1024: legacy CoQ cannot be dated 27.05.2026 — it cites 197-13-M-26 of 10.08.2026; planned 17.08.2026 (first working day 7 days after) | P060152: legacy CoQ cannot be dated 27.05.2026 — it cites 197-16-M-26 of 10.08.2026; planned 17.08.2026 (first working day 7 days after) | P060202: legacy CoQ cannot be dated 27.05.2026 — it cites 547-1078-26 of 31.08.2026; planned 07.09.2026 (first working day 7 days after) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | OPM1024: legacy CoQ cannot be dated 27.05.2026 — it cites 197-17-M-26 of 10.08.2026; planned 17.08.2026 (first working day 7 days after) | P060222: legacy CoQ cannot be dated 27.05.2026 — it cites 546-1077-26 of 31.08.2026; planned 07.09.2026 (first working day 7 days after) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: legacy CoQ cannot be dated 27.05.2026 — it cites 549-1080-26 of 31.08.2026; planned 07.09.2026 (first working day 7 days after) | P050142: legacy CoQ cannot be dated 27.05.2026 — it cites 559-1090-26 of 01.09.2026; planned 08.09.2026 (first working day 7 days after) | P060102: legacy CoQ cannot be dated 27.05.2026 — it cites 551-1082-26 of 01.09.2026; planned 08.09.2026 (first working day 7 days after)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; a CoQ with an uncertified determination is not issuable and carries no number (Status names the gaps); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins, microbiology by IJZ-MB) and the initial certificates for the rest; its rule date is the first working day 7 days after the latest retest certificate, and it is issued once the in-house retest iCoA exists. FORMULAS: No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the later of the rule date and the iCoA's date; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #9 — only the retest 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -12971,7 +12971,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>retest — not yet sampled</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>retest — not yet sampled</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>retest — not yet sampled</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #3, #4, #5, #6, #8, #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #3, #4, #5, #6, #8, #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="T7" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #3, #4, #5, #6, #8, #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="T22" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #3, #4, #5, #6, #8, #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #3, #4, #5, #6, #8, #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18000,7 @@
       </c>
       <c r="T48" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="T49" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -18188,7 +18188,7 @@
       </c>
       <c r="T50" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -18282,7 +18282,7 @@
       </c>
       <c r="T51" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -18376,7 +18376,7 @@
       </c>
       <c r="T52" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="T53" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="T54" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -18846,7 +18846,7 @@
       </c>
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -18940,7 +18940,7 @@
       </c>
       <c r="T58" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="T67" s="7" t="inlineStr">
         <is>
-          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate (CNP): #3, #4, #5, #6, #8, #9, #10, #11, #12</t>
+          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -19974,7 +19974,7 @@
       </c>
       <c r="T69" s="7" t="inlineStr">
         <is>
-          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate (CNP): #3, #4, #5, #6, #8, #9, #10, #11, #12</t>
+          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -20011,11 +20011,11 @@
         </is>
       </c>
       <c r="H70" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060382|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060342|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I70" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060382|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060342|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>SCR012603</t>
+          <t>SCR012601* (from the list)</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>P060382</t>
+          <t>P060342</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -20060,17 +20060,17 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0026</t>
+          <t>— not in the issuance plan —</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>P060382|I</t>
+          <t>P060342|I</t>
         </is>
       </c>
       <c r="T70" s="7" t="inlineStr">
         <is>
-          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate (CNP): #3, #4, #5, #6, #8, #9, #10, #11, #12</t>
+          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -20096,20 +20096,22 @@
         <f>IF(ISNUMBER(F71),IF(AND(J71="legacy",F71&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F71+7)+CHOOSE(WEEKDAY(F71+7,2),0,0,0,0,0,2,1))),IF(J71="legacy",DATE(2026,5,27),""))</f>
         <v/>
       </c>
-      <c r="F71" s="5" t="n">
-        <v>46203</v>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>ППК26111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H71" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060362|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060382|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I71" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060362|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060382|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -20124,23 +20126,27 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>JD012603</t>
+          <t>SCR012603</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>P060362</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>ППК26111, (30.06.2026) [CNP]</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
+          <t>P060382</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="O71" s="6" t="inlineStr">
+        <is>
+          <t>— no cannabinoid certificate from the initial testing —</t>
+        </is>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -20150,17 +20156,17 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0020</t>
+          <t>CoQ-PP-2026-0026</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>P060362|I</t>
+          <t>P060382|I</t>
         </is>
       </c>
       <c r="T71" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -20191,15 +20197,15 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>ППК26111</t>
+          <t>ППК26110</t>
         </is>
       </c>
       <c r="H72" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060422|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060392|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I72" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060422|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060392|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -20214,23 +20220,27 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>JD012603</t>
+          <t>FB012603V</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>P060422</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>P060392</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ППК26111, (30.06.2026) [CNP]</t>
+          <t>ППК26110, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
+          <t>A: ППК26110 / B: ППК26110 / FM: ППК26110</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -20240,17 +20250,17 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0022</t>
+          <t>(assigned on issue)</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>P060422|I</t>
+          <t>P060392|I</t>
         </is>
       </c>
       <c r="T72" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -20281,15 +20291,15 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>ППК26114</t>
+          <t>ППК26111</t>
         </is>
       </c>
       <c r="H73" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060402|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060362|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I73" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060402|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060362|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -20304,27 +20314,23 @@
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>GG012603</t>
+          <t>JD012603</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>P060402</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>GorillaGlue</t>
-        </is>
-      </c>
+          <t>P060362</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ППК26114, (30.06.2026) [CNP]</t>
+          <t>ППК26111, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26114 / B: ППК26114 / FM: ППК26114</t>
+          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -20334,17 +20340,17 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0023</t>
+          <t>CoQ-PP-2026-0020</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>P060402|I</t>
+          <t>P060362|I</t>
         </is>
       </c>
       <c r="T73" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -20379,11 +20385,11 @@
         </is>
       </c>
       <c r="H74" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060412|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060422|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I74" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060412|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060422|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -20403,7 +20409,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>P060412</t>
+          <t>P060422</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr"/>
@@ -20424,17 +20430,17 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0025</t>
+          <t>CoQ-PP-2026-0022</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>P060412|I</t>
+          <t>P060422|I</t>
         </is>
       </c>
       <c r="T74" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -20461,19 +20467,19 @@
         <v/>
       </c>
       <c r="F75" s="5" t="n">
-        <v>46224</v>
+        <v>46203</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>ППК26127</t>
+          <t>ППК26114</t>
         </is>
       </c>
       <c r="H75" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060452|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060402|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I75" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060452|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060402|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -20488,27 +20494,27 @@
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>FB032601</t>
+          <t>GG012603</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>P060452</t>
+          <t>P060402</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>GorillaGlue</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ППК26127, (21.07.2026) [CNP]</t>
+          <t>ППК26114, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26127 / B: ППК26127 / FM: ППК26127</t>
+          <t>A: ППК26114 / B: ППК26114 / FM: ППК26114</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -20518,17 +20524,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>(assigned on issue)</t>
+          <t>CoQ-PP-2026-0023</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>P060452|I</t>
+          <t>P060402|I</t>
         </is>
       </c>
       <c r="T75" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -20555,19 +20561,19 @@
         <v/>
       </c>
       <c r="F76" s="5" t="n">
-        <v>46224</v>
+        <v>46203</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>ППК26128</t>
+          <t>ППК26111</t>
         </is>
       </c>
       <c r="H76" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060462|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060412|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I76" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060462|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060412|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -20582,27 +20588,23 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>GG032601</t>
+          <t>JD012603</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>P060462</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>GorillaGlue</t>
-        </is>
-      </c>
+          <t>P060412</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ППК26128, (21.07.2026) [CNP]</t>
+          <t>ППК26111, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26128 / B: ППК26128 / FM: ППК26128</t>
+          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -20612,17 +20614,17 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>(assigned on issue)</t>
+          <t>CoQ-PP-2026-0025</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>P060462|I</t>
+          <t>P060412|I</t>
         </is>
       </c>
       <c r="T76" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -20653,15 +20655,15 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>ППК26115</t>
+          <t>ППК26112</t>
         </is>
       </c>
       <c r="H77" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060482|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060432|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I77" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060482|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060432|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -20676,27 +20678,27 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>JD022601</t>
+          <t>FB012603</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>P060482</t>
+          <t>P060432</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ППК26115, (30.06.2026) [CNP]</t>
+          <t>ППК26112, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26115 / B: ППК26115 / FM: ППК26115</t>
+          <t>A: ППК26112 / B: ППК26112 / FM: ППК26112</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -20711,12 +20713,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>P060482|I</t>
+          <t>P060432|I</t>
         </is>
       </c>
       <c r="T77" s="7" t="inlineStr">
         <is>
-          <t>registered — held to the packaging date · initial certificate to locate (CNP): #9, #10, #11, #12</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -20743,19 +20745,19 @@
         <v/>
       </c>
       <c r="F78" s="5" t="n">
-        <v>46265</v>
+        <v>46209</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>538-1069-26</t>
+          <t>ППК26116</t>
         </is>
       </c>
       <c r="H78" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060392|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060442|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I78" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060392|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060442|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -20770,27 +20772,27 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>FB012603V</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>P060392</t>
+          <t>P060442</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ППК26110, (30.06.2026) [CNP]</t>
+          <t>ППК26116, (06.07.2026) [CNP]</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26110 / B: ППК26110 / FM: ППК26110</t>
+          <t>A: ППК26116 / B: ППК26116 / FM: ППК26116</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -20805,12 +20807,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>P060392|I</t>
+          <t>P060442|I</t>
         </is>
       </c>
       <c r="T78" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate (CNP): #10, #11, #12</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -20837,19 +20839,19 @@
         <v/>
       </c>
       <c r="F79" s="5" t="n">
-        <v>46265</v>
+        <v>46224</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>539-1070-26</t>
+          <t>ППК26127</t>
         </is>
       </c>
       <c r="H79" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060342|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060452|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I79" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060342|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060452|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -20864,27 +20866,27 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>SCR012601* (from the list)</t>
+          <t>FB032601</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>P060342</t>
+          <t>P060452</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-      <c r="O79" s="6" t="inlineStr">
-        <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
-        </is>
-      </c>
-      <c r="P79" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>FatBastard</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>ППК26127, (21.07.2026) [CNP]</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>A: ППК26127 / B: ППК26127 / FM: ППК26127</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -20894,17 +20896,17 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>— not in the issuance plan —</t>
+          <t>(assigned on issue)</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>P060342|I</t>
+          <t>P060452|I</t>
         </is>
       </c>
       <c r="T79" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate (CNP): #3, #4, #5, #6, #8, #10, #11, #12</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -20931,19 +20933,19 @@
         <v/>
       </c>
       <c r="F80" s="5" t="n">
-        <v>46265</v>
+        <v>46224</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>537-1068-26</t>
+          <t>ППК26128</t>
         </is>
       </c>
       <c r="H80" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060432|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060462|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I80" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060432|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060462|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -20958,27 +20960,27 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>FB012603</t>
+          <t>GG032601</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>P060432</t>
+          <t>P060462</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>GorillaGlue</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ППК26112, (30.06.2026) [CNP]</t>
+          <t>ППК26128, (21.07.2026) [CNP]</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26112 / B: ППК26112 / FM: ППК26112</t>
+          <t>A: ППК26128 / B: ППК26128 / FM: ППК26128</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -20993,12 +20995,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>P060432|I</t>
+          <t>P060462|I</t>
         </is>
       </c>
       <c r="T80" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate (CNP): #10, #11, #12</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -21025,19 +21027,19 @@
         <v/>
       </c>
       <c r="F81" s="5" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>536-1067-26</t>
+          <t>ППК26115</t>
         </is>
       </c>
       <c r="H81" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060442|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060482|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I81" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060442|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060482|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -21052,27 +21054,27 @@
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>JD022601</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>P060442</t>
+          <t>P060482</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>JellyDonutz</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ППК26116, (06.07.2026) [CNP]</t>
+          <t>ППК26115, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26116 / B: ППК26116 / FM: ППК26116</t>
+          <t>A: ППК26115 / B: ППК26115 / FM: ППК26115</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -21087,12 +21089,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>P060442|I</t>
+          <t>P060482|I</t>
         </is>
       </c>
       <c r="T81" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate (CNP): #10, #11, #12</t>
+          <t>registered — held to the packaging date · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -27808,14 +27810,12 @@
         <f>IF(ISNUMBER(F153),MAX(DATE(2026,5,27),(F153+7)+CHOOSE(WEEKDAY(F153+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
         <v/>
       </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>— not yet sampled —</t>
-        </is>
+      <c r="F153" s="5" t="n">
+        <v>46265</v>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>537-1068-26</t>
         </is>
       </c>
       <c r="H153" s="2">
@@ -27833,7 +27833,7 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>retest — not yet sampled</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L153" s="3" t="inlineStr">
@@ -27878,7 +27878,7 @@
       </c>
       <c r="T153" s="9" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -27904,14 +27904,12 @@
         <f>IF(ISNUMBER(F154),MAX(DATE(2026,5,27),(F154+7)+CHOOSE(WEEKDAY(F154+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
         <v/>
       </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>— not yet sampled —</t>
-        </is>
+      <c r="F154" s="5" t="n">
+        <v>46265</v>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>538-1069-26</t>
         </is>
       </c>
       <c r="H154" s="2">
@@ -27929,7 +27927,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>retest — not yet sampled</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr">
@@ -27974,7 +27972,7 @@
       </c>
       <c r="T154" s="9" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -28096,14 +28094,12 @@
         <f>IF(ISNUMBER(F156),MAX(DATE(2026,5,27),(F156+7)+CHOOSE(WEEKDAY(F156+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
         <v/>
       </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>— not yet sampled —</t>
-        </is>
+      <c r="F156" s="5" t="n">
+        <v>46265</v>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>536-1067-26</t>
         </is>
       </c>
       <c r="H156" s="2">
@@ -28121,7 +28117,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>retest — not yet sampled</t>
+          <t>retest — sampled — Tranche 2/3 (potency and mycotoxins pending)</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr">
@@ -28166,7 +28162,7 @@
       </c>
       <c r="T156" s="9" t="inlineStr">
         <is>
-          <t>not yet issuable — pending — not yet sampled · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
+          <t>not yet issuable — sampled — microbiology on file, retest assay pending · issued on the first working day 7 days after the latest retest certificate, once the in-house iCoA exists</t>
         </is>
       </c>
     </row>
@@ -28365,7 +28361,7 @@
     <row r="160" ht="150" customHeight="1">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins, microbiology by IJZ-MB) and the initial certificates for the rest; its rule date is the first working day 7 days after the latest retest certificate, and it is issued once the in-house retest iCoA exists. FORMULAS: No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 28.05.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 01.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #9 — only the retest 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins, microbiology by IJZ-MB) and the initial certificates for the rest; its rule date is the first working day 7 days after the latest retest certificate, and it is issued once the in-house retest iCoA exists. FORMULAS: No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 28.05.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 01.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #9 — only the retest 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 01.06.2026 | P060342: no initial certificate for #9 — only the retest 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
@@ -31750,7 +31746,7 @@
     <row r="3" ht="190" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins, microbiology by IJZ-MB) and the initial certificates for the rest; its rule date is the first working day 7 days after the latest retest certificate, and it is issued once the in-house retest iCoA exists. FORMULAS: No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 28.05.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 01.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #9 — only the retest 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins, microbiology by IJZ-MB) and the initial certificates for the rest; its rule date is the first working day 7 days after the latest retest certificate, and it is issued once the in-house retest iCoA exists. FORMULAS: No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 28.05.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 01.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #9 — only the retest 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 01.06.2026 | P060342: no initial certificate for #9 — only the retest 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -5094,17 +5094,17 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>JD112501＊</t>
+          <t>OPM112501</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>P060212</t>
+          <t>P060222</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5118,17 +5118,17 @@
         </is>
       </c>
       <c r="N56" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("JD112501|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0015</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060222|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>JD112501|I</t>
+          <t>P060222|I</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
@@ -5175,17 +5175,17 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>OPM112501</t>
+          <t>PM112501</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>P060222</t>
+          <t>P060232</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Permanent Market</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -5199,17 +5199,17 @@
         </is>
       </c>
       <c r="N57" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060222|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O57" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060232|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0016</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>P060222|I</t>
+          <t>P060232|I</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
@@ -5256,17 +5256,17 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>PM112501</t>
+          <t>OPM122501</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>P060232</t>
+          <t>P060242</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5280,17 +5280,17 @@
         </is>
       </c>
       <c r="N58" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060232|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060242|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0016</t>
+          <t>iCoA-PP-2026-0017</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>P060232|I</t>
+          <t>P060242|I</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>OPM122501</t>
+          <t>GG112501</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>P060242</t>
+          <t>P060252</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -5361,17 +5361,17 @@
         </is>
       </c>
       <c r="N59" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060242|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0017</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060252|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O59" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>P060242|I</t>
+          <t>P060252|I</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -5418,17 +5418,17 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>GG112501</t>
+          <t>J31122501</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>P060252</t>
+          <t>P060262</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="N60" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060252|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060262|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O60" s="6" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>P060252|I</t>
+          <t>P060262|I</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>registered — issued with the legacy series on 15.05.2026</t>
+          <t>registered — first working day 5 days after packaging</t>
         </is>
       </c>
     </row>
@@ -5499,17 +5499,17 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>CC112501</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>P060262</t>
+          <t>P060272</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="N61" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060262|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060272|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O61" s="6" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>P060262|I</t>
+          <t>P060272|I</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
@@ -5580,17 +5580,17 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>CC112501</t>
+          <t>SCR112501</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>P060272</t>
+          <t>P060282</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -5604,17 +5604,17 @@
         </is>
       </c>
       <c r="N62" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060272|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O62" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060282|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0018</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>P060272|I</t>
+          <t>P060282|I</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
@@ -5661,17 +5661,17 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>SCR112501</t>
+          <t>FB112501</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>P060282</t>
+          <t>P060292</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -5685,17 +5685,17 @@
         </is>
       </c>
       <c r="N63" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060282|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0018</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060292|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O63" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>P060282|I</t>
+          <t>P060292|I</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
@@ -5742,17 +5742,17 @@
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>GG012601＊</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>P060292</t>
+          <t>P060302</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="N64" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060292|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060302|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O64" s="6" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>P060292|I</t>
+          <t>P060302|I</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
@@ -5823,17 +5823,17 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>GG012601＊</t>
+          <t>JD012601＊</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>P060302</t>
+          <t>P060312</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
         </is>
       </c>
       <c r="N65" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060302|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060312|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O65" s="6" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>P060302|I</t>
+          <t>P060312|I</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
@@ -5904,19 +5904,15 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>JD012601＊</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>P060312</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Jelly Donutz</t>
-        </is>
-      </c>
+          <t>P060332</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -5928,7 +5924,7 @@
         </is>
       </c>
       <c r="N66" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060312|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060332|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O66" s="6" t="inlineStr">
@@ -5938,7 +5934,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>P060312|I</t>
+          <t>P060332|I</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
@@ -5985,15 +5981,19 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
+          <t>FB012601_1</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>P060332</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr"/>
+          <t>P060322</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -6005,17 +6005,17 @@
         </is>
       </c>
       <c r="N67" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060332|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O67" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060322|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0019</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>P060332|I</t>
+          <t>P060322|I</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>FB012601_1</t>
+          <t>FB012602*</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>P060322</t>
+          <t>P060352</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -6086,17 +6086,17 @@
         </is>
       </c>
       <c r="N68" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060322|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060352|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0019</t>
+          <t>iCoA-PP-2026-0021</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>P060322|I</t>
+          <t>P060352|I</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
@@ -6143,17 +6143,17 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>FB012602*</t>
+          <t>SCR012601* (from the list)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>P060352</t>
+          <t>P060342</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -6167,17 +6167,17 @@
         </is>
       </c>
       <c r="N69" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060352|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0021</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060342|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O69" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>P060352|I</t>
+          <t>P060342|I</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>SCR012601* (from the list)</t>
+          <t>SCR012603</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>P060342</t>
+          <t>P060382</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -6248,17 +6248,17 @@
         </is>
       </c>
       <c r="N70" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060342|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O70" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060382|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0026</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>P060342|I</t>
+          <t>P060382|I</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
@@ -6276,9 +6276,9 @@
         <f>IF(A71&lt;&gt;"","iCoA-PP_26-"&amp;TEXT(A71,"000"),IF(C71="n/a","not needed","— at issue —"))</f>
         <v/>
       </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D71" s="5">
@@ -6305,46 +6305,46 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>SCR012603</t>
+          <t>FB012603V</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>P060382</t>
+          <t>P060392</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Ident A + Ident B + Foreign matter</t>
-        </is>
-      </c>
-      <c r="M71" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>— all three on the CNP certificate —</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>A: ППК26110 / B: ППК26110 / FM: ППК26110</t>
         </is>
       </c>
       <c r="N71" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060382|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0026</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060392|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O71" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>P060382|I</t>
-        </is>
-      </c>
-      <c r="Q71" s="7" t="inlineStr">
-        <is>
-          <t>registered — first working day 5 days after packaging</t>
+          <t>P060392|I</t>
+        </is>
+      </c>
+      <c r="Q71" s="8" t="inlineStr">
+        <is>
+          <t>not needed — CNP covers A, B and foreign matter</t>
         </is>
       </c>
     </row>
@@ -6386,19 +6386,15 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>FB012603V</t>
+          <t>JD012603</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>P060392</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Fat Bastard</t>
-        </is>
-      </c>
+          <t>P060362</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
           <t>— all three on the CNP certificate —</t>
@@ -6406,21 +6402,21 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26110 / B: ППК26110 / FM: ППК26110</t>
+          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
         </is>
       </c>
       <c r="N72" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060392|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O72" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060362|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0020</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>P060392|I</t>
+          <t>P060362|I</t>
         </is>
       </c>
       <c r="Q72" s="8" t="inlineStr">
@@ -6472,7 +6468,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>P060362</t>
+          <t>P060422</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
@@ -6487,17 +6483,17 @@
         </is>
       </c>
       <c r="N73" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060362|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060422|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0020</t>
+          <t>iCoA-PP-2026-0022</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>P060362|I</t>
+          <t>P060422|I</t>
         </is>
       </c>
       <c r="Q73" s="8" t="inlineStr">
@@ -6544,15 +6540,19 @@
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>JD012603</t>
+          <t>GG012603</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>P060422</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
+          <t>P060402</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>GorillaGlue</t>
+        </is>
+      </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
           <t>— all three on the CNP certificate —</t>
@@ -6560,21 +6560,21 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
+          <t>A: ППК26114 / B: ППК26114 / FM: ППК26114</t>
         </is>
       </c>
       <c r="N74" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060422|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060402|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0022</t>
+          <t>iCoA-PP-2026-0023</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>P060422|I</t>
+          <t>P060402|I</t>
         </is>
       </c>
       <c r="Q74" s="8" t="inlineStr">
@@ -6621,19 +6621,15 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>GG012603</t>
+          <t>JD012603</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>P060402</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>GorillaGlue</t>
-        </is>
-      </c>
+          <t>P060412</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
           <t>— all three on the CNP certificate —</t>
@@ -6641,21 +6637,21 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26114 / B: ППК26114 / FM: ППК26114</t>
+          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
         </is>
       </c>
       <c r="N75" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060402|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060412|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0023</t>
+          <t>iCoA-PP-2026-0025</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>P060402|I</t>
+          <t>P060412|I</t>
         </is>
       </c>
       <c r="Q75" s="8" t="inlineStr">
@@ -6702,15 +6698,19 @@
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>JD012603</t>
+          <t>FB012603</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>P060412</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
+          <t>P060432</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
           <t>— all three on the CNP certificate —</t>
@@ -6718,21 +6718,21 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
+          <t>A: ППК26112 / B: ППК26112 / FM: ППК26112</t>
         </is>
       </c>
       <c r="N76" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060412|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0025</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060432|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>P060412|I</t>
+          <t>P060432|I</t>
         </is>
       </c>
       <c r="Q76" s="8" t="inlineStr">
@@ -6779,17 +6779,17 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>FB012603</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>P060432</t>
+          <t>P060442</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -6799,11 +6799,11 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26112 / B: ППК26112 / FM: ППК26112</t>
+          <t>A: ППК26116 / B: ППК26116 / FM: ППК26116</t>
         </is>
       </c>
       <c r="N77" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060432|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060442|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O77" s="6" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>P060432|I</t>
+          <t>P060442|I</t>
         </is>
       </c>
       <c r="Q77" s="8" t="inlineStr">
@@ -6860,17 +6860,17 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>FB032601</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>P060442</t>
+          <t>P060452</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>FatBastard</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -6880,11 +6880,11 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26116 / B: ППК26116 / FM: ППК26116</t>
+          <t>A: ППК26127 / B: ППК26127 / FM: ППК26127</t>
         </is>
       </c>
       <c r="N78" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060442|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060452|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O78" s="6" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>P060442|I</t>
+          <t>P060452|I</t>
         </is>
       </c>
       <c r="Q78" s="8" t="inlineStr">
@@ -6941,17 +6941,17 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>FB032601</t>
+          <t>GG032601</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>P060452</t>
+          <t>P060462</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>GorillaGlue</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -6961,11 +6961,11 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26127 / B: ППК26127 / FM: ППК26127</t>
+          <t>A: ППК26128 / B: ППК26128 / FM: ППК26128</t>
         </is>
       </c>
       <c r="N79" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060452|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060462|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O79" s="6" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>P060452|I</t>
+          <t>P060462|I</t>
         </is>
       </c>
       <c r="Q79" s="8" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>GG032601</t>
+          <t>JD022601</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>P060462</t>
+          <t>P060482</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>JellyDonutz</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7042,11 +7042,11 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26128 / B: ППК26128 / FM: ППК26128</t>
+          <t>A: ППК26115 / B: ППК26115 / FM: ППК26115</t>
         </is>
       </c>
       <c r="N80" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060462|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060482|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O80" s="6" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>P060462|I</t>
+          <t>P060482|I</t>
         </is>
       </c>
       <c r="Q80" s="8" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -7103,19 +7103,15 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>JD022601</t>
+          <t>— not recorded —</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>P060482</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>JellyDonutz</t>
-        </is>
-      </c>
+          <t>P160012</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
           <t>— all three on the CNP certificate —</t>
@@ -7123,11 +7119,11 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26115 / B: ППК26115 / FM: ППК26115</t>
+          <t>A: ППК26117 / B: ППК26117 / FM: ППК26117</t>
         </is>
       </c>
       <c r="N81" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060482|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("— not recorded —|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O81" s="6" t="inlineStr">
@@ -7137,7 +7133,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>P060482|I</t>
+          <t>— not recorded —|I</t>
         </is>
       </c>
       <c r="Q81" s="8" t="inlineStr">
@@ -7189,7 +7185,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>P160012</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
@@ -7200,7 +7196,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26117 / B: ППК26117 / FM: ППК26117</t>
+          <t>A: ППК26118 / B: ППК26118 / FM: ППК26118</t>
         </is>
       </c>
       <c r="N82" s="2">
@@ -7266,7 +7262,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>P160032</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
@@ -7277,7 +7273,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26118 / B: ППК26118 / FM: ППК26118</t>
+          <t>A: ППК26119 / B: ППК26119 / FM: ППК26119</t>
         </is>
       </c>
       <c r="N83" s="2">
@@ -7309,9 +7305,9 @@
         <f>IF(A84&lt;&gt;"","iCoA-PP_26-"&amp;TEXT(A84,"000"),IF(C84="n/a","not needed","— at issue —"))</f>
         <v/>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="D84" s="5">
@@ -7338,42 +7334,46 @@
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>— not recorded —</t>
+          <t>JD112501＊</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>P160032</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr"/>
+          <t>N/A — no P batch assigned</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>— all three on the CNP certificate —</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>A: ППК26119 / B: ППК26119 / FM: ППК26119</t>
+          <t>Ident A + Ident B + Foreign matter</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N84" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("— not recorded —|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O84" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("JD112501|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0015</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>— not recorded —|I</t>
-        </is>
-      </c>
-      <c r="Q84" s="8" t="inlineStr">
-        <is>
-          <t>not needed — CNP covers A, B and foreign matter</t>
+          <t>JD112501|I</t>
+        </is>
+      </c>
+      <c r="Q84" s="9" t="inlineStr">
+        <is>
+          <t>not yet issuable — no packaging date on the list</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>P060212</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -18685,19 +18685,19 @@
         <v/>
       </c>
       <c r="F56" s="5" t="n">
-        <v>46153</v>
+        <v>46086</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>ППК26065</t>
+          <t>ППК26031</t>
         </is>
       </c>
       <c r="H56" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("JD112501|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060222|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I56" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("JD112501|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060222|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -18712,22 +18712,22 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>JD112501＊</t>
+          <t>OPM112501</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>P060212</t>
+          <t>P060222</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ППК26065, (11.05.2026) [CNP]</t>
+          <t>ППК26031, (05.03.2026) [CNP]</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
@@ -18742,17 +18742,17 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0015</t>
+          <t>(assigned on issue)</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>JD112501|I</t>
+          <t>P060222|I</t>
         </is>
       </c>
       <c r="T56" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -18783,15 +18783,15 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>ППК26031</t>
+          <t>ППК26030</t>
         </is>
       </c>
       <c r="H57" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060222|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060232|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I57" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060222|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060232|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -18806,22 +18806,22 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>OPM112501</t>
+          <t>PM112501</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>P060222</t>
+          <t>P060232</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Permanent Market</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ППК26031, (05.03.2026) [CNP]</t>
+          <t>ППК26030, (05.03.2026) [CNP]</t>
         </is>
       </c>
       <c r="P57" s="6" t="inlineStr">
@@ -18836,12 +18836,12 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>(assigned on issue)</t>
+          <t>CoQ-PP-2026-0016</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>P060222|I</t>
+          <t>P060232|I</t>
         </is>
       </c>
       <c r="T57" s="7" t="inlineStr">
@@ -18873,19 +18873,19 @@
         <v/>
       </c>
       <c r="F58" s="5" t="n">
-        <v>46086</v>
+        <v>46135</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>ППК26030</t>
+          <t>1627-2026</t>
         </is>
       </c>
       <c r="H58" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060232|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060242|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I58" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060232|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060242|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -18900,22 +18900,22 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>PM112501</t>
+          <t>OPM122501</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>P060232</t>
+          <t>P060242</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ППК26030, (05.03.2026) [CNP]</t>
+          <t>100-4-K-26, (09.04.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P58" s="6" t="inlineStr">
@@ -18930,17 +18930,17 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0016</t>
+          <t>CoQ-PP-2026-0017</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>P060232|I</t>
+          <t>P060242|I</t>
         </is>
       </c>
       <c r="T58" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026 · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — legacy series, issued 27.05.2026</t>
         </is>
       </c>
     </row>
@@ -18967,19 +18967,19 @@
         <v/>
       </c>
       <c r="F59" s="5" t="n">
-        <v>46135</v>
+        <v>46153</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1627-2026</t>
+          <t>ППК26061</t>
         </is>
       </c>
       <c r="H59" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060242|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060252|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I59" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060242|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060252|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -18994,22 +18994,22 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>OPM122501</t>
+          <t>GG112501</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>P060242</t>
+          <t>P060252</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>100-4-K-26, (09.04.2026) [FHM-K]</t>
+          <t>ППК26061, (11.05.2026) [CNP]</t>
         </is>
       </c>
       <c r="P59" s="6" t="inlineStr">
@@ -19024,12 +19024,12 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0017</t>
+          <t>(assigned on issue)</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>P060242|I</t>
+          <t>P060252|I</t>
         </is>
       </c>
       <c r="T59" s="7" t="inlineStr">
@@ -19061,24 +19061,24 @@
         <v/>
       </c>
       <c r="F60" s="5" t="n">
-        <v>46153</v>
+        <v>46135</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>ППК26061</t>
+          <t>1625-2026</t>
         </is>
       </c>
       <c r="H60" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060252|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060262|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I60" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060252|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060262|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -19088,22 +19088,22 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>GG112501</t>
+          <t>J31122501</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>P060252</t>
+          <t>P060262</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ППК26061, (11.05.2026) [CNP]</t>
+          <t>100-2-K-26, (09.04.2026) [FHM-K]</t>
         </is>
       </c>
       <c r="P60" s="6" t="inlineStr">
@@ -19123,12 +19123,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>P060252|I</t>
+          <t>P060262|I</t>
         </is>
       </c>
       <c r="T60" s="7" t="inlineStr">
         <is>
-          <t>registered — legacy series, issued 27.05.2026</t>
+          <t>registered — rule date 30.04.2026 held to the legacy series day</t>
         </is>
       </c>
     </row>
@@ -19155,19 +19155,19 @@
         <v/>
       </c>
       <c r="F61" s="5" t="n">
-        <v>46135</v>
+        <v>46153</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1625-2026</t>
+          <t>ППК26068</t>
         </is>
       </c>
       <c r="H61" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060262|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060272|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I61" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060262|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060272|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -19182,22 +19182,22 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>CC112501</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>P060262</t>
+          <t>P060272</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>100-2-K-26, (09.04.2026) [FHM-K]</t>
+          <t>ППК26068, (11.05.2026) [CNP]</t>
         </is>
       </c>
       <c r="P61" s="6" t="inlineStr">
@@ -19217,12 +19217,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>P060262|I</t>
+          <t>P060272|I</t>
         </is>
       </c>
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>registered — rule date 30.04.2026 held to the legacy series day</t>
+          <t>registered — rule date 18.05.2026 held to the legacy series day</t>
         </is>
       </c>
     </row>
@@ -19253,15 +19253,15 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>ППК26068</t>
+          <t>ППК26069</t>
         </is>
       </c>
       <c r="H62" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060272|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060282|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I62" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060272|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060282|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -19276,22 +19276,22 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>CC112501</t>
+          <t>SCR112501</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>P060272</t>
+          <t>P060282</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ППК26068, (11.05.2026) [CNP]</t>
+          <t>ППК26069, (11.05.2026) [CNP]</t>
         </is>
       </c>
       <c r="P62" s="6" t="inlineStr">
@@ -19306,12 +19306,12 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>(assigned on issue)</t>
+          <t>CoQ-PP-2026-0018</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>P060272|I</t>
+          <t>P060282|I</t>
         </is>
       </c>
       <c r="T62" s="7" t="inlineStr">
@@ -19347,15 +19347,15 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>ППК26069</t>
+          <t>ППК26066</t>
         </is>
       </c>
       <c r="H63" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060282|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060292|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I63" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060282|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060292|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -19370,22 +19370,22 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>SCR112501</t>
+          <t>FB112501</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>P060282</t>
+          <t>P060292</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ППК26069, (11.05.2026) [CNP]</t>
+          <t>ППК26066, (11.05.2026) [CNP]</t>
         </is>
       </c>
       <c r="P63" s="6" t="inlineStr">
@@ -19400,12 +19400,12 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0018</t>
+          <t>(assigned on issue)</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>P060282|I</t>
+          <t>P060292|I</t>
         </is>
       </c>
       <c r="T63" s="7" t="inlineStr">
@@ -19441,15 +19441,15 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>ППК26066</t>
+          <t>ППК26062</t>
         </is>
       </c>
       <c r="H64" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060292|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060302|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I64" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060292|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060302|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -19464,22 +19464,22 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>GG012601＊</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>P060292</t>
+          <t>P060302</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ППК26066, (11.05.2026) [CNP]</t>
+          <t>ППК26062, (11.05.2026) [CNP]</t>
         </is>
       </c>
       <c r="P64" s="6" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>P060292|I</t>
+          <t>P060302|I</t>
         </is>
       </c>
       <c r="T64" s="7" t="inlineStr">
@@ -19535,15 +19535,15 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>ППК26062</t>
+          <t>ППК26064</t>
         </is>
       </c>
       <c r="H65" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060302|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060312|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I65" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060302|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060312|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -19558,22 +19558,22 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>GG012601＊</t>
+          <t>JD012601＊</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>P060302</t>
+          <t>P060312</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ППК26062, (11.05.2026) [CNP]</t>
+          <t>ППК26064, (11.05.2026) [CNP]</t>
         </is>
       </c>
       <c r="P65" s="6" t="inlineStr">
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>P060302|I</t>
+          <t>P060312|I</t>
         </is>
       </c>
       <c r="T65" s="7" t="inlineStr">
@@ -19624,20 +19624,22 @@
         <f>IF(ISNUMBER(F66),IF(AND(J66="legacy",F66&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F66+7)+CHOOSE(WEEKDAY(F66+7,2),0,0,0,0,0,2,1))),IF(J66="legacy",DATE(2026,5,27),""))</f>
         <v/>
       </c>
-      <c r="F66" s="5" t="n">
-        <v>46153</v>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>ППК26064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H66" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060312|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060332|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I66" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060312|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060332|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -19652,22 +19654,18 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>JD012601＊</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>P060312</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>Jelly Donutz</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>ППК26064, (11.05.2026) [CNP]</t>
+          <t>P060332</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="P66" s="6" t="inlineStr">
@@ -19682,17 +19680,17 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>(assigned on issue)</t>
+          <t>— not in the issuance plan —</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>P060312|I</t>
+          <t>P060332|I</t>
         </is>
       </c>
       <c r="T66" s="7" t="inlineStr">
         <is>
-          <t>registered — rule date 18.05.2026 held to the legacy series day</t>
+          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -19718,22 +19716,20 @@
         <f>IF(ISNUMBER(F67),IF(AND(J67="legacy",F67&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F67+7)+CHOOSE(WEEKDAY(F67+7,2),0,0,0,0,0,2,1))),IF(J67="legacy",DATE(2026,5,27),""))</f>
         <v/>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F67" s="5" t="n">
+        <v>46153</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ППК26067</t>
         </is>
       </c>
       <c r="H67" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060332|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060322|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I67" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060332|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060322|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -19748,18 +19744,22 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
+          <t>FB012601_1</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>P060332</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr"/>
-      <c r="O67" s="6" t="inlineStr">
-        <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
+          <t>P060322</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>ППК26067, (11.05.2026) [CNP]</t>
         </is>
       </c>
       <c r="P67" s="6" t="inlineStr">
@@ -19774,17 +19774,17 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>— not in the issuance plan —</t>
+          <t>CoQ-PP-2026-0019</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>P060332|I</t>
+          <t>P060322|I</t>
         </is>
       </c>
       <c r="T67" s="7" t="inlineStr">
         <is>
-          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — rule date 18.05.2026 held to the legacy series day</t>
         </is>
       </c>
     </row>
@@ -19810,20 +19810,22 @@
         <f>IF(ISNUMBER(F68),IF(AND(J68="legacy",F68&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F68+7)+CHOOSE(WEEKDAY(F68+7,2),0,0,0,0,0,2,1))),IF(J68="legacy",DATE(2026,5,27),""))</f>
         <v/>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>46153</v>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>ППК26067</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H68" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060322|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060352|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I68" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060322|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060352|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -19838,12 +19840,12 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>FB012601_1</t>
+          <t>FB012602*</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>P060322</t>
+          <t>P060352</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -19851,9 +19853,9 @@
           <t>Fat Bastard</t>
         </is>
       </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>ППК26067, (11.05.2026) [CNP]</t>
+      <c r="O68" s="6" t="inlineStr">
+        <is>
+          <t>— no cannabinoid certificate from the initial testing —</t>
         </is>
       </c>
       <c r="P68" s="6" t="inlineStr">
@@ -19868,17 +19870,17 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0019</t>
+          <t>CoQ-PP-2026-0021</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>P060322|I</t>
+          <t>P060352|I</t>
         </is>
       </c>
       <c r="T68" s="7" t="inlineStr">
         <is>
-          <t>registered — rule date 18.05.2026 held to the legacy series day</t>
+          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -19915,11 +19917,11 @@
         </is>
       </c>
       <c r="H69" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060352|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060342|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I69" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060352|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060342|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -19934,17 +19936,17 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>FB012602*</t>
+          <t>SCR012601* (from the list)</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>P060352</t>
+          <t>P060342</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr">
@@ -19964,12 +19966,12 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0021</t>
+          <t>— not in the issuance plan —</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>P060352|I</t>
+          <t>P060342|I</t>
         </is>
       </c>
       <c r="T69" s="7" t="inlineStr">
@@ -20011,11 +20013,11 @@
         </is>
       </c>
       <c r="H70" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060342|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060382|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I70" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060342|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060382|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -20030,12 +20032,12 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>SCR012601* (from the list)</t>
+          <t>SCR012603</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>P060342</t>
+          <t>P060382</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -20060,12 +20062,12 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>— not in the issuance plan —</t>
+          <t>CoQ-PP-2026-0026</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>P060342|I</t>
+          <t>P060382|I</t>
         </is>
       </c>
       <c r="T70" s="7" t="inlineStr">
@@ -20096,22 +20098,20 @@
         <f>IF(ISNUMBER(F71),IF(AND(J71="legacy",F71&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F71+7)+CHOOSE(WEEKDAY(F71+7,2),0,0,0,0,0,2,1))),IF(J71="legacy",DATE(2026,5,27),""))</f>
         <v/>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F71" s="5" t="n">
+        <v>46203</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ППК26110</t>
         </is>
       </c>
       <c r="H71" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060382|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060392|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I71" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060382|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060392|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -20126,27 +20126,27 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>SCR012603</t>
+          <t>FB012603V</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>P060382</t>
+          <t>P060392</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-      <c r="O71" s="6" t="inlineStr">
-        <is>
-          <t>— no cannabinoid certificate from the initial testing —</t>
-        </is>
-      </c>
-      <c r="P71" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>ППК26110, (30.06.2026) [CNP]</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>A: ППК26110 / B: ППК26110 / FM: ППК26110</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -20156,17 +20156,17 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0026</t>
+          <t>(assigned on issue)</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>P060382|I</t>
+          <t>P060392|I</t>
         </is>
       </c>
       <c r="T71" s="7" t="inlineStr">
         <is>
-          <t>registered — provisional date: no initial certificate on file yet — the date follows the latest eCoA once located · initial certificate to locate: #3 (CNP), #4 (CNP), #5 (CNP), #6 (CNP), #8 (CNP), #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -20197,15 +20197,15 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>ППК26110</t>
+          <t>ППК26111</t>
         </is>
       </c>
       <c r="H72" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060392|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060362|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I72" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060392|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060362|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -20220,27 +20220,23 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>FB012603V</t>
+          <t>JD012603</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>P060392</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>Fat Bastard</t>
-        </is>
-      </c>
+          <t>P060362</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ППК26110, (30.06.2026) [CNP]</t>
+          <t>ППК26111, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26110 / B: ППК26110 / FM: ППК26110</t>
+          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -20250,12 +20246,12 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>(assigned on issue)</t>
+          <t>CoQ-PP-2026-0020</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>P060392|I</t>
+          <t>P060362|I</t>
         </is>
       </c>
       <c r="T72" s="7" t="inlineStr">
@@ -20295,11 +20291,11 @@
         </is>
       </c>
       <c r="H73" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060362|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060422|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I73" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060362|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060422|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -20319,7 +20315,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>P060362</t>
+          <t>P060422</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr"/>
@@ -20340,12 +20336,12 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0020</t>
+          <t>CoQ-PP-2026-0022</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>P060362|I</t>
+          <t>P060422|I</t>
         </is>
       </c>
       <c r="T73" s="7" t="inlineStr">
@@ -20381,15 +20377,15 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>ППК26111</t>
+          <t>ППК26114</t>
         </is>
       </c>
       <c r="H74" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060422|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060402|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I74" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060422|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060402|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -20404,23 +20400,27 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>JD012603</t>
+          <t>GG012603</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>P060422</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>P060402</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>GorillaGlue</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ППК26111, (30.06.2026) [CNP]</t>
+          <t>ППК26114, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
+          <t>A: ППК26114 / B: ППК26114 / FM: ППК26114</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -20430,12 +20430,12 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0022</t>
+          <t>CoQ-PP-2026-0023</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>P060422|I</t>
+          <t>P060402|I</t>
         </is>
       </c>
       <c r="T74" s="7" t="inlineStr">
@@ -20471,15 +20471,15 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>ППК26114</t>
+          <t>ППК26111</t>
         </is>
       </c>
       <c r="H75" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060402|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060412|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I75" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060402|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060412|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -20494,27 +20494,23 @@
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>GG012603</t>
+          <t>JD012603</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>P060402</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>GorillaGlue</t>
-        </is>
-      </c>
+          <t>P060412</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ППК26114, (30.06.2026) [CNP]</t>
+          <t>ППК26111, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26114 / B: ППК26114 / FM: ППК26114</t>
+          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -20524,12 +20520,12 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0023</t>
+          <t>CoQ-PP-2026-0025</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>P060402|I</t>
+          <t>P060412|I</t>
         </is>
       </c>
       <c r="T75" s="7" t="inlineStr">
@@ -20565,15 +20561,15 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>ППК26111</t>
+          <t>ППК26112</t>
         </is>
       </c>
       <c r="H76" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060412|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060432|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I76" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060412|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060432|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -20588,23 +20584,27 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>JD012603</t>
+          <t>FB012603</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>P060412</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>P060432</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ППК26111, (30.06.2026) [CNP]</t>
+          <t>ППК26112, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26111 / B: ППК26111 / FM: ППК26111</t>
+          <t>A: ППК26112 / B: ППК26112 / FM: ППК26112</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -20614,12 +20614,12 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>CoQ-PP-2026-0025</t>
+          <t>(assigned on issue)</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>P060412|I</t>
+          <t>P060432|I</t>
         </is>
       </c>
       <c r="T76" s="7" t="inlineStr">
@@ -20651,19 +20651,19 @@
         <v/>
       </c>
       <c r="F77" s="5" t="n">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>ППК26112</t>
+          <t>ППК26116</t>
         </is>
       </c>
       <c r="H77" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060432|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060442|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I77" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060432|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060442|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -20678,27 +20678,27 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>FB012603</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>P060432</t>
+          <t>P060442</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ППК26112, (30.06.2026) [CNP]</t>
+          <t>ППК26116, (06.07.2026) [CNP]</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26112 / B: ППК26112 / FM: ППК26112</t>
+          <t>A: ППК26116 / B: ППК26116 / FM: ППК26116</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>P060432|I</t>
+          <t>P060442|I</t>
         </is>
       </c>
       <c r="T77" s="7" t="inlineStr">
@@ -20745,19 +20745,19 @@
         <v/>
       </c>
       <c r="F78" s="5" t="n">
-        <v>46209</v>
+        <v>46224</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>ППК26116</t>
+          <t>ППК26127</t>
         </is>
       </c>
       <c r="H78" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060442|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060452|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I78" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060442|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060452|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -20772,27 +20772,27 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>FB032601</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>P060442</t>
+          <t>P060452</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>FatBastard</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ППК26116, (06.07.2026) [CNP]</t>
+          <t>ППК26127, (21.07.2026) [CNP]</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26116 / B: ППК26116 / FM: ППК26116</t>
+          <t>A: ППК26127 / B: ППК26127 / FM: ППК26127</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -20807,7 +20807,7 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>P060442|I</t>
+          <t>P060452|I</t>
         </is>
       </c>
       <c r="T78" s="7" t="inlineStr">
@@ -20843,15 +20843,15 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>ППК26127</t>
+          <t>ППК26128</t>
         </is>
       </c>
       <c r="H79" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060452|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060462|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I79" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060452|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060462|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -20866,27 +20866,27 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>FB032601</t>
+          <t>GG032601</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>P060452</t>
+          <t>P060462</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>GorillaGlue</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ППК26127, (21.07.2026) [CNP]</t>
+          <t>ППК26128, (21.07.2026) [CNP]</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26127 / B: ППК26127 / FM: ППК26127</t>
+          <t>A: ППК26128 / B: ППК26128 / FM: ППК26128</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -20901,7 +20901,7 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>P060452|I</t>
+          <t>P060462|I</t>
         </is>
       </c>
       <c r="T79" s="7" t="inlineStr">
@@ -20933,19 +20933,19 @@
         <v/>
       </c>
       <c r="F80" s="5" t="n">
-        <v>46224</v>
+        <v>46203</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>ППК26128</t>
+          <t>ППК26115</t>
         </is>
       </c>
       <c r="H80" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060462|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060482|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I80" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060462|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060482|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -20960,27 +20960,27 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>GG032601</t>
+          <t>JD022601</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>P060462</t>
+          <t>P060482</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>JellyDonutz</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ППК26128, (21.07.2026) [CNP]</t>
+          <t>ППК26115, (30.06.2026) [CNP]</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>A: ППК26128 / B: ППК26128 / FM: ППК26128</t>
+          <t>A: ППК26115 / B: ППК26115 / FM: ППК26115</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -20995,12 +20995,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>P060462|I</t>
+          <t>P060482|I</t>
         </is>
       </c>
       <c r="T80" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 7 days after the latest eCoA · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>registered — held to the packaging date · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
         </is>
       </c>
     </row>
@@ -21013,9 +21013,9 @@
         <f>IF(A81&lt;&gt;"","CoQ-PP_26-"&amp;TEXT(A81,"000"),"— at issue —")</f>
         <v/>
       </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="D81" s="5">
@@ -21027,24 +21027,24 @@
         <v/>
       </c>
       <c r="F81" s="5" t="n">
-        <v>46203</v>
+        <v>46153</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>ППК26115</t>
+          <t>ППК26065</t>
         </is>
       </c>
       <c r="H81" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P060482|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("JD112501|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I81" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P060482|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("JD112501|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -21054,27 +21054,27 @@
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>JD022601</t>
+          <t>JD112501＊</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>P060482</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ППК26115, (30.06.2026) [CNP]</t>
-        </is>
-      </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>A: ППК26115 / B: ППК26115 / FM: ППК26115</t>
+          <t>ППК26065, (11.05.2026) [CNP]</t>
+        </is>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -21084,17 +21084,17 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>(assigned on issue)</t>
+          <t>CoQ-PP-2026-0015</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>P060482|I</t>
-        </is>
-      </c>
-      <c r="T81" s="7" t="inlineStr">
-        <is>
-          <t>registered — held to the packaging date · initial certificate to locate: #9 (IJZ), #10 (CNP), #11 (CNP), #12 (CNP)</t>
+          <t>JD112501|I</t>
+        </is>
+      </c>
+      <c r="T81" s="9" t="inlineStr">
+        <is>
+          <t>not yet issuable — no packaging date on the list</t>
         </is>
       </c>
     </row>
@@ -26142,7 +26142,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -26157,7 +26157,7 @@
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>P060212</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -30745,7 +30745,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>JD112501＊</t>
+          <t>JD112501</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr"/>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="N81" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("— not recorded —|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P160012|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O81" s="6" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>— not recorded —|I</t>
+          <t>P160012|I</t>
         </is>
       </c>
       <c r="Q81" s="8" t="inlineStr">
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="N82" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("— not recorded —|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P160022|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O82" s="6" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>— not recorded —|I</t>
+          <t>P160022|I</t>
         </is>
       </c>
       <c r="Q82" s="8" t="inlineStr">
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="N83" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("— not recorded —|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P160032|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O83" s="6" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>— not recorded —|I</t>
+          <t>P160032|I</t>
         </is>
       </c>
       <c r="Q83" s="8" t="inlineStr">
@@ -21129,11 +21129,11 @@
         </is>
       </c>
       <c r="H82" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("— not recorded —|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P160012|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I82" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("— not recorded —|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P160012|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>— not recorded —|I</t>
+          <t>P160012|I</t>
         </is>
       </c>
       <c r="T82" s="9" t="inlineStr">
@@ -21219,11 +21219,11 @@
         </is>
       </c>
       <c r="H83" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("— not recorded —|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P160022|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I83" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("— not recorded —|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P160022|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -21269,7 +21269,7 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>— not recorded —|I</t>
+          <t>P160022|I</t>
         </is>
       </c>
       <c r="T83" s="9" t="inlineStr">
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="H84" s="2">
-        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("— not recorded —|I",'iCoA Register'!$P:$P,0)),"—")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$B:$B,MATCH("P160032|I",'iCoA Register'!$P:$P,0)),"—")</f>
         <v/>
       </c>
       <c r="I84" s="5">
-        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("— not recorded —|I",'iCoA Register'!$P:$P,0)),"")</f>
+        <f>IFERROR(INDEX('iCoA Register'!$D:$D,MATCH("P160032|I",'iCoA Register'!$P:$P,0)),"")</f>
         <v/>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -21359,7 +21359,7 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>— not recorded —|I</t>
+          <t>P160032|I</t>
         </is>
       </c>
       <c r="T84" s="9" t="inlineStr">

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>BSS1024_01/2 (from the list)</t>
+          <t>BSS1024_01/2</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>WED102501 (from the list)</t>
+          <t>WED102501</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>SCR012601* (from the list)</t>
+          <t>SCR012601*</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>BSS1024_01/2 (from the list)</t>
+          <t>BSS1024_01/2</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>WED102501 (from the list)</t>
+          <t>WED102501</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -19936,7 +19936,7 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>SCR012601* (from the list)</t>
+          <t>SCR012601*</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -29052,7 +29052,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>P050142</t>
+          <t>BSS1024_01/2</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -30375,7 +30375,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>P060102</t>
+          <t>WED102501</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr"/>
@@ -31152,7 +31152,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>P060342</t>
+          <t>SCR012601*</t>
         </is>
       </c>
       <c r="J73" s="8" t="inlineStr"/>
@@ -31732,7 +31732,7 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v11 on 05.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v12 on 05.09.2026</t>
         </is>
       </c>
     </row>
@@ -31753,7 +31753,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v11.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v12.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -31732,7 +31732,7 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v12 on 05.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v13 on 05.09.2026</t>
         </is>
       </c>
     </row>
@@ -31753,7 +31753,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v12.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v13.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iCoA Register" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CoQ Register" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch Dates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="iCoA Register" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CoQ Register" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Batch Dates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31732,7 +31732,7 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v13 on 05.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v21 on 05.09.2026</t>
         </is>
       </c>
     </row>
@@ -31753,7 +31753,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v13.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v21.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D2" s="5">
-        <f>IF(A2="","",IF(G2="legacy",DATE(2026,5,15),IF(ISNUMBER(F2),(F2+5)+CHOOSE(WEEKDAY(F2+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A2="","",IF(ISNUMBER(E2),MAX(DATE(2026,6,3),E2),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E2" s="5">
@@ -714,7 +714,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>CJ1024</t>
+          <t>J31122501</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
+          <t>P060262</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="N2" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("CJ1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060262|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O2" s="6" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>CJ1024|I</t>
+          <t>P060262|I</t>
         </is>
       </c>
       <c r="Q2" s="7" t="inlineStr">
         <is>
-          <t>registered — issued with the legacy series on 15.05.2026</t>
+          <t>registered — first working day 5 days after packaging</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <f>IF(A3="","",IF(G3="legacy",DATE(2026,5,15),IF(ISNUMBER(F3),(F3+5)+CHOOSE(WEEKDAY(F3+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A3="","",IF(ISNUMBER(E3),MAX(DATE(2026,6,3),E3),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E3" s="5">
@@ -795,7 +795,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>BSS1024</t>
+          <t>CC112501</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
+          <t>P060272</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -829,22 +829,22 @@
         </is>
       </c>
       <c r="N3" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("BSS1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2025-0001</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060272|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>BSS1024|I</t>
+          <t>P060272|I</t>
         </is>
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>registered — issued with the legacy series on 15.05.2026</t>
+          <t>registered — first working day 5 days after packaging</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D4" s="5">
-        <f>IF(A4="","",IF(G4="legacy",DATE(2026,5,15),IF(ISNUMBER(F4),(F4+5)+CHOOSE(WEEKDAY(F4+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A4="","",IF(ISNUMBER(E4),MAX(DATE(2026,6,3),E4),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E4" s="5">
@@ -876,7 +876,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -886,17 +886,17 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>BG1024</t>
+          <t>SCR112501</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
+          <t>P060282</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Blue Gelato</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="N4" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("BG1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060282|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0002</t>
+          <t>iCoA-PP-2026-0018</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>BG1024|I</t>
+          <t>P060282|I</t>
         </is>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>registered — issued with the legacy series on 15.05.2026</t>
+          <t>registered — first working day 5 days after packaging</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="D5" s="5">
-        <f>IF(A5="","",IF(G5="legacy",DATE(2026,5,15),IF(ISNUMBER(F5),(F5+5)+CHOOSE(WEEKDAY(F5+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A5="","",IF(ISNUMBER(E5),MAX(DATE(2026,6,3),E5),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E5" s="5">
@@ -957,7 +957,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -967,17 +967,17 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>GG1024</t>
+          <t>FB112501</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
+          <t>P060292</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -991,22 +991,22 @@
         </is>
       </c>
       <c r="N5" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("GG1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2025-0003</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060292|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>GG1024|I</t>
+          <t>P060292|I</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>registered — issued with the legacy series on 15.05.2026</t>
+          <t>registered — first working day 5 days after packaging</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D6" s="5">
-        <f>IF(A6="","",IF(G6="legacy",DATE(2026,5,15),IF(ISNUMBER(F6),(F6+5)+CHOOSE(WEEKDAY(F6+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A6="","",IF(ISNUMBER(E6),MAX(DATE(2026,6,3),E6),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E6" s="5">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1048,17 +1048,17 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>HPA1024</t>
+          <t>GG012601＊</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
+          <t>P060302</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>HighProAmnesia</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1072,22 +1072,22 @@
         </is>
       </c>
       <c r="N6" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("HPA1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2025-0004</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060302|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>HPA1024|I</t>
+          <t>P060302|I</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>registered — issued with the legacy series on 15.05.2026</t>
+          <t>registered — first working day 5 days after packaging</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="D7" s="5">
-        <f>IF(A7="","",IF(G7="legacy",DATE(2026,5,15),IF(ISNUMBER(F7),(F7+5)+CHOOSE(WEEKDAY(F7+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A7="","",IF(ISNUMBER(E7),MAX(DATE(2026,6,3),E7),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E7" s="5">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1129,17 +1129,17 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>JD012601＊</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>N/A — no P batch assigned</t>
+          <t>P060312</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>OrangePunchMimosa</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1153,22 +1153,22 @@
         </is>
       </c>
       <c r="N7" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("OPM1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2025-0005</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060312|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>OPM1024|I</t>
+          <t>P060312|I</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>registered — issued with the legacy series on 15.05.2026</t>
+          <t>registered — first working day 5 days after packaging</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="D8" s="5">
-        <f>IF(A8="","",IF(G8="legacy",DATE(2026,5,15),IF(ISNUMBER(F8),(F8+5)+CHOOSE(WEEKDAY(F8+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A8="","",IF(ISNUMBER(E8),MAX(DATE(2026,6,3),E8),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E8" s="5">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1210,19 +1210,15 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>GP0824_02</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>P050022</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
+          <t>P060332</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -1234,22 +1230,22 @@
         </is>
       </c>
       <c r="N8" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050022|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2025-0006</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060332|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>P050022|I</t>
+          <t>P060332|I</t>
         </is>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>registered — issued with the legacy series on 15.05.2026</t>
+          <t>registered — first working day 5 days after packaging</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1264,7 @@
         </is>
       </c>
       <c r="D9" s="5">
-        <f>IF(A9="","",IF(G9="legacy",DATE(2026,5,15),IF(ISNUMBER(F9),(F9+5)+CHOOSE(WEEKDAY(F9+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A9="","",IF(ISNUMBER(E9),MAX(DATE(2026,6,3),E9),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E9" s="5">
@@ -1281,7 +1277,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1291,17 +1287,17 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>GG1024_02</t>
+          <t>FB012601_1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>P050012</t>
+          <t>P060322</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1315,22 +1311,22 @@
         </is>
       </c>
       <c r="N9" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050012|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060322|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0019</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>P050012|I</t>
+          <t>P060322|I</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>registered — issued with the legacy series on 15.05.2026</t>
+          <t>registered — first working day 5 days after packaging</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1345,7 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <f>IF(A10="","",IF(G10="legacy",DATE(2026,5,15),IF(ISNUMBER(F10),(F10+5)+CHOOSE(WEEKDAY(F10+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A10="","",IF(ISNUMBER(E10),MAX(DATE(2026,6,3),E10),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E10" s="5">
@@ -1362,7 +1358,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1372,17 +1368,17 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>MB0824_04</t>
+          <t>FB012602*</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>P050032</t>
+          <t>P060352</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1396,22 +1392,22 @@
         </is>
       </c>
       <c r="N10" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050032|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060352|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0021</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>P050032|I</t>
+          <t>P060352|I</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>registered — issued with the legacy series on 15.05.2026</t>
+          <t>registered — first working day 5 days after packaging</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1426,7 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <f>IF(A11="","",IF(G11="legacy",DATE(2026,5,15),IF(ISNUMBER(F11),(F11+5)+CHOOSE(WEEKDAY(F11+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A11="","",IF(ISNUMBER(E11),MAX(DATE(2026,6,3),E11),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -1443,7 +1439,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1453,17 +1449,17 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>OMP1024_01</t>
+          <t>SCR012601*</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>P050042</t>
+          <t>P060342</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1477,22 +1473,22 @@
         </is>
       </c>
       <c r="N11" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050042|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2025-0007</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060342|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>P050042|I</t>
+          <t>P060342|I</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>registered — issued with the legacy series on 15.05.2026</t>
+          <t>registered — first working day 5 days after packaging</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1507,7 @@
         </is>
       </c>
       <c r="D12" s="5">
-        <f>IF(A12="","",IF(G12="legacy",DATE(2026,5,15),IF(ISNUMBER(F12),(F12+5)+CHOOSE(WEEKDAY(F12+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A12="","",IF(ISNUMBER(E12),MAX(DATE(2026,6,3),E12),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -1524,7 +1520,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>post-SOP</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1534,17 +1530,17 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>HPA1024_01</t>
+          <t>SCR012603</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>P050052</t>
+          <t>P060382</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1558,22 +1554,22 @@
         </is>
       </c>
       <c r="N12" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050052|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060382|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0008</t>
+          <t>iCoA-PP-2026-0026</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>P050052|I</t>
+          <t>P060382|I</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>registered — issued with the legacy series on 15.05.2026</t>
+          <t>registered — first working day 5 days after packaging</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1588,7 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <f>IF(A13="","",IF(G13="legacy",DATE(2026,5,15),IF(ISNUMBER(F13),(F13+5)+CHOOSE(WEEKDAY(F13+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A13="","",IF(ISNUMBER(E13),MAX(DATE(2026,6,3),E13),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -1615,17 +1611,17 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>OPM1024_02</t>
+          <t>CJ1024</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>P050062</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1639,17 +1635,17 @@
         </is>
       </c>
       <c r="N13" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050062|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2025-0009</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("CJ1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>P050062|I</t>
+          <t>CJ1024|I</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -1673,7 +1669,7 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <f>IF(A14="","",IF(G14="legacy",DATE(2026,5,15),IF(ISNUMBER(F14),(F14+5)+CHOOSE(WEEKDAY(F14+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A14="","",IF(ISNUMBER(E14),MAX(DATE(2026,6,3),E14),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -1696,17 +1692,17 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>GP0824_03</t>
+          <t>BSS1024</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>P050072</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1720,17 +1716,17 @@
         </is>
       </c>
       <c r="N14" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050072|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("BSS1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0010</t>
+          <t>iCoA-PP-2025-0001</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>P050072|I</t>
+          <t>BSS1024|I</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
@@ -1754,7 +1750,7 @@
         </is>
       </c>
       <c r="D15" s="5">
-        <f>IF(A15="","",IF(G15="legacy",DATE(2026,5,15),IF(ISNUMBER(F15),(F15+5)+CHOOSE(WEEKDAY(F15+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A15="","",IF(ISNUMBER(E15),MAX(DATE(2026,6,3),E15),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -1777,17 +1773,17 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>OPM1024_03</t>
+          <t>BG1024</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>P050082</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Blue Gelato</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1801,17 +1797,17 @@
         </is>
       </c>
       <c r="N15" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050082|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("BG1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0011</t>
+          <t>iCoA-PP-2025-0002</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>P050082|I</t>
+          <t>BG1024|I</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
@@ -1835,7 +1831,7 @@
         </is>
       </c>
       <c r="D16" s="5">
-        <f>IF(A16="","",IF(G16="legacy",DATE(2026,5,15),IF(ISNUMBER(F16),(F16+5)+CHOOSE(WEEKDAY(F16+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A16="","",IF(ISNUMBER(E16),MAX(DATE(2026,6,3),E16),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -1858,12 +1854,12 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>GG1024_01</t>
+          <t>GG1024</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>P050092</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1882,17 +1878,17 @@
         </is>
       </c>
       <c r="N16" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050092|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("GG1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0012</t>
+          <t>iCoA-PP-2025-0003</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>P050092|I</t>
+          <t>GG1024|I</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
@@ -1916,7 +1912,7 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <f>IF(A17="","",IF(G17="legacy",DATE(2026,5,15),IF(ISNUMBER(F17),(F17+5)+CHOOSE(WEEKDAY(F17+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A17="","",IF(ISNUMBER(E17),MAX(DATE(2026,6,3),E17),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -1939,17 +1935,17 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>GP0824_01</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>P050102</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>HighProAmnesia</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1963,17 +1959,17 @@
         </is>
       </c>
       <c r="N17" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050102|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("HPA1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2025-0004</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>P050102|I</t>
+          <t>HPA1024|I</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
@@ -1997,7 +1993,7 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <f>IF(A18="","",IF(G18="legacy",DATE(2026,5,15),IF(ISNUMBER(F18),(F18+5)+CHOOSE(WEEKDAY(F18+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A18="","",IF(ISNUMBER(E18),MAX(DATE(2026,6,3),E18),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -2020,17 +2016,17 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>MB0824_05</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>P050112</t>
+          <t>N/A — no P batch assigned</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>OrangePunchMimosa</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2044,17 +2040,17 @@
         </is>
       </c>
       <c r="N18" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050112|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("OPM1024|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0013</t>
+          <t>iCoA-PP-2025-0005</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>P050112|I</t>
+          <t>OPM1024|I</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
@@ -2078,7 +2074,7 @@
         </is>
       </c>
       <c r="D19" s="5">
-        <f>IF(A19="","",IF(G19="legacy",DATE(2026,5,15),IF(ISNUMBER(F19),(F19+5)+CHOOSE(WEEKDAY(F19+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A19="","",IF(ISNUMBER(E19),MAX(DATE(2026,6,3),E19),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -2101,17 +2097,17 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>BSS1024_01/1</t>
+          <t>GP0824_02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>P050122</t>
+          <t>P050022</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2125,17 +2121,17 @@
         </is>
       </c>
       <c r="N19" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050122|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050022|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2025-0006</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>P050122|I</t>
+          <t>P050022|I</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
@@ -2159,7 +2155,7 @@
         </is>
       </c>
       <c r="D20" s="5">
-        <f>IF(A20="","",IF(G20="legacy",DATE(2026,5,15),IF(ISNUMBER(F20),(F20+5)+CHOOSE(WEEKDAY(F20+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A20="","",IF(ISNUMBER(E20),MAX(DATE(2026,6,3),E20),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E20" s="5">
@@ -2182,17 +2178,17 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>OPM052501</t>
+          <t>GG1024_02</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>P050132</t>
+          <t>P050012</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2206,7 +2202,7 @@
         </is>
       </c>
       <c r="N20" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050132|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050012|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O20" s="6" t="inlineStr">
@@ -2216,7 +2212,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>P050132|I</t>
+          <t>P050012|I</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
@@ -2240,7 +2236,7 @@
         </is>
       </c>
       <c r="D21" s="5">
-        <f>IF(A21="","",IF(G21="legacy",DATE(2026,5,15),IF(ISNUMBER(F21),(F21+5)+CHOOSE(WEEKDAY(F21+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A21="","",IF(ISNUMBER(E21),MAX(DATE(2026,6,3),E21),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E21" s="5">
@@ -2263,17 +2259,17 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>GP052501</t>
+          <t>MB0824_04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>P050152</t>
+          <t>P050032</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2287,17 +2283,17 @@
         </is>
       </c>
       <c r="N21" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050152|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2025-0014</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050032|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>P050152|I</t>
+          <t>P050032|I</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
@@ -2321,7 +2317,7 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <f>IF(A22="","",IF(G22="legacy",DATE(2026,5,15),IF(ISNUMBER(F22),(F22+5)+CHOOSE(WEEKDAY(F22+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A22="","",IF(ISNUMBER(E22),MAX(DATE(2026,6,3),E22),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E22" s="5">
@@ -2344,17 +2340,17 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>BSS1024_01/2</t>
+          <t>OMP1024_01</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>P050142</t>
+          <t>P050042</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2368,17 +2364,17 @@
         </is>
       </c>
       <c r="N22" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050142|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050042|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2025-0007</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>P050142|I</t>
+          <t>P050042|I</t>
         </is>
       </c>
       <c r="Q22" s="7" t="inlineStr">
@@ -2402,7 +2398,7 @@
         </is>
       </c>
       <c r="D23" s="5">
-        <f>IF(A23="","",IF(G23="legacy",DATE(2026,5,15),IF(ISNUMBER(F23),(F23+5)+CHOOSE(WEEKDAY(F23+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A23="","",IF(ISNUMBER(E23),MAX(DATE(2026,6,3),E23),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E23" s="5">
@@ -2425,17 +2421,17 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>CJ052501/01</t>
+          <t>HPA1024_01</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>P050162</t>
+          <t>P050052</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2449,17 +2445,17 @@
         </is>
       </c>
       <c r="N23" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050162|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050052|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0015</t>
+          <t>iCoA-PP-2025-0008</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>P050162|I</t>
+          <t>P050052|I</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
@@ -2483,7 +2479,7 @@
         </is>
       </c>
       <c r="D24" s="5">
-        <f>IF(A24="","",IF(G24="legacy",DATE(2026,5,15),IF(ISNUMBER(F24),(F24+5)+CHOOSE(WEEKDAY(F24+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A24="","",IF(ISNUMBER(E24),MAX(DATE(2026,6,3),E24),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E24" s="5">
@@ -2506,17 +2502,17 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>CJ052501/02</t>
+          <t>OPM1024_02</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>P050172</t>
+          <t>P050062</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2530,17 +2526,17 @@
         </is>
       </c>
       <c r="N24" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050172|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O24" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050062|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2025-0009</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>P050172|I</t>
+          <t>P050062|I</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
@@ -2564,7 +2560,7 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>IF(A25="","",IF(G25="legacy",DATE(2026,5,15),IF(ISNUMBER(F25),(F25+5)+CHOOSE(WEEKDAY(F25+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A25="","",IF(ISNUMBER(E25),MAX(DATE(2026,6,3),E25),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E25" s="5">
@@ -2587,17 +2583,17 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>HPA052501</t>
+          <t>GP0824_03</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>P050182</t>
+          <t>P050072</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2611,17 +2607,17 @@
         </is>
       </c>
       <c r="N25" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050182|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050072|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0016</t>
+          <t>iCoA-PP-2025-0010</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>P050182|I</t>
+          <t>P050072|I</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
@@ -2645,7 +2641,7 @@
         </is>
       </c>
       <c r="D26" s="5">
-        <f>IF(A26="","",IF(G26="legacy",DATE(2026,5,15),IF(ISNUMBER(F26),(F26+5)+CHOOSE(WEEKDAY(F26+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A26="","",IF(ISNUMBER(E26),MAX(DATE(2026,6,3),E26),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E26" s="5">
@@ -2668,17 +2664,17 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>BSS052501</t>
+          <t>OPM1024_03</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>P050192</t>
+          <t>P050082</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2692,17 +2688,17 @@
         </is>
       </c>
       <c r="N26" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050192|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050082|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0017</t>
+          <t>iCoA-PP-2025-0011</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>P050192|I</t>
+          <t>P050082|I</t>
         </is>
       </c>
       <c r="Q26" s="7" t="inlineStr">
@@ -2726,7 +2722,7 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <f>IF(A27="","",IF(G27="legacy",DATE(2026,5,15),IF(ISNUMBER(F27),(F27+5)+CHOOSE(WEEKDAY(F27+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A27="","",IF(ISNUMBER(E27),MAX(DATE(2026,6,3),E27),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E27" s="5">
@@ -2749,17 +2745,17 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>GP062501</t>
+          <t>GG1024_01</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>P050202</t>
+          <t>P050092</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2773,17 +2769,17 @@
         </is>
       </c>
       <c r="N27" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050202|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O27" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050092|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2025-0012</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>P050202|I</t>
+          <t>P050092|I</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
@@ -2807,7 +2803,7 @@
         </is>
       </c>
       <c r="D28" s="5">
-        <f>IF(A28="","",IF(G28="legacy",DATE(2026,5,15),IF(ISNUMBER(F28),(F28+5)+CHOOSE(WEEKDAY(F28+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A28="","",IF(ISNUMBER(E28),MAX(DATE(2026,6,3),E28),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E28" s="5">
@@ -2830,17 +2826,17 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>CJ062501/2</t>
+          <t>GP0824_01</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>P050212</t>
+          <t>P050102</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2854,7 +2850,7 @@
         </is>
       </c>
       <c r="N28" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050212|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050102|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O28" s="6" t="inlineStr">
@@ -2864,7 +2860,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>P050212|I</t>
+          <t>P050102|I</t>
         </is>
       </c>
       <c r="Q28" s="7" t="inlineStr">
@@ -2888,7 +2884,7 @@
         </is>
       </c>
       <c r="D29" s="5">
-        <f>IF(A29="","",IF(G29="legacy",DATE(2026,5,15),IF(ISNUMBER(F29),(F29+5)+CHOOSE(WEEKDAY(F29+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A29="","",IF(ISNUMBER(E29),MAX(DATE(2026,6,3),E29),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E29" s="5">
@@ -2911,17 +2907,17 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>CJ062501/1</t>
+          <t>MB0824_05</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>P050222</t>
+          <t>P050112</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2935,17 +2931,17 @@
         </is>
       </c>
       <c r="N29" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050222|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050112|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0018</t>
+          <t>iCoA-PP-2025-0013</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>P050222|I</t>
+          <t>P050112|I</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
@@ -2969,7 +2965,7 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <f>IF(A30="","",IF(G30="legacy",DATE(2026,5,15),IF(ISNUMBER(F30),(F30+5)+CHOOSE(WEEKDAY(F30+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A30="","",IF(ISNUMBER(E30),MAX(DATE(2026,6,3),E30),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E30" s="5">
@@ -2992,17 +2988,17 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>CJ072501</t>
+          <t>BSS1024_01/1</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>P050252</t>
+          <t>P050122</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3016,7 +3012,7 @@
         </is>
       </c>
       <c r="N30" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050252|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050122|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O30" s="6" t="inlineStr">
@@ -3026,7 +3022,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>P050252|I</t>
+          <t>P050122|I</t>
         </is>
       </c>
       <c r="Q30" s="7" t="inlineStr">
@@ -3050,7 +3046,7 @@
         </is>
       </c>
       <c r="D31" s="5">
-        <f>IF(A31="","",IF(G31="legacy",DATE(2026,5,15),IF(ISNUMBER(F31),(F31+5)+CHOOSE(WEEKDAY(F31+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A31="","",IF(ISNUMBER(E31),MAX(DATE(2026,6,3),E31),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E31" s="5">
@@ -3073,17 +3069,17 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>WC072501</t>
+          <t>OPM052501</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>P050262</t>
+          <t>P050132</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Wedding Crusher</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3097,7 +3093,7 @@
         </is>
       </c>
       <c r="N31" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050262|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050132|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O31" s="6" t="inlineStr">
@@ -3107,7 +3103,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>P050262|I</t>
+          <t>P050132|I</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
@@ -3131,7 +3127,7 @@
         </is>
       </c>
       <c r="D32" s="5">
-        <f>IF(A32="","",IF(G32="legacy",DATE(2026,5,15),IF(ISNUMBER(F32),(F32+5)+CHOOSE(WEEKDAY(F32+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A32="","",IF(ISNUMBER(E32),MAX(DATE(2026,6,3),E32),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E32" s="5">
@@ -3154,17 +3150,17 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>PM072501</t>
+          <t>GP052501</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>P050272</t>
+          <t>P050152</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3178,17 +3174,17 @@
         </is>
       </c>
       <c r="N32" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050272|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050152|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2025-0014</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>P050272|I</t>
+          <t>P050152|I</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
@@ -3212,7 +3208,7 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <f>IF(A33="","",IF(G33="legacy",DATE(2026,5,15),IF(ISNUMBER(F33),(F33+5)+CHOOSE(WEEKDAY(F33+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A33="","",IF(ISNUMBER(E33),MAX(DATE(2026,6,3),E33),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E33" s="5">
@@ -3235,17 +3231,17 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>CLE072501</t>
+          <t>BSS1024_01/2</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>P050282</t>
+          <t>P050142</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Clemosa a bud</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -3259,17 +3255,17 @@
         </is>
       </c>
       <c r="N33" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050282|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2025-0019</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050142|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>P050282|I</t>
+          <t>P050142|I</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
@@ -3293,7 +3289,7 @@
         </is>
       </c>
       <c r="D34" s="5">
-        <f>IF(A34="","",IF(G34="legacy",DATE(2026,5,15),IF(ISNUMBER(F34),(F34+5)+CHOOSE(WEEKDAY(F34+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A34="","",IF(ISNUMBER(E34),MAX(DATE(2026,6,3),E34),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E34" s="5">
@@ -3316,17 +3312,17 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>GP072501/1</t>
+          <t>CJ052501/01</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>P050292</t>
+          <t>P050162</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Cup Junky</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3340,17 +3336,17 @@
         </is>
       </c>
       <c r="N34" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050292|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O34" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050162|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2025-0015</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>P050292|I</t>
+          <t>P050162|I</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
@@ -3374,7 +3370,7 @@
         </is>
       </c>
       <c r="D35" s="5">
-        <f>IF(A35="","",IF(G35="legacy",DATE(2026,5,15),IF(ISNUMBER(F35),(F35+5)+CHOOSE(WEEKDAY(F35+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A35="","",IF(ISNUMBER(E35),MAX(DATE(2026,6,3),E35),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E35" s="5">
@@ -3397,17 +3393,17 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>GP072501/2</t>
+          <t>CJ052501/02</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>P050302</t>
+          <t>P050172</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3421,17 +3417,17 @@
         </is>
       </c>
       <c r="N35" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050302|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2025-0020</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050172|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>P050302|I</t>
+          <t>P050172|I</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
@@ -3455,7 +3451,7 @@
         </is>
       </c>
       <c r="D36" s="5">
-        <f>IF(A36="","",IF(G36="legacy",DATE(2026,5,15),IF(ISNUMBER(F36),(F36+5)+CHOOSE(WEEKDAY(F36+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A36="","",IF(ISNUMBER(E36),MAX(DATE(2026,6,3),E36),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E36" s="5">
@@ -3478,17 +3474,17 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>GP082501/1</t>
+          <t>HPA052501</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>P050312</t>
+          <t>P050182</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3502,17 +3498,17 @@
         </is>
       </c>
       <c r="N36" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050312|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050182|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0021</t>
+          <t>iCoA-PP-2025-0016</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>P050312|I</t>
+          <t>P050182|I</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
@@ -3536,7 +3532,7 @@
         </is>
       </c>
       <c r="D37" s="5">
-        <f>IF(A37="","",IF(G37="legacy",DATE(2026,5,15),IF(ISNUMBER(F37),(F37+5)+CHOOSE(WEEKDAY(F37+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A37="","",IF(ISNUMBER(E37),MAX(DATE(2026,6,3),E37),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E37" s="5">
@@ -3559,17 +3555,17 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>GP082501/2</t>
+          <t>BSS052501</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>P050322</t>
+          <t>P050192</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -3583,17 +3579,17 @@
         </is>
       </c>
       <c r="N37" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050322|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050192|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2025-0022</t>
+          <t>iCoA-PP-2025-0017</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>P050322|I</t>
+          <t>P050192|I</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
@@ -3617,7 +3613,7 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <f>IF(A38="","",IF(G38="legacy",DATE(2026,5,15),IF(ISNUMBER(F38),(F38+5)+CHOOSE(WEEKDAY(F38+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A38="","",IF(ISNUMBER(E38),MAX(DATE(2026,6,3),E38),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E38" s="5">
@@ -3640,17 +3636,17 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>WC082501</t>
+          <t>GP062501</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>P060012</t>
+          <t>P050202</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3664,17 +3660,17 @@
         </is>
       </c>
       <c r="N38" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060012|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0001</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050202|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>P060012|I</t>
+          <t>P050202|I</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
@@ -3698,7 +3694,7 @@
         </is>
       </c>
       <c r="D39" s="5">
-        <f>IF(A39="","",IF(G39="legacy",DATE(2026,5,15),IF(ISNUMBER(F39),(F39+5)+CHOOSE(WEEKDAY(F39+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A39="","",IF(ISNUMBER(E39),MAX(DATE(2026,6,3),E39),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E39" s="5">
@@ -3721,17 +3717,17 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>CJ082501/1</t>
+          <t>CJ062501/2</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>P060022</t>
+          <t>P050212</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3745,17 +3741,17 @@
         </is>
       </c>
       <c r="N39" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060022|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0002</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050212|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>P060022|I</t>
+          <t>P050212|I</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
@@ -3779,7 +3775,7 @@
         </is>
       </c>
       <c r="D40" s="5">
-        <f>IF(A40="","",IF(G40="legacy",DATE(2026,5,15),IF(ISNUMBER(F40),(F40+5)+CHOOSE(WEEKDAY(F40+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A40="","",IF(ISNUMBER(E40),MAX(DATE(2026,6,3),E40),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E40" s="5">
@@ -3802,17 +3798,17 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>CJ082501/2</t>
+          <t>CJ062501/1</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>P060032</t>
+          <t>P050222</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3826,17 +3822,17 @@
         </is>
       </c>
       <c r="N40" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060032|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050222|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0003</t>
+          <t>iCoA-PP-2025-0018</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>P060032|I</t>
+          <t>P050222|I</t>
         </is>
       </c>
       <c r="Q40" s="7" t="inlineStr">
@@ -3860,7 +3856,7 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <f>IF(A41="","",IF(G41="legacy",DATE(2026,5,15),IF(ISNUMBER(F41),(F41+5)+CHOOSE(WEEKDAY(F41+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A41="","",IF(ISNUMBER(E41),MAX(DATE(2026,6,3),E41),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E41" s="5">
@@ -3883,17 +3879,17 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>OPM092501</t>
+          <t>CJ072501</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>P060042</t>
+          <t>P050252</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3907,17 +3903,17 @@
         </is>
       </c>
       <c r="N41" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060042|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0004</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050252|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>P060042|I</t>
+          <t>P050252|I</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
@@ -3941,7 +3937,7 @@
         </is>
       </c>
       <c r="D42" s="5">
-        <f>IF(A42="","",IF(G42="legacy",DATE(2026,5,15),IF(ISNUMBER(F42),(F42+5)+CHOOSE(WEEKDAY(F42+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A42="","",IF(ISNUMBER(E42),MAX(DATE(2026,6,3),E42),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E42" s="5">
@@ -3964,17 +3960,17 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>AB092501</t>
+          <t>WC072501</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>P060052</t>
+          <t>P050262</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Apple and Banana</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3988,7 +3984,7 @@
         </is>
       </c>
       <c r="N42" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060052|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050262|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O42" s="6" t="inlineStr">
@@ -3998,7 +3994,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>P060052|I</t>
+          <t>P050262|I</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
@@ -4022,7 +4018,7 @@
         </is>
       </c>
       <c r="D43" s="5">
-        <f>IF(A43="","",IF(G43="legacy",DATE(2026,5,15),IF(ISNUMBER(F43),(F43+5)+CHOOSE(WEEKDAY(F43+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A43="","",IF(ISNUMBER(E43),MAX(DATE(2026,6,3),E43),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E43" s="5">
@@ -4045,17 +4041,17 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>PM092501</t>
+          <t>PM072501</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>P060062</t>
+          <t>P050272</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -4069,17 +4065,17 @@
         </is>
       </c>
       <c r="N43" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060062|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0005</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050272|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>P060062|I</t>
+          <t>P050272|I</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
@@ -4103,7 +4099,7 @@
         </is>
       </c>
       <c r="D44" s="5">
-        <f>IF(A44="","",IF(G44="legacy",DATE(2026,5,15),IF(ISNUMBER(F44),(F44+5)+CHOOSE(WEEKDAY(F44+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A44="","",IF(ISNUMBER(E44),MAX(DATE(2026,6,3),E44),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E44" s="5">
@@ -4126,17 +4122,17 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>CJ092501</t>
+          <t>CLE072501</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>P060072</t>
+          <t>P050282</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Clemosa a bud</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4150,17 +4146,17 @@
         </is>
       </c>
       <c r="N44" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060072|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050282|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0006</t>
+          <t>iCoA-PP-2025-0019</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>P060072|I</t>
+          <t>P050282|I</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
@@ -4184,7 +4180,7 @@
         </is>
       </c>
       <c r="D45" s="5">
-        <f>IF(A45="","",IF(G45="legacy",DATE(2026,5,15),IF(ISNUMBER(F45),(F45+5)+CHOOSE(WEEKDAY(F45+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A45="","",IF(ISNUMBER(E45),MAX(DATE(2026,6,3),E45),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E45" s="5">
@@ -4207,15 +4203,19 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>SJ0925021</t>
+          <t>GP072501/1</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>P060082</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
+          <t>P050292</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -4227,17 +4227,17 @@
         </is>
       </c>
       <c r="N45" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060082|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0007</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050292|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>P060082|I</t>
+          <t>P050292|I</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="D46" s="5">
-        <f>IF(A46="","",IF(G46="legacy",DATE(2026,5,15),IF(ISNUMBER(F46),(F46+5)+CHOOSE(WEEKDAY(F46+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A46="","",IF(ISNUMBER(E46),MAX(DATE(2026,6,3),E46),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E46" s="5">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>GP092501</t>
+          <t>GP072501/2</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>P060092</t>
+          <t>P050302</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -4308,17 +4308,17 @@
         </is>
       </c>
       <c r="N46" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060092|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050302|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0008</t>
+          <t>iCoA-PP-2025-0020</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>P060092|I</t>
+          <t>P050302|I</t>
         </is>
       </c>
       <c r="Q46" s="7" t="inlineStr">
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="D47" s="5">
-        <f>IF(A47="","",IF(G47="legacy",DATE(2026,5,15),IF(ISNUMBER(F47),(F47+5)+CHOOSE(WEEKDAY(F47+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A47="","",IF(ISNUMBER(E47),MAX(DATE(2026,6,3),E47),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E47" s="5">
@@ -4365,17 +4365,17 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>WED102501</t>
+          <t>GP082501/1</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>P060102</t>
+          <t>P050312</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Wedding Cake</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -4389,17 +4389,17 @@
         </is>
       </c>
       <c r="N47" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060102|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O47" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050312|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2025-0021</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>P060102|I</t>
+          <t>P050312|I</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="D48" s="5">
-        <f>IF(A48="","",IF(G48="legacy",DATE(2026,5,15),IF(ISNUMBER(F48),(F48+5)+CHOOSE(WEEKDAY(F48+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A48="","",IF(ISNUMBER(E48),MAX(DATE(2026,6,3),E48),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E48" s="5">
@@ -4446,17 +4446,17 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>GRC102501</t>
+          <t>GP082501/2</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>P060142</t>
+          <t>P050322</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4470,17 +4470,17 @@
         </is>
       </c>
       <c r="N48" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060142|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O48" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P050322|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2025-0022</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>P060142|I</t>
+          <t>P050322|I</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="D49" s="5">
-        <f>IF(A49="","",IF(G49="legacy",DATE(2026,5,15),IF(ISNUMBER(F49),(F49+5)+CHOOSE(WEEKDAY(F49+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A49="","",IF(ISNUMBER(E49),MAX(DATE(2026,6,3),E49),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E49" s="5">
@@ -4527,17 +4527,17 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>J31102501</t>
+          <t>WC082501</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>P060152</t>
+          <t>P060012</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Wedding Crasher</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -4551,17 +4551,17 @@
         </is>
       </c>
       <c r="N49" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060152|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060012|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0012</t>
+          <t>iCoA-PP-2026-0001</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>P060152|I</t>
+          <t>P060012|I</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="D50" s="5">
-        <f>IF(A50="","",IF(G50="legacy",DATE(2026,5,15),IF(ISNUMBER(F50),(F50+5)+CHOOSE(WEEKDAY(F50+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A50="","",IF(ISNUMBER(E50),MAX(DATE(2026,6,3),E50),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E50" s="5">
@@ -4608,17 +4608,17 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>SJ102501</t>
+          <t>CJ082501/1</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>P060162</t>
+          <t>P060022</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4632,17 +4632,17 @@
         </is>
       </c>
       <c r="N50" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060162|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O50" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060022|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0002</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>P060162|I</t>
+          <t>P060022|I</t>
         </is>
       </c>
       <c r="Q50" s="7" t="inlineStr">
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="D51" s="5">
-        <f>IF(A51="","",IF(G51="legacy",DATE(2026,5,15),IF(ISNUMBER(F51),(F51+5)+CHOOSE(WEEKDAY(F51+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A51="","",IF(ISNUMBER(E51),MAX(DATE(2026,6,3),E51),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E51" s="5">
@@ -4689,17 +4689,17 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>KC102501</t>
+          <t>CJ082501/2</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>P060172</t>
+          <t>P060032</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -4713,17 +4713,17 @@
         </is>
       </c>
       <c r="N51" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060172|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060032|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0013</t>
+          <t>iCoA-PP-2026-0003</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>P060172|I</t>
+          <t>P060032|I</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="D52" s="5">
-        <f>IF(A52="","",IF(G52="legacy",DATE(2026,5,15),IF(ISNUMBER(F52),(F52+5)+CHOOSE(WEEKDAY(F52+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A52="","",IF(ISNUMBER(E52),MAX(DATE(2026,6,3),E52),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E52" s="5">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>GRC102501</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>P060182</t>
+          <t>P060042</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4794,17 +4794,17 @@
         </is>
       </c>
       <c r="N52" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060182|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060042|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0014</t>
+          <t>iCoA-PP-2026-0004</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>P060182|I</t>
+          <t>P060042|I</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="D53" s="5">
-        <f>IF(A53="","",IF(G53="legacy",DATE(2026,5,15),IF(ISNUMBER(F53),(F53+5)+CHOOSE(WEEKDAY(F53+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A53="","",IF(ISNUMBER(E53),MAX(DATE(2026,6,3),E53),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E53" s="5">
@@ -4851,17 +4851,17 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>SJ112501</t>
+          <t>AB092501</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>P060192</t>
+          <t>P060052</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Apple and Banana</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="N53" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060192|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060052|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O53" s="6" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>P060192|I</t>
+          <t>P060052|I</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="D54" s="5">
-        <f>IF(A54="","",IF(G54="legacy",DATE(2026,5,15),IF(ISNUMBER(F54),(F54+5)+CHOOSE(WEEKDAY(F54+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A54="","",IF(ISNUMBER(E54),MAX(DATE(2026,6,3),E54),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E54" s="5">
@@ -4932,17 +4932,17 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>J31112501</t>
+          <t>PM092501</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>P060202</t>
+          <t>P060062</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Permanent Market</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -4956,17 +4956,17 @@
         </is>
       </c>
       <c r="N54" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060202|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O54" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060062|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0005</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>P060202|I</t>
+          <t>P060062|I</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="D55" s="5">
-        <f>IF(A55="","",IF(G55="legacy",DATE(2026,5,15),IF(ISNUMBER(F55),(F55+5)+CHOOSE(WEEKDAY(F55+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A55="","",IF(ISNUMBER(E55),MAX(DATE(2026,6,3),E55),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E55" s="5">
@@ -5013,17 +5013,17 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>JD112501</t>
+          <t>CJ092501</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>P060212</t>
+          <t>P060072</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -5037,17 +5037,17 @@
         </is>
       </c>
       <c r="N55" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060212|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060072|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0015</t>
+          <t>iCoA-PP-2026-0006</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>P060212|I</t>
+          <t>P060072|I</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="D56" s="5">
-        <f>IF(A56="","",IF(G56="legacy",DATE(2026,5,15),IF(ISNUMBER(F56),(F56+5)+CHOOSE(WEEKDAY(F56+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A56="","",IF(ISNUMBER(E56),MAX(DATE(2026,6,3),E56),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E56" s="5">
@@ -5094,19 +5094,15 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>OPM112501</t>
+          <t>SJ0925021</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>P060222</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa</t>
-        </is>
-      </c>
+          <t>P060082</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -5118,17 +5114,17 @@
         </is>
       </c>
       <c r="N56" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060222|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O56" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060082|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0007</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>P060222|I</t>
+          <t>P060082|I</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
@@ -5152,7 +5148,7 @@
         </is>
       </c>
       <c r="D57" s="5">
-        <f>IF(A57="","",IF(G57="legacy",DATE(2026,5,15),IF(ISNUMBER(F57),(F57+5)+CHOOSE(WEEKDAY(F57+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A57="","",IF(ISNUMBER(E57),MAX(DATE(2026,6,3),E57),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E57" s="5">
@@ -5175,17 +5171,17 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>PM112501</t>
+          <t>GP092501</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>P060232</t>
+          <t>P060092</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -5199,17 +5195,17 @@
         </is>
       </c>
       <c r="N57" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060232|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060092|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0016</t>
+          <t>iCoA-PP-2026-0008</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>P060232|I</t>
+          <t>P060092|I</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
@@ -5233,7 +5229,7 @@
         </is>
       </c>
       <c r="D58" s="5">
-        <f>IF(A58="","",IF(G58="legacy",DATE(2026,5,15),IF(ISNUMBER(F58),(F58+5)+CHOOSE(WEEKDAY(F58+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A58="","",IF(ISNUMBER(E58),MAX(DATE(2026,6,3),E58),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E58" s="5">
@@ -5256,17 +5252,17 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>OPM122501</t>
+          <t>WED102501</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>P060242</t>
+          <t>P060102</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Wedding Cake</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5280,17 +5276,17 @@
         </is>
       </c>
       <c r="N58" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060242|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0017</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060102|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O58" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>P060242|I</t>
+          <t>P060102|I</t>
         </is>
       </c>
       <c r="Q58" s="7" t="inlineStr">
@@ -5314,7 +5310,7 @@
         </is>
       </c>
       <c r="D59" s="5">
-        <f>IF(A59="","",IF(G59="legacy",DATE(2026,5,15),IF(ISNUMBER(F59),(F59+5)+CHOOSE(WEEKDAY(F59+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A59="","",IF(ISNUMBER(E59),MAX(DATE(2026,6,3),E59),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E59" s="5">
@@ -5337,17 +5333,17 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>GG112501</t>
+          <t>GRC102501</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>P060252</t>
+          <t>P060142</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Graps &amp; Creme</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -5361,7 +5357,7 @@
         </is>
       </c>
       <c r="N59" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060252|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060142|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O59" s="6" t="inlineStr">
@@ -5371,7 +5367,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>P060252|I</t>
+          <t>P060142|I</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
@@ -5395,7 +5391,7 @@
         </is>
       </c>
       <c r="D60" s="5">
-        <f>IF(A60="","",IF(G60="legacy",DATE(2026,5,15),IF(ISNUMBER(F60),(F60+5)+CHOOSE(WEEKDAY(F60+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A60="","",IF(ISNUMBER(E60),MAX(DATE(2026,6,3),E60),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E60" s="5">
@@ -5408,7 +5404,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -5418,12 +5414,12 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>J31102501</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>P060262</t>
+          <t>P060152</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -5442,22 +5438,22 @@
         </is>
       </c>
       <c r="N60" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060262|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O60" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060152|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0012</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>P060262|I</t>
+          <t>P060152|I</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 5 days after packaging</t>
+          <t>registered — issued with the legacy series on 15.05.2026</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5472,7 @@
         </is>
       </c>
       <c r="D61" s="5">
-        <f>IF(A61="","",IF(G61="legacy",DATE(2026,5,15),IF(ISNUMBER(F61),(F61+5)+CHOOSE(WEEKDAY(F61+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A61="","",IF(ISNUMBER(E61),MAX(DATE(2026,6,3),E61),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E61" s="5">
@@ -5489,7 +5485,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5499,17 +5495,17 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>CC112501</t>
+          <t>SJ102501</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>P060272</t>
+          <t>P060162</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -5523,7 +5519,7 @@
         </is>
       </c>
       <c r="N61" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060272|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060162|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O61" s="6" t="inlineStr">
@@ -5533,12 +5529,12 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>P060272|I</t>
+          <t>P060162|I</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 5 days after packaging</t>
+          <t>registered — issued with the legacy series on 15.05.2026</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5553,7 @@
         </is>
       </c>
       <c r="D62" s="5">
-        <f>IF(A62="","",IF(G62="legacy",DATE(2026,5,15),IF(ISNUMBER(F62),(F62+5)+CHOOSE(WEEKDAY(F62+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A62="","",IF(ISNUMBER(E62),MAX(DATE(2026,6,3),E62),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E62" s="5">
@@ -5570,7 +5566,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5580,17 +5576,17 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>SCR112501</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>P060282</t>
+          <t>P060172</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -5604,22 +5600,22 @@
         </is>
       </c>
       <c r="N62" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060282|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060172|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0018</t>
+          <t>iCoA-PP-2026-0013</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>P060282|I</t>
+          <t>P060172|I</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 5 days after packaging</t>
+          <t>registered — issued with the legacy series on 15.05.2026</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5634,7 @@
         </is>
       </c>
       <c r="D63" s="5">
-        <f>IF(A63="","",IF(G63="legacy",DATE(2026,5,15),IF(ISNUMBER(F63),(F63+5)+CHOOSE(WEEKDAY(F63+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A63="","",IF(ISNUMBER(E63),MAX(DATE(2026,6,3),E63),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E63" s="5">
@@ -5651,7 +5647,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5661,17 +5657,17 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>GRC102501</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>P060292</t>
+          <t>P060182</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Graps &amp; Creme</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -5685,22 +5681,22 @@
         </is>
       </c>
       <c r="N63" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060292|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O63" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060182|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0014</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>P060292|I</t>
+          <t>P060182|I</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 5 days after packaging</t>
+          <t>registered — issued with the legacy series on 15.05.2026</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5715,7 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <f>IF(A64="","",IF(G64="legacy",DATE(2026,5,15),IF(ISNUMBER(F64),(F64+5)+CHOOSE(WEEKDAY(F64+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A64="","",IF(ISNUMBER(E64),MAX(DATE(2026,6,3),E64),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E64" s="5">
@@ -5732,7 +5728,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5742,17 +5738,17 @@
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>GG012601＊</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>P060302</t>
+          <t>P060192</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -5766,7 +5762,7 @@
         </is>
       </c>
       <c r="N64" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060302|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060192|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O64" s="6" t="inlineStr">
@@ -5776,12 +5772,12 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>P060302|I</t>
+          <t>P060192|I</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 5 days after packaging</t>
+          <t>registered — issued with the legacy series on 15.05.2026</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5796,7 @@
         </is>
       </c>
       <c r="D65" s="5">
-        <f>IF(A65="","",IF(G65="legacy",DATE(2026,5,15),IF(ISNUMBER(F65),(F65+5)+CHOOSE(WEEKDAY(F65+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A65="","",IF(ISNUMBER(E65),MAX(DATE(2026,6,3),E65),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E65" s="5">
@@ -5813,7 +5809,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5823,17 +5819,17 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>JD012601＊</t>
+          <t>J31112501</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>P060312</t>
+          <t>P060202</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -5847,7 +5843,7 @@
         </is>
       </c>
       <c r="N65" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060312|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060202|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O65" s="6" t="inlineStr">
@@ -5857,12 +5853,12 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>P060312|I</t>
+          <t>P060202|I</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 5 days after packaging</t>
+          <t>registered — issued with the legacy series on 15.05.2026</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5877,7 @@
         </is>
       </c>
       <c r="D66" s="5">
-        <f>IF(A66="","",IF(G66="legacy",DATE(2026,5,15),IF(ISNUMBER(F66),(F66+5)+CHOOSE(WEEKDAY(F66+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A66="","",IF(ISNUMBER(E66),MAX(DATE(2026,6,3),E66),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E66" s="5">
@@ -5894,7 +5890,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5904,15 +5900,19 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
+          <t>JD112501</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>P060332</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr"/>
+          <t>P060212</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
           <t>Ident A + Ident B + Foreign matter</t>
@@ -5924,22 +5924,22 @@
         </is>
       </c>
       <c r="N66" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060332|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O66" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060212|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0015</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>P060332|I</t>
+          <t>P060212|I</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 5 days after packaging</t>
+          <t>registered — issued with the legacy series on 15.05.2026</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="D67" s="5">
-        <f>IF(A67="","",IF(G67="legacy",DATE(2026,5,15),IF(ISNUMBER(F67),(F67+5)+CHOOSE(WEEKDAY(F67+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A67="","",IF(ISNUMBER(E67),MAX(DATE(2026,6,3),E67),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E67" s="5">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5981,17 +5981,17 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>FB012601_1</t>
+          <t>OPM112501</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>P060322</t>
+          <t>P060222</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -6005,22 +6005,22 @@
         </is>
       </c>
       <c r="N67" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060322|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0019</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060222|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O67" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>P060322|I</t>
+          <t>P060222|I</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 5 days after packaging</t>
+          <t>registered — issued with the legacy series on 15.05.2026</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="D68" s="5">
-        <f>IF(A68="","",IF(G68="legacy",DATE(2026,5,15),IF(ISNUMBER(F68),(F68+5)+CHOOSE(WEEKDAY(F68+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A68="","",IF(ISNUMBER(E68),MAX(DATE(2026,6,3),E68),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E68" s="5">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -6062,17 +6062,17 @@
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>FB012602*</t>
+          <t>PM112501</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>P060352</t>
+          <t>P060232</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Permanent Market</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -6086,22 +6086,22 @@
         </is>
       </c>
       <c r="N68" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060352|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060232|I",'CoQ Register'!$S:$S,0)),"—")</f>
         <v/>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>iCoA-PP-2026-0021</t>
+          <t>iCoA-PP-2026-0016</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>P060352|I</t>
+          <t>P060232|I</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 5 days after packaging</t>
+          <t>registered — issued with the legacy series on 15.05.2026</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="D69" s="5">
-        <f>IF(A69="","",IF(G69="legacy",DATE(2026,5,15),IF(ISNUMBER(F69),(F69+5)+CHOOSE(WEEKDAY(F69+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A69="","",IF(ISNUMBER(E69),MAX(DATE(2026,6,3),E69),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E69" s="5">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -6143,17 +6143,17 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>SCR012601*</t>
+          <t>OPM122501</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>P060342</t>
+          <t>P060242</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -6167,22 +6167,22 @@
         </is>
       </c>
       <c r="N69" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060342|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O69" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060242|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>iCoA-PP-2026-0017</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>P060342|I</t>
+          <t>P060242|I</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 5 days after packaging</t>
+          <t>registered — issued with the legacy series on 15.05.2026</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="D70" s="5">
-        <f>IF(A70="","",IF(G70="legacy",DATE(2026,5,15),IF(ISNUMBER(F70),(F70+5)+CHOOSE(WEEKDAY(F70+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A70="","",IF(ISNUMBER(E70),MAX(DATE(2026,6,3),E70),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E70" s="5">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>post-SOP</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -6224,17 +6224,17 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>SCR012603</t>
+          <t>GG112501</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>P060382</t>
+          <t>P060252</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -6248,22 +6248,22 @@
         </is>
       </c>
       <c r="N70" s="2">
-        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060382|I",'CoQ Register'!$S:$S,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>iCoA-PP-2026-0026</t>
+        <f>IFERROR(INDEX('CoQ Register'!$B:$B,MATCH("P060252|I",'CoQ Register'!$S:$S,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="O70" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>P060382|I</t>
+          <t>P060252|I</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
         <is>
-          <t>registered — first working day 5 days after packaging</t>
+          <t>registered — issued with the legacy series on 15.05.2026</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="D71" s="5">
-        <f>IF(A71="","",IF(G71="legacy",DATE(2026,5,15),IF(ISNUMBER(F71),(F71+5)+CHOOSE(WEEKDAY(F71+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A71="","",IF(ISNUMBER(E71),MAX(DATE(2026,6,3),E71),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E71" s="5">
@@ -6363,7 +6363,7 @@
         </is>
       </c>
       <c r="D72" s="5">
-        <f>IF(A72="","",IF(G72="legacy",DATE(2026,5,15),IF(ISNUMBER(F72),(F72+5)+CHOOSE(WEEKDAY(F72+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A72="","",IF(ISNUMBER(E72),MAX(DATE(2026,6,3),E72),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E72" s="5">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="D73" s="5">
-        <f>IF(A73="","",IF(G73="legacy",DATE(2026,5,15),IF(ISNUMBER(F73),(F73+5)+CHOOSE(WEEKDAY(F73+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A73="","",IF(ISNUMBER(E73),MAX(DATE(2026,6,3),E73),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E73" s="5">
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="D74" s="5">
-        <f>IF(A74="","",IF(G74="legacy",DATE(2026,5,15),IF(ISNUMBER(F74),(F74+5)+CHOOSE(WEEKDAY(F74+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A74="","",IF(ISNUMBER(E74),MAX(DATE(2026,6,3),E74),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E74" s="5">
@@ -6598,7 +6598,7 @@
         </is>
       </c>
       <c r="D75" s="5">
-        <f>IF(A75="","",IF(G75="legacy",DATE(2026,5,15),IF(ISNUMBER(F75),(F75+5)+CHOOSE(WEEKDAY(F75+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A75="","",IF(ISNUMBER(E75),MAX(DATE(2026,6,3),E75),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E75" s="5">
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="D76" s="5">
-        <f>IF(A76="","",IF(G76="legacy",DATE(2026,5,15),IF(ISNUMBER(F76),(F76+5)+CHOOSE(WEEKDAY(F76+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A76="","",IF(ISNUMBER(E76),MAX(DATE(2026,6,3),E76),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E76" s="5">
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="D77" s="5">
-        <f>IF(A77="","",IF(G77="legacy",DATE(2026,5,15),IF(ISNUMBER(F77),(F77+5)+CHOOSE(WEEKDAY(F77+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A77="","",IF(ISNUMBER(E77),MAX(DATE(2026,6,3),E77),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E77" s="5">
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="D78" s="5">
-        <f>IF(A78="","",IF(G78="legacy",DATE(2026,5,15),IF(ISNUMBER(F78),(F78+5)+CHOOSE(WEEKDAY(F78+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A78="","",IF(ISNUMBER(E78),MAX(DATE(2026,6,3),E78),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E78" s="5">
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="D79" s="5">
-        <f>IF(A79="","",IF(G79="legacy",DATE(2026,5,15),IF(ISNUMBER(F79),(F79+5)+CHOOSE(WEEKDAY(F79+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A79="","",IF(ISNUMBER(E79),MAX(DATE(2026,6,3),E79),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E79" s="5">
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="D80" s="5">
-        <f>IF(A80="","",IF(G80="legacy",DATE(2026,5,15),IF(ISNUMBER(F80),(F80+5)+CHOOSE(WEEKDAY(F80+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A80="","",IF(ISNUMBER(E80),MAX(DATE(2026,6,3),E80),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E80" s="5">
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="D81" s="5">
-        <f>IF(A81="","",IF(G81="legacy",DATE(2026,5,15),IF(ISNUMBER(F81),(F81+5)+CHOOSE(WEEKDAY(F81+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A81="","",IF(ISNUMBER(E81),MAX(DATE(2026,6,3),E81),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E81" s="5">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="D82" s="5">
-        <f>IF(A82="","",IF(G82="legacy",DATE(2026,5,15),IF(ISNUMBER(F82),(F82+5)+CHOOSE(WEEKDAY(F82+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A82="","",IF(ISNUMBER(E82),MAX(DATE(2026,6,3),E82),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E82" s="5">
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="D83" s="5">
-        <f>IF(A83="","",IF(G83="legacy",DATE(2026,5,15),IF(ISNUMBER(F83),(F83+5)+CHOOSE(WEEKDAY(F83+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A83="","",IF(ISNUMBER(E83),MAX(DATE(2026,6,3),E83),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E83" s="5">
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="D84" s="5">
-        <f>IF(A84="","",IF(G84="legacy",DATE(2026,5,15),IF(ISNUMBER(F84),(F84+5)+CHOOSE(WEEKDAY(F84+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A84="","",IF(ISNUMBER(E84),MAX(DATE(2026,6,3),E84),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E84" s="5">
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="D85" s="5">
-        <f>IF(A85="","",IF(G85="legacy",DATE(2026,5,15),IF(ISNUMBER(F85),(F85+5)+CHOOSE(WEEKDAY(F85+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A85="","",IF(ISNUMBER(E85),MAX(DATE(2026,6,3),E85),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="D86" s="5">
-        <f>IF(A86="","",IF(G86="legacy",DATE(2026,5,15),IF(ISNUMBER(F86),(F86+5)+CHOOSE(WEEKDAY(F86+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A86="","",IF(ISNUMBER(E86),MAX(DATE(2026,6,3),E86),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="D87" s="5">
-        <f>IF(A87="","",IF(G87="legacy",DATE(2026,5,15),IF(ISNUMBER(F87),(F87+5)+CHOOSE(WEEKDAY(F87+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A87="","",IF(ISNUMBER(E87),MAX(DATE(2026,6,3),E87),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="D88" s="5">
-        <f>IF(A88="","",IF(G88="legacy",DATE(2026,5,15),IF(ISNUMBER(F88),(F88+5)+CHOOSE(WEEKDAY(F88+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A88="","",IF(ISNUMBER(E88),MAX(DATE(2026,6,3),E88),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="D89" s="5">
-        <f>IF(A89="","",IF(G89="legacy",DATE(2026,5,15),IF(ISNUMBER(F89),(F89+5)+CHOOSE(WEEKDAY(F89+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A89="","",IF(ISNUMBER(E89),MAX(DATE(2026,6,3),E89),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -7802,7 +7802,7 @@
         </is>
       </c>
       <c r="D90" s="5">
-        <f>IF(A90="","",IF(G90="legacy",DATE(2026,5,15),IF(ISNUMBER(F90),(F90+5)+CHOOSE(WEEKDAY(F90+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A90="","",IF(ISNUMBER(E90),MAX(DATE(2026,6,3),E90),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="D91" s="5">
-        <f>IF(A91="","",IF(G91="legacy",DATE(2026,5,15),IF(ISNUMBER(F91),(F91+5)+CHOOSE(WEEKDAY(F91+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A91="","",IF(ISNUMBER(E91),MAX(DATE(2026,6,3),E91),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -7966,7 +7966,7 @@
         </is>
       </c>
       <c r="D92" s="5">
-        <f>IF(A92="","",IF(G92="legacy",DATE(2026,5,15),IF(ISNUMBER(F92),(F92+5)+CHOOSE(WEEKDAY(F92+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A92="","",IF(ISNUMBER(E92),MAX(DATE(2026,6,3),E92),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="D93" s="5">
-        <f>IF(A93="","",IF(G93="legacy",DATE(2026,5,15),IF(ISNUMBER(F93),(F93+5)+CHOOSE(WEEKDAY(F93+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A93="","",IF(ISNUMBER(E93),MAX(DATE(2026,6,3),E93),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -8130,7 +8130,7 @@
         </is>
       </c>
       <c r="D94" s="5">
-        <f>IF(A94="","",IF(G94="legacy",DATE(2026,5,15),IF(ISNUMBER(F94),(F94+5)+CHOOSE(WEEKDAY(F94+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A94="","",IF(ISNUMBER(E94),MAX(DATE(2026,6,3),E94),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -8212,7 +8212,7 @@
         </is>
       </c>
       <c r="D95" s="5">
-        <f>IF(A95="","",IF(G95="legacy",DATE(2026,5,15),IF(ISNUMBER(F95),(F95+5)+CHOOSE(WEEKDAY(F95+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A95="","",IF(ISNUMBER(E95),MAX(DATE(2026,6,3),E95),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="D96" s="5">
-        <f>IF(A96="","",IF(G96="legacy",DATE(2026,5,15),IF(ISNUMBER(F96),(F96+5)+CHOOSE(WEEKDAY(F96+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A96="","",IF(ISNUMBER(E96),MAX(DATE(2026,6,3),E96),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="D97" s="5">
-        <f>IF(A97="","",IF(G97="legacy",DATE(2026,5,15),IF(ISNUMBER(F97),(F97+5)+CHOOSE(WEEKDAY(F97+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A97="","",IF(ISNUMBER(E97),MAX(DATE(2026,6,3),E97),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -8458,7 +8458,7 @@
         </is>
       </c>
       <c r="D98" s="5">
-        <f>IF(A98="","",IF(G98="legacy",DATE(2026,5,15),IF(ISNUMBER(F98),(F98+5)+CHOOSE(WEEKDAY(F98+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A98="","",IF(ISNUMBER(E98),MAX(DATE(2026,6,3),E98),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="D99" s="5">
-        <f>IF(A99="","",IF(G99="legacy",DATE(2026,5,15),IF(ISNUMBER(F99),(F99+5)+CHOOSE(WEEKDAY(F99+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A99="","",IF(ISNUMBER(E99),MAX(DATE(2026,6,3),E99),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="D100" s="5">
-        <f>IF(A100="","",IF(G100="legacy",DATE(2026,5,15),IF(ISNUMBER(F100),(F100+5)+CHOOSE(WEEKDAY(F100+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A100="","",IF(ISNUMBER(E100),MAX(DATE(2026,6,3),E100),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="D101" s="5">
-        <f>IF(A101="","",IF(G101="legacy",DATE(2026,5,15),IF(ISNUMBER(F101),(F101+5)+CHOOSE(WEEKDAY(F101+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A101="","",IF(ISNUMBER(E101),MAX(DATE(2026,6,3),E101),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="D102" s="5">
-        <f>IF(A102="","",IF(G102="legacy",DATE(2026,5,15),IF(ISNUMBER(F102),(F102+5)+CHOOSE(WEEKDAY(F102+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A102="","",IF(ISNUMBER(E102),MAX(DATE(2026,6,3),E102),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="D103" s="5">
-        <f>IF(A103="","",IF(G103="legacy",DATE(2026,5,15),IF(ISNUMBER(F103),(F103+5)+CHOOSE(WEEKDAY(F103+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A103="","",IF(ISNUMBER(E103),MAX(DATE(2026,6,3),E103),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="D104" s="5">
-        <f>IF(A104="","",IF(G104="legacy",DATE(2026,5,15),IF(ISNUMBER(F104),(F104+5)+CHOOSE(WEEKDAY(F104+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A104="","",IF(ISNUMBER(E104),MAX(DATE(2026,6,3),E104),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="D105" s="5">
-        <f>IF(A105="","",IF(G105="legacy",DATE(2026,5,15),IF(ISNUMBER(F105),(F105+5)+CHOOSE(WEEKDAY(F105+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A105="","",IF(ISNUMBER(E105),MAX(DATE(2026,6,3),E105),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="D106" s="5">
-        <f>IF(A106="","",IF(G106="legacy",DATE(2026,5,15),IF(ISNUMBER(F106),(F106+5)+CHOOSE(WEEKDAY(F106+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A106="","",IF(ISNUMBER(E106),MAX(DATE(2026,6,3),E106),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="D107" s="5">
-        <f>IF(A107="","",IF(G107="legacy",DATE(2026,5,15),IF(ISNUMBER(F107),(F107+5)+CHOOSE(WEEKDAY(F107+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A107="","",IF(ISNUMBER(E107),MAX(DATE(2026,6,3),E107),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="D108" s="5">
-        <f>IF(A108="","",IF(G108="legacy",DATE(2026,5,15),IF(ISNUMBER(F108),(F108+5)+CHOOSE(WEEKDAY(F108+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A108="","",IF(ISNUMBER(E108),MAX(DATE(2026,6,3),E108),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="D109" s="5">
-        <f>IF(A109="","",IF(G109="legacy",DATE(2026,5,15),IF(ISNUMBER(F109),(F109+5)+CHOOSE(WEEKDAY(F109+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A109="","",IF(ISNUMBER(E109),MAX(DATE(2026,6,3),E109),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -9430,7 +9430,7 @@
         </is>
       </c>
       <c r="D110" s="5">
-        <f>IF(A110="","",IF(G110="legacy",DATE(2026,5,15),IF(ISNUMBER(F110),(F110+5)+CHOOSE(WEEKDAY(F110+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A110="","",IF(ISNUMBER(E110),MAX(DATE(2026,6,3),E110),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -9512,7 +9512,7 @@
         </is>
       </c>
       <c r="D111" s="5">
-        <f>IF(A111="","",IF(G111="legacy",DATE(2026,5,15),IF(ISNUMBER(F111),(F111+5)+CHOOSE(WEEKDAY(F111+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A111="","",IF(ISNUMBER(E111),MAX(DATE(2026,6,3),E111),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="D112" s="5">
-        <f>IF(A112="","",IF(G112="legacy",DATE(2026,5,15),IF(ISNUMBER(F112),(F112+5)+CHOOSE(WEEKDAY(F112+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A112="","",IF(ISNUMBER(E112),MAX(DATE(2026,6,3),E112),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="D113" s="5">
-        <f>IF(A113="","",IF(G113="legacy",DATE(2026,5,15),IF(ISNUMBER(F113),(F113+5)+CHOOSE(WEEKDAY(F113+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A113="","",IF(ISNUMBER(E113),MAX(DATE(2026,6,3),E113),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -9758,7 +9758,7 @@
         </is>
       </c>
       <c r="D114" s="5">
-        <f>IF(A114="","",IF(G114="legacy",DATE(2026,5,15),IF(ISNUMBER(F114),(F114+5)+CHOOSE(WEEKDAY(F114+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A114="","",IF(ISNUMBER(E114),MAX(DATE(2026,6,3),E114),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -9840,7 +9840,7 @@
         </is>
       </c>
       <c r="D115" s="5">
-        <f>IF(A115="","",IF(G115="legacy",DATE(2026,5,15),IF(ISNUMBER(F115),(F115+5)+CHOOSE(WEEKDAY(F115+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A115="","",IF(ISNUMBER(E115),MAX(DATE(2026,6,3),E115),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="D116" s="5">
-        <f>IF(A116="","",IF(G116="legacy",DATE(2026,5,15),IF(ISNUMBER(F116),(F116+5)+CHOOSE(WEEKDAY(F116+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A116="","",IF(ISNUMBER(E116),MAX(DATE(2026,6,3),E116),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -10004,7 +10004,7 @@
         </is>
       </c>
       <c r="D117" s="5">
-        <f>IF(A117="","",IF(G117="legacy",DATE(2026,5,15),IF(ISNUMBER(F117),(F117+5)+CHOOSE(WEEKDAY(F117+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A117="","",IF(ISNUMBER(E117),MAX(DATE(2026,6,3),E117),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="D118" s="5">
-        <f>IF(A118="","",IF(G118="legacy",DATE(2026,5,15),IF(ISNUMBER(F118),(F118+5)+CHOOSE(WEEKDAY(F118+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A118="","",IF(ISNUMBER(E118),MAX(DATE(2026,6,3),E118),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -10168,7 +10168,7 @@
         </is>
       </c>
       <c r="D119" s="5">
-        <f>IF(A119="","",IF(G119="legacy",DATE(2026,5,15),IF(ISNUMBER(F119),(F119+5)+CHOOSE(WEEKDAY(F119+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A119="","",IF(ISNUMBER(E119),MAX(DATE(2026,6,3),E119),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -10250,7 +10250,7 @@
         </is>
       </c>
       <c r="D120" s="5">
-        <f>IF(A120="","",IF(G120="legacy",DATE(2026,5,15),IF(ISNUMBER(F120),(F120+5)+CHOOSE(WEEKDAY(F120+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A120="","",IF(ISNUMBER(E120),MAX(DATE(2026,6,3),E120),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -10332,7 +10332,7 @@
         </is>
       </c>
       <c r="D121" s="5">
-        <f>IF(A121="","",IF(G121="legacy",DATE(2026,5,15),IF(ISNUMBER(F121),(F121+5)+CHOOSE(WEEKDAY(F121+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A121="","",IF(ISNUMBER(E121),MAX(DATE(2026,6,3),E121),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="D122" s="5">
-        <f>IF(A122="","",IF(G122="legacy",DATE(2026,5,15),IF(ISNUMBER(F122),(F122+5)+CHOOSE(WEEKDAY(F122+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A122="","",IF(ISNUMBER(E122),MAX(DATE(2026,6,3),E122),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -10496,7 +10496,7 @@
         </is>
       </c>
       <c r="D123" s="5">
-        <f>IF(A123="","",IF(G123="legacy",DATE(2026,5,15),IF(ISNUMBER(F123),(F123+5)+CHOOSE(WEEKDAY(F123+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A123="","",IF(ISNUMBER(E123),MAX(DATE(2026,6,3),E123),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="D124" s="5">
-        <f>IF(A124="","",IF(G124="legacy",DATE(2026,5,15),IF(ISNUMBER(F124),(F124+5)+CHOOSE(WEEKDAY(F124+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A124="","",IF(ISNUMBER(E124),MAX(DATE(2026,6,3),E124),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="D125" s="5">
-        <f>IF(A125="","",IF(G125="legacy",DATE(2026,5,15),IF(ISNUMBER(F125),(F125+5)+CHOOSE(WEEKDAY(F125+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A125="","",IF(ISNUMBER(E125),MAX(DATE(2026,6,3),E125),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -10742,7 +10742,7 @@
         </is>
       </c>
       <c r="D126" s="5">
-        <f>IF(A126="","",IF(G126="legacy",DATE(2026,5,15),IF(ISNUMBER(F126),(F126+5)+CHOOSE(WEEKDAY(F126+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A126="","",IF(ISNUMBER(E126),MAX(DATE(2026,6,3),E126),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -10824,7 +10824,7 @@
         </is>
       </c>
       <c r="D127" s="5">
-        <f>IF(A127="","",IF(G127="legacy",DATE(2026,5,15),IF(ISNUMBER(F127),(F127+5)+CHOOSE(WEEKDAY(F127+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A127="","",IF(ISNUMBER(E127),MAX(DATE(2026,6,3),E127),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -10906,7 +10906,7 @@
         </is>
       </c>
       <c r="D128" s="5">
-        <f>IF(A128="","",IF(G128="legacy",DATE(2026,5,15),IF(ISNUMBER(F128),(F128+5)+CHOOSE(WEEKDAY(F128+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A128="","",IF(ISNUMBER(E128),MAX(DATE(2026,6,3),E128),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="D129" s="5">
-        <f>IF(A129="","",IF(G129="legacy",DATE(2026,5,15),IF(ISNUMBER(F129),(F129+5)+CHOOSE(WEEKDAY(F129+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A129="","",IF(ISNUMBER(E129),MAX(DATE(2026,6,3),E129),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="D130" s="5">
-        <f>IF(A130="","",IF(G130="legacy",DATE(2026,5,15),IF(ISNUMBER(F130),(F130+5)+CHOOSE(WEEKDAY(F130+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A130="","",IF(ISNUMBER(E130),MAX(DATE(2026,6,3),E130),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="D131" s="5">
-        <f>IF(A131="","",IF(G131="legacy",DATE(2026,5,15),IF(ISNUMBER(F131),(F131+5)+CHOOSE(WEEKDAY(F131+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A131="","",IF(ISNUMBER(E131),MAX(DATE(2026,6,3),E131),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="D132" s="5">
-        <f>IF(A132="","",IF(G132="legacy",DATE(2026,5,15),IF(ISNUMBER(F132),(F132+5)+CHOOSE(WEEKDAY(F132+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A132="","",IF(ISNUMBER(E132),MAX(DATE(2026,6,3),E132),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -11316,7 +11316,7 @@
         </is>
       </c>
       <c r="D133" s="5">
-        <f>IF(A133="","",IF(G133="legacy",DATE(2026,5,15),IF(ISNUMBER(F133),(F133+5)+CHOOSE(WEEKDAY(F133+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A133="","",IF(ISNUMBER(E133),MAX(DATE(2026,6,3),E133),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -11398,7 +11398,7 @@
         </is>
       </c>
       <c r="D134" s="5">
-        <f>IF(A134="","",IF(G134="legacy",DATE(2026,5,15),IF(ISNUMBER(F134),(F134+5)+CHOOSE(WEEKDAY(F134+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A134="","",IF(ISNUMBER(E134),MAX(DATE(2026,6,3),E134),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -11476,7 +11476,7 @@
         </is>
       </c>
       <c r="D135" s="5">
-        <f>IF(A135="","",IF(G135="legacy",DATE(2026,5,15),IF(ISNUMBER(F135),(F135+5)+CHOOSE(WEEKDAY(F135+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A135="","",IF(ISNUMBER(E135),MAX(DATE(2026,6,3),E135),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="D136" s="5">
-        <f>IF(A136="","",IF(G136="legacy",DATE(2026,5,15),IF(ISNUMBER(F136),(F136+5)+CHOOSE(WEEKDAY(F136+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A136="","",IF(ISNUMBER(E136),MAX(DATE(2026,6,3),E136),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -11640,7 +11640,7 @@
         </is>
       </c>
       <c r="D137" s="5">
-        <f>IF(A137="","",IF(G137="legacy",DATE(2026,5,15),IF(ISNUMBER(F137),(F137+5)+CHOOSE(WEEKDAY(F137+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A137="","",IF(ISNUMBER(E137),MAX(DATE(2026,6,3),E137),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -11722,7 +11722,7 @@
         </is>
       </c>
       <c r="D138" s="5">
-        <f>IF(A138="","",IF(G138="legacy",DATE(2026,5,15),IF(ISNUMBER(F138),(F138+5)+CHOOSE(WEEKDAY(F138+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A138="","",IF(ISNUMBER(E138),MAX(DATE(2026,6,3),E138),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="D139" s="5">
-        <f>IF(A139="","",IF(G139="legacy",DATE(2026,5,15),IF(ISNUMBER(F139),(F139+5)+CHOOSE(WEEKDAY(F139+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A139="","",IF(ISNUMBER(E139),MAX(DATE(2026,6,3),E139),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -11886,7 +11886,7 @@
         </is>
       </c>
       <c r="D140" s="5">
-        <f>IF(A140="","",IF(G140="legacy",DATE(2026,5,15),IF(ISNUMBER(F140),(F140+5)+CHOOSE(WEEKDAY(F140+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A140="","",IF(ISNUMBER(E140),MAX(DATE(2026,6,3),E140),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="D141" s="5">
-        <f>IF(A141="","",IF(G141="legacy",DATE(2026,5,15),IF(ISNUMBER(F141),(F141+5)+CHOOSE(WEEKDAY(F141+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A141="","",IF(ISNUMBER(E141),MAX(DATE(2026,6,3),E141),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -12050,7 +12050,7 @@
         </is>
       </c>
       <c r="D142" s="5">
-        <f>IF(A142="","",IF(G142="legacy",DATE(2026,5,15),IF(ISNUMBER(F142),(F142+5)+CHOOSE(WEEKDAY(F142+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A142="","",IF(ISNUMBER(E142),MAX(DATE(2026,6,3),E142),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -12132,7 +12132,7 @@
         </is>
       </c>
       <c r="D143" s="5">
-        <f>IF(A143="","",IF(G143="legacy",DATE(2026,5,15),IF(ISNUMBER(F143),(F143+5)+CHOOSE(WEEKDAY(F143+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A143="","",IF(ISNUMBER(E143),MAX(DATE(2026,6,3),E143),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -12214,7 +12214,7 @@
         </is>
       </c>
       <c r="D144" s="5">
-        <f>IF(A144="","",IF(G144="legacy",DATE(2026,5,15),IF(ISNUMBER(F144),(F144+5)+CHOOSE(WEEKDAY(F144+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A144="","",IF(ISNUMBER(E144),MAX(DATE(2026,6,3),E144),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -12296,7 +12296,7 @@
         </is>
       </c>
       <c r="D145" s="5">
-        <f>IF(A145="","",IF(G145="legacy",DATE(2026,5,15),IF(ISNUMBER(F145),(F145+5)+CHOOSE(WEEKDAY(F145+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A145="","",IF(ISNUMBER(E145),MAX(DATE(2026,6,3),E145),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="D146" s="5">
-        <f>IF(A146="","",IF(G146="legacy",DATE(2026,5,15),IF(ISNUMBER(F146),(F146+5)+CHOOSE(WEEKDAY(F146+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A146="","",IF(ISNUMBER(E146),MAX(DATE(2026,6,3),E146),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="D147" s="5">
-        <f>IF(A147="","",IF(G147="legacy",DATE(2026,5,15),IF(ISNUMBER(F147),(F147+5)+CHOOSE(WEEKDAY(F147+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A147="","",IF(ISNUMBER(E147),MAX(DATE(2026,6,3),E147),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -12542,7 +12542,7 @@
         </is>
       </c>
       <c r="D148" s="5">
-        <f>IF(A148="","",IF(G148="legacy",DATE(2026,5,15),IF(ISNUMBER(F148),(F148+5)+CHOOSE(WEEKDAY(F148+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A148="","",IF(ISNUMBER(E148),MAX(DATE(2026,6,3),E148),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -12624,7 +12624,7 @@
         </is>
       </c>
       <c r="D149" s="5">
-        <f>IF(A149="","",IF(G149="legacy",DATE(2026,5,15),IF(ISNUMBER(F149),(F149+5)+CHOOSE(WEEKDAY(F149+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A149="","",IF(ISNUMBER(E149),MAX(DATE(2026,6,3),E149),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -12706,7 +12706,7 @@
         </is>
       </c>
       <c r="D150" s="5">
-        <f>IF(A150="","",IF(G150="legacy",DATE(2026,5,15),IF(ISNUMBER(F150),(F150+5)+CHOOSE(WEEKDAY(F150+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A150="","",IF(ISNUMBER(E150),MAX(DATE(2026,6,3),E150),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -12788,7 +12788,7 @@
         </is>
       </c>
       <c r="D151" s="5">
-        <f>IF(A151="","",IF(G151="legacy",DATE(2026,5,15),IF(ISNUMBER(F151),(F151+5)+CHOOSE(WEEKDAY(F151+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A151="","",IF(ISNUMBER(E151),MAX(DATE(2026,6,3),E151),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -12870,7 +12870,7 @@
         </is>
       </c>
       <c r="D152" s="5">
-        <f>IF(A152="","",IF(G152="legacy",DATE(2026,5,15),IF(ISNUMBER(F152),(F152+5)+CHOOSE(WEEKDAY(F152+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A152="","",IF(ISNUMBER(E152),MAX(DATE(2026,6,3),E152),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="D153" s="5">
-        <f>IF(A153="","",IF(G153="legacy",DATE(2026,5,15),IF(ISNUMBER(F153),(F153+5)+CHOOSE(WEEKDAY(F153+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A153="","",IF(ISNUMBER(E153),MAX(DATE(2026,6,3),E153),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="D154" s="5">
-        <f>IF(A154="","",IF(G154="legacy",DATE(2026,5,15),IF(ISNUMBER(F154),(F154+5)+CHOOSE(WEEKDAY(F154+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A154="","",IF(ISNUMBER(E154),MAX(DATE(2026,6,3),E154),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="D155" s="5">
-        <f>IF(A155="","",IF(G155="legacy",DATE(2026,5,15),IF(ISNUMBER(F155),(F155+5)+CHOOSE(WEEKDAY(F155+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A155="","",IF(ISNUMBER(E155),MAX(DATE(2026,6,3),E155),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="D156" s="5">
-        <f>IF(A156="","",IF(G156="legacy",DATE(2026,5,15),IF(ISNUMBER(F156),(F156+5)+CHOOSE(WEEKDAY(F156+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A156="","",IF(ISNUMBER(E156),MAX(DATE(2026,6,3),E156),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="D157" s="5">
-        <f>IF(A157="","",IF(G157="legacy",DATE(2026,5,15),IF(ISNUMBER(F157),(F157+5)+CHOOSE(WEEKDAY(F157+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A157="","",IF(ISNUMBER(E157),MAX(DATE(2026,6,3),E157),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="D158" s="5">
-        <f>IF(A158="","",IF(G158="legacy",DATE(2026,5,15),IF(ISNUMBER(F158),(F158+5)+CHOOSE(WEEKDAY(F158+5,2),0,0,0,0,0,2,1),"")))</f>
+        <f>IF(A158="","",IF(ISNUMBER(E158),MAX(DATE(2026,6,3),E158),DATE(2026,6,3)))</f>
         <v/>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -13595,11 +13595,11 @@
         </is>
       </c>
       <c r="D2" s="5">
-        <f>IF(A2="","",MAX(E2,IF(ISNUMBER(I2),I2,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S2,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S2,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S2,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A2="","",MAX(E2,IF(ISNUMBER(I2),I2,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S2,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S2,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E2" s="5">
-        <f>IF(ISNUMBER(F2),IF(AND(J2="legacy",F2&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F2+7)+CHOOSE(WEEKDAY(F2+7,2),0,0,0,0,0,2,1))),IF(J2="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F2),MAX(DATE(2026,6,6),F2+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F2" s="5" t="n">
@@ -13689,11 +13689,11 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <f>IF(A3="","",MAX(E3,IF(ISNUMBER(I3),I3,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S3,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S3,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S3,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A3="","",MAX(E3,IF(ISNUMBER(I3),I3,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S3,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S3,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E3" s="5">
-        <f>IF(ISNUMBER(F3),IF(AND(J3="legacy",F3&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F3+7)+CHOOSE(WEEKDAY(F3+7,2),0,0,0,0,0,2,1))),IF(J3="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F3),MAX(DATE(2026,6,6),F3+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F3" s="5" t="n">
@@ -13783,11 +13783,11 @@
         </is>
       </c>
       <c r="D4" s="5">
-        <f>IF(A4="","",MAX(E4,IF(ISNUMBER(I4),I4,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S4,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S4,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S4,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A4="","",MAX(E4,IF(ISNUMBER(I4),I4,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S4,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S4,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>IF(ISNUMBER(F4),IF(AND(J4="legacy",F4&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F4+7)+CHOOSE(WEEKDAY(F4+7,2),0,0,0,0,0,2,1))),IF(J4="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F4),MAX(DATE(2026,6,6),F4+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F4" s="5" t="n">
@@ -13877,11 +13877,11 @@
         </is>
       </c>
       <c r="D5" s="5">
-        <f>IF(A5="","",MAX(E5,IF(ISNUMBER(I5),I5,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S5,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S5,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S5,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A5="","",MAX(E5,IF(ISNUMBER(I5),I5,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S5,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S5,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>IF(ISNUMBER(F5),IF(AND(J5="legacy",F5&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F5+7)+CHOOSE(WEEKDAY(F5+7,2),0,0,0,0,0,2,1))),IF(J5="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F5),MAX(DATE(2026,6,6),F5+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -13973,11 +13973,11 @@
         </is>
       </c>
       <c r="D6" s="5">
-        <f>IF(A6="","",MAX(E6,IF(ISNUMBER(I6),I6,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S6,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S6,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S6,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A6="","",MAX(E6,IF(ISNUMBER(I6),I6,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S6,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S6,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>IF(ISNUMBER(F6),IF(AND(J6="legacy",F6&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F6+7)+CHOOSE(WEEKDAY(F6+7,2),0,0,0,0,0,2,1))),IF(J6="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F6),MAX(DATE(2026,6,6),F6+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -14069,11 +14069,11 @@
         </is>
       </c>
       <c r="D7" s="5">
-        <f>IF(A7="","",MAX(E7,IF(ISNUMBER(I7),I7,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S7,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S7,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S7,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A7="","",MAX(E7,IF(ISNUMBER(I7),I7,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S7,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S7,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>IF(ISNUMBER(F7),IF(AND(J7="legacy",F7&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F7+7)+CHOOSE(WEEKDAY(F7+7,2),0,0,0,0,0,2,1))),IF(J7="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F7),MAX(DATE(2026,6,6),F7+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -14165,11 +14165,11 @@
         </is>
       </c>
       <c r="D8" s="5">
-        <f>IF(A8="","",MAX(E8,IF(ISNUMBER(I8),I8,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S8,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S8,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S8,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A8="","",MAX(E8,IF(ISNUMBER(I8),I8,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S8,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S8,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>IF(ISNUMBER(F8),IF(AND(J8="legacy",F8&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F8+7)+CHOOSE(WEEKDAY(F8+7,2),0,0,0,0,0,2,1))),IF(J8="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F8),MAX(DATE(2026,6,6),F8+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F8" s="5" t="n">
@@ -14259,11 +14259,11 @@
         </is>
       </c>
       <c r="D9" s="5">
-        <f>IF(A9="","",MAX(E9,IF(ISNUMBER(I9),I9,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S9,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S9,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S9,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A9="","",MAX(E9,IF(ISNUMBER(I9),I9,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S9,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S9,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>IF(ISNUMBER(F9),IF(AND(J9="legacy",F9&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F9+7)+CHOOSE(WEEKDAY(F9+7,2),0,0,0,0,0,2,1))),IF(J9="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F9),MAX(DATE(2026,6,6),F9+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F9" s="5" t="n">
@@ -14353,11 +14353,11 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <f>IF(A10="","",MAX(E10,IF(ISNUMBER(I10),I10,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S10,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S10,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S10,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A10="","",MAX(E10,IF(ISNUMBER(I10),I10,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S10,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S10,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>IF(ISNUMBER(F10),IF(AND(J10="legacy",F10&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F10+7)+CHOOSE(WEEKDAY(F10+7,2),0,0,0,0,0,2,1))),IF(J10="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F10),MAX(DATE(2026,6,6),F10+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F10" s="5" t="n">
@@ -14447,11 +14447,11 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <f>IF(A11="","",MAX(E11,IF(ISNUMBER(I11),I11,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S11,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S11,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S11,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A11="","",MAX(E11,IF(ISNUMBER(I11),I11,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S11,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S11,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E11" s="5">
-        <f>IF(ISNUMBER(F11),IF(AND(J11="legacy",F11&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F11+7)+CHOOSE(WEEKDAY(F11+7,2),0,0,0,0,0,2,1))),IF(J11="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F11),MAX(DATE(2026,6,6),F11+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F11" s="5" t="n">
@@ -14541,11 +14541,11 @@
         </is>
       </c>
       <c r="D12" s="5">
-        <f>IF(A12="","",MAX(E12,IF(ISNUMBER(I12),I12,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S12,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S12,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S12,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A12="","",MAX(E12,IF(ISNUMBER(I12),I12,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S12,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S12,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>IF(ISNUMBER(F12),IF(AND(J12="legacy",F12&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F12+7)+CHOOSE(WEEKDAY(F12+7,2),0,0,0,0,0,2,1))),IF(J12="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F12),MAX(DATE(2026,6,6),F12+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F12" s="5" t="n">
@@ -14635,11 +14635,11 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <f>IF(A13="","",MAX(E13,IF(ISNUMBER(I13),I13,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S13,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S13,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S13,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A13="","",MAX(E13,IF(ISNUMBER(I13),I13,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S13,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S13,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>IF(ISNUMBER(F13),IF(AND(J13="legacy",F13&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F13+7)+CHOOSE(WEEKDAY(F13+7,2),0,0,0,0,0,2,1))),IF(J13="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F13),MAX(DATE(2026,6,6),F13+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F13" s="5" t="n">
@@ -14729,11 +14729,11 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <f>IF(A14="","",MAX(E14,IF(ISNUMBER(I14),I14,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S14,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S14,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S14,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A14="","",MAX(E14,IF(ISNUMBER(I14),I14,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S14,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S14,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>IF(ISNUMBER(F14),IF(AND(J14="legacy",F14&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F14+7)+CHOOSE(WEEKDAY(F14+7,2),0,0,0,0,0,2,1))),IF(J14="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F14),MAX(DATE(2026,6,6),F14+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F14" s="5" t="n">
@@ -14823,11 +14823,11 @@
         </is>
       </c>
       <c r="D15" s="5">
-        <f>IF(A15="","",MAX(E15,IF(ISNUMBER(I15),I15,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S15,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S15,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S15,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A15="","",MAX(E15,IF(ISNUMBER(I15),I15,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S15,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S15,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>IF(ISNUMBER(F15),IF(AND(J15="legacy",F15&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F15+7)+CHOOSE(WEEKDAY(F15+7,2),0,0,0,0,0,2,1))),IF(J15="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F15),MAX(DATE(2026,6,6),F15+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F15" s="5" t="n">
@@ -14917,11 +14917,11 @@
         </is>
       </c>
       <c r="D16" s="5">
-        <f>IF(A16="","",MAX(E16,IF(ISNUMBER(I16),I16,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S16,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S16,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S16,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A16="","",MAX(E16,IF(ISNUMBER(I16),I16,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S16,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S16,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>IF(ISNUMBER(F16),IF(AND(J16="legacy",F16&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F16+7)+CHOOSE(WEEKDAY(F16+7,2),0,0,0,0,0,2,1))),IF(J16="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F16),MAX(DATE(2026,6,6),F16+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F16" s="5" t="n">
@@ -15011,11 +15011,11 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <f>IF(A17="","",MAX(E17,IF(ISNUMBER(I17),I17,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S17,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S17,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S17,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A17="","",MAX(E17,IF(ISNUMBER(I17),I17,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S17,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S17,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>IF(ISNUMBER(F17),IF(AND(J17="legacy",F17&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F17+7)+CHOOSE(WEEKDAY(F17+7,2),0,0,0,0,0,2,1))),IF(J17="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F17),MAX(DATE(2026,6,6),F17+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F17" s="5" t="n">
@@ -15105,11 +15105,11 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <f>IF(A18="","",MAX(E18,IF(ISNUMBER(I18),I18,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S18,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S18,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S18,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A18="","",MAX(E18,IF(ISNUMBER(I18),I18,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S18,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S18,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>IF(ISNUMBER(F18),IF(AND(J18="legacy",F18&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F18+7)+CHOOSE(WEEKDAY(F18+7,2),0,0,0,0,0,2,1))),IF(J18="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F18),MAX(DATE(2026,6,6),F18+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F18" s="5" t="n">
@@ -15199,11 +15199,11 @@
         </is>
       </c>
       <c r="D19" s="5">
-        <f>IF(A19="","",MAX(E19,IF(ISNUMBER(I19),I19,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S19,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S19,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S19,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A19="","",MAX(E19,IF(ISNUMBER(I19),I19,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S19,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S19,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>IF(ISNUMBER(F19),IF(AND(J19="legacy",F19&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F19+7)+CHOOSE(WEEKDAY(F19+7,2),0,0,0,0,0,2,1))),IF(J19="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F19),MAX(DATE(2026,6,6),F19+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F19" s="5" t="n">
@@ -15293,11 +15293,11 @@
         </is>
       </c>
       <c r="D20" s="5">
-        <f>IF(A20="","",MAX(E20,IF(ISNUMBER(I20),I20,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S20,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S20,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S20,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A20="","",MAX(E20,IF(ISNUMBER(I20),I20,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S20,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S20,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>IF(ISNUMBER(F20),IF(AND(J20="legacy",F20&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F20+7)+CHOOSE(WEEKDAY(F20+7,2),0,0,0,0,0,2,1))),IF(J20="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F20),MAX(DATE(2026,6,6),F20+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F20" s="5" t="n">
@@ -15387,11 +15387,11 @@
         </is>
       </c>
       <c r="D21" s="5">
-        <f>IF(A21="","",MAX(E21,IF(ISNUMBER(I21),I21,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S21,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S21,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S21,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A21="","",MAX(E21,IF(ISNUMBER(I21),I21,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S21,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S21,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>IF(ISNUMBER(F21),IF(AND(J21="legacy",F21&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F21+7)+CHOOSE(WEEKDAY(F21+7,2),0,0,0,0,0,2,1))),IF(J21="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F21),MAX(DATE(2026,6,6),F21+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F21" s="5" t="n">
@@ -15481,11 +15481,11 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <f>IF(A22="","",MAX(E22,IF(ISNUMBER(I22),I22,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S22,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S22,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S22,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A22="","",MAX(E22,IF(ISNUMBER(I22),I22,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S22,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S22,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>IF(ISNUMBER(F22),IF(AND(J22="legacy",F22&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F22+7)+CHOOSE(WEEKDAY(F22+7,2),0,0,0,0,0,2,1))),IF(J22="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F22),MAX(DATE(2026,6,6),F22+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -15577,11 +15577,11 @@
         </is>
       </c>
       <c r="D23" s="5">
-        <f>IF(A23="","",MAX(E23,IF(ISNUMBER(I23),I23,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S23,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S23,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S23,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A23="","",MAX(E23,IF(ISNUMBER(I23),I23,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S23,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S23,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>IF(ISNUMBER(F23),IF(AND(J23="legacy",F23&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F23+7)+CHOOSE(WEEKDAY(F23+7,2),0,0,0,0,0,2,1))),IF(J23="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F23),MAX(DATE(2026,6,6),F23+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F23" s="5" t="n">
@@ -15671,11 +15671,11 @@
         </is>
       </c>
       <c r="D24" s="5">
-        <f>IF(A24="","",MAX(E24,IF(ISNUMBER(I24),I24,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S24,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S24,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S24,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A24="","",MAX(E24,IF(ISNUMBER(I24),I24,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S24,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S24,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>IF(ISNUMBER(F24),IF(AND(J24="legacy",F24&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F24+7)+CHOOSE(WEEKDAY(F24+7,2),0,0,0,0,0,2,1))),IF(J24="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F24),MAX(DATE(2026,6,6),F24+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F24" s="5" t="n">
@@ -15765,11 +15765,11 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <f>IF(A25="","",MAX(E25,IF(ISNUMBER(I25),I25,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S25,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S25,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S25,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A25="","",MAX(E25,IF(ISNUMBER(I25),I25,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S25,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S25,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>IF(ISNUMBER(F25),IF(AND(J25="legacy",F25&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F25+7)+CHOOSE(WEEKDAY(F25+7,2),0,0,0,0,0,2,1))),IF(J25="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F25),MAX(DATE(2026,6,6),F25+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F25" s="5" t="n">
@@ -15859,11 +15859,11 @@
         </is>
       </c>
       <c r="D26" s="5">
-        <f>IF(A26="","",MAX(E26,IF(ISNUMBER(I26),I26,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S26,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S26,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S26,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A26="","",MAX(E26,IF(ISNUMBER(I26),I26,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S26,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S26,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>IF(ISNUMBER(F26),IF(AND(J26="legacy",F26&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F26+7)+CHOOSE(WEEKDAY(F26+7,2),0,0,0,0,0,2,1))),IF(J26="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F26),MAX(DATE(2026,6,6),F26+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F26" s="5" t="n">
@@ -15953,11 +15953,11 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <f>IF(A27="","",MAX(E27,IF(ISNUMBER(I27),I27,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S27,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S27,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S27,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A27="","",MAX(E27,IF(ISNUMBER(I27),I27,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S27,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S27,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>IF(ISNUMBER(F27),IF(AND(J27="legacy",F27&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F27+7)+CHOOSE(WEEKDAY(F27+7,2),0,0,0,0,0,2,1))),IF(J27="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F27),MAX(DATE(2026,6,6),F27+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F27" s="5" t="n">
@@ -16047,11 +16047,11 @@
         </is>
       </c>
       <c r="D28" s="5">
-        <f>IF(A28="","",MAX(E28,IF(ISNUMBER(I28),I28,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S28,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S28,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S28,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A28="","",MAX(E28,IF(ISNUMBER(I28),I28,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S28,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S28,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>IF(ISNUMBER(F28),IF(AND(J28="legacy",F28&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F28+7)+CHOOSE(WEEKDAY(F28+7,2),0,0,0,0,0,2,1))),IF(J28="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F28),MAX(DATE(2026,6,6),F28+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F28" s="5" t="n">
@@ -16141,11 +16141,11 @@
         </is>
       </c>
       <c r="D29" s="5">
-        <f>IF(A29="","",MAX(E29,IF(ISNUMBER(I29),I29,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S29,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S29,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S29,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A29="","",MAX(E29,IF(ISNUMBER(I29),I29,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S29,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S29,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>IF(ISNUMBER(F29),IF(AND(J29="legacy",F29&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F29+7)+CHOOSE(WEEKDAY(F29+7,2),0,0,0,0,0,2,1))),IF(J29="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F29),MAX(DATE(2026,6,6),F29+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F29" s="5" t="n">
@@ -16235,11 +16235,11 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <f>IF(A30="","",MAX(E30,IF(ISNUMBER(I30),I30,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S30,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S30,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S30,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A30="","",MAX(E30,IF(ISNUMBER(I30),I30,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S30,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S30,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>IF(ISNUMBER(F30),IF(AND(J30="legacy",F30&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F30+7)+CHOOSE(WEEKDAY(F30+7,2),0,0,0,0,0,2,1))),IF(J30="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F30),MAX(DATE(2026,6,6),F30+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F30" s="5" t="n">
@@ -16329,11 +16329,11 @@
         </is>
       </c>
       <c r="D31" s="5">
-        <f>IF(A31="","",MAX(E31,IF(ISNUMBER(I31),I31,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S31,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S31,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S31,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A31="","",MAX(E31,IF(ISNUMBER(I31),I31,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S31,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S31,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>IF(ISNUMBER(F31),IF(AND(J31="legacy",F31&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F31+7)+CHOOSE(WEEKDAY(F31+7,2),0,0,0,0,0,2,1))),IF(J31="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F31),MAX(DATE(2026,6,6),F31+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F31" s="5" t="n">
@@ -16423,11 +16423,11 @@
         </is>
       </c>
       <c r="D32" s="5">
-        <f>IF(A32="","",MAX(E32,IF(ISNUMBER(I32),I32,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S32,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S32,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S32,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A32="","",MAX(E32,IF(ISNUMBER(I32),I32,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S32,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S32,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>IF(ISNUMBER(F32),IF(AND(J32="legacy",F32&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F32+7)+CHOOSE(WEEKDAY(F32+7,2),0,0,0,0,0,2,1))),IF(J32="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F32),MAX(DATE(2026,6,6),F32+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F32" s="5" t="n">
@@ -16517,11 +16517,11 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <f>IF(A33="","",MAX(E33,IF(ISNUMBER(I33),I33,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S33,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S33,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S33,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A33="","",MAX(E33,IF(ISNUMBER(I33),I33,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S33,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S33,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E33" s="5">
-        <f>IF(ISNUMBER(F33),IF(AND(J33="legacy",F33&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F33+7)+CHOOSE(WEEKDAY(F33+7,2),0,0,0,0,0,2,1))),IF(J33="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F33),MAX(DATE(2026,6,6),F33+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F33" s="5" t="n">
@@ -16611,11 +16611,11 @@
         </is>
       </c>
       <c r="D34" s="5">
-        <f>IF(A34="","",MAX(E34,IF(ISNUMBER(I34),I34,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S34,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S34,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S34,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A34="","",MAX(E34,IF(ISNUMBER(I34),I34,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S34,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S34,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E34" s="5">
-        <f>IF(ISNUMBER(F34),IF(AND(J34="legacy",F34&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F34+7)+CHOOSE(WEEKDAY(F34+7,2),0,0,0,0,0,2,1))),IF(J34="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F34),MAX(DATE(2026,6,6),F34+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F34" s="5" t="n">
@@ -16705,11 +16705,11 @@
         </is>
       </c>
       <c r="D35" s="5">
-        <f>IF(A35="","",MAX(E35,IF(ISNUMBER(I35),I35,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S35,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S35,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S35,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A35="","",MAX(E35,IF(ISNUMBER(I35),I35,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S35,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S35,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E35" s="5">
-        <f>IF(ISNUMBER(F35),IF(AND(J35="legacy",F35&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F35+7)+CHOOSE(WEEKDAY(F35+7,2),0,0,0,0,0,2,1))),IF(J35="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F35),MAX(DATE(2026,6,6),F35+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F35" s="5" t="n">
@@ -16799,11 +16799,11 @@
         </is>
       </c>
       <c r="D36" s="5">
-        <f>IF(A36="","",MAX(E36,IF(ISNUMBER(I36),I36,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S36,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S36,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S36,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A36="","",MAX(E36,IF(ISNUMBER(I36),I36,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S36,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S36,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E36" s="5">
-        <f>IF(ISNUMBER(F36),IF(AND(J36="legacy",F36&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F36+7)+CHOOSE(WEEKDAY(F36+7,2),0,0,0,0,0,2,1))),IF(J36="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F36),MAX(DATE(2026,6,6),F36+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F36" s="5" t="n">
@@ -16893,11 +16893,11 @@
         </is>
       </c>
       <c r="D37" s="5">
-        <f>IF(A37="","",MAX(E37,IF(ISNUMBER(I37),I37,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S37,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S37,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S37,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A37="","",MAX(E37,IF(ISNUMBER(I37),I37,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S37,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S37,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E37" s="5">
-        <f>IF(ISNUMBER(F37),IF(AND(J37="legacy",F37&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F37+7)+CHOOSE(WEEKDAY(F37+7,2),0,0,0,0,0,2,1))),IF(J37="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F37),MAX(DATE(2026,6,6),F37+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F37" s="5" t="n">
@@ -16987,11 +16987,11 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <f>IF(A38="","",MAX(E38,IF(ISNUMBER(I38),I38,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S38,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S38,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S38,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A38="","",MAX(E38,IF(ISNUMBER(I38),I38,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S38,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S38,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E38" s="5">
-        <f>IF(ISNUMBER(F38),IF(AND(J38="legacy",F38&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F38+7)+CHOOSE(WEEKDAY(F38+7,2),0,0,0,0,0,2,1))),IF(J38="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F38),MAX(DATE(2026,6,6),F38+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F38" s="5" t="n">
@@ -17081,11 +17081,11 @@
         </is>
       </c>
       <c r="D39" s="5">
-        <f>IF(A39="","",MAX(E39,IF(ISNUMBER(I39),I39,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S39,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S39,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S39,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A39="","",MAX(E39,IF(ISNUMBER(I39),I39,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S39,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S39,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E39" s="5">
-        <f>IF(ISNUMBER(F39),IF(AND(J39="legacy",F39&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F39+7)+CHOOSE(WEEKDAY(F39+7,2),0,0,0,0,0,2,1))),IF(J39="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F39),MAX(DATE(2026,6,6),F39+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F39" s="5" t="n">
@@ -17175,11 +17175,11 @@
         </is>
       </c>
       <c r="D40" s="5">
-        <f>IF(A40="","",MAX(E40,IF(ISNUMBER(I40),I40,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S40,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S40,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S40,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A40="","",MAX(E40,IF(ISNUMBER(I40),I40,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S40,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S40,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E40" s="5">
-        <f>IF(ISNUMBER(F40),IF(AND(J40="legacy",F40&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F40+7)+CHOOSE(WEEKDAY(F40+7,2),0,0,0,0,0,2,1))),IF(J40="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F40),MAX(DATE(2026,6,6),F40+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F40" s="5" t="n">
@@ -17269,11 +17269,11 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <f>IF(A41="","",MAX(E41,IF(ISNUMBER(I41),I41,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S41,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S41,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S41,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A41="","",MAX(E41,IF(ISNUMBER(I41),I41,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S41,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S41,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E41" s="5">
-        <f>IF(ISNUMBER(F41),IF(AND(J41="legacy",F41&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F41+7)+CHOOSE(WEEKDAY(F41+7,2),0,0,0,0,0,2,1))),IF(J41="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F41),MAX(DATE(2026,6,6),F41+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F41" s="5" t="n">
@@ -17363,11 +17363,11 @@
         </is>
       </c>
       <c r="D42" s="5">
-        <f>IF(A42="","",MAX(E42,IF(ISNUMBER(I42),I42,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S42,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S42,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S42,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A42="","",MAX(E42,IF(ISNUMBER(I42),I42,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S42,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S42,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E42" s="5">
-        <f>IF(ISNUMBER(F42),IF(AND(J42="legacy",F42&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F42+7)+CHOOSE(WEEKDAY(F42+7,2),0,0,0,0,0,2,1))),IF(J42="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F42),MAX(DATE(2026,6,6),F42+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F42" s="5" t="n">
@@ -17457,11 +17457,11 @@
         </is>
       </c>
       <c r="D43" s="5">
-        <f>IF(A43="","",MAX(E43,IF(ISNUMBER(I43),I43,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S43,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S43,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S43,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A43="","",MAX(E43,IF(ISNUMBER(I43),I43,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S43,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S43,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E43" s="5">
-        <f>IF(ISNUMBER(F43),IF(AND(J43="legacy",F43&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F43+7)+CHOOSE(WEEKDAY(F43+7,2),0,0,0,0,0,2,1))),IF(J43="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F43),MAX(DATE(2026,6,6),F43+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F43" s="5" t="n">
@@ -17551,11 +17551,11 @@
         </is>
       </c>
       <c r="D44" s="5">
-        <f>IF(A44="","",MAX(E44,IF(ISNUMBER(I44),I44,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S44,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S44,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S44,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A44="","",MAX(E44,IF(ISNUMBER(I44),I44,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S44,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S44,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E44" s="5">
-        <f>IF(ISNUMBER(F44),IF(AND(J44="legacy",F44&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F44+7)+CHOOSE(WEEKDAY(F44+7,2),0,0,0,0,0,2,1))),IF(J44="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F44),MAX(DATE(2026,6,6),F44+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F44" s="5" t="n">
@@ -17645,11 +17645,11 @@
         </is>
       </c>
       <c r="D45" s="5">
-        <f>IF(A45="","",MAX(E45,IF(ISNUMBER(I45),I45,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S45,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S45,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S45,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A45="","",MAX(E45,IF(ISNUMBER(I45),I45,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S45,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S45,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E45" s="5">
-        <f>IF(ISNUMBER(F45),IF(AND(J45="legacy",F45&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F45+7)+CHOOSE(WEEKDAY(F45+7,2),0,0,0,0,0,2,1))),IF(J45="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F45),MAX(DATE(2026,6,6),F45+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F45" s="5" t="n">
@@ -17735,11 +17735,11 @@
         </is>
       </c>
       <c r="D46" s="5">
-        <f>IF(A46="","",MAX(E46,IF(ISNUMBER(I46),I46,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S46,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S46,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S46,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A46="","",MAX(E46,IF(ISNUMBER(I46),I46,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S46,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S46,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E46" s="5">
-        <f>IF(ISNUMBER(F46),IF(AND(J46="legacy",F46&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F46+7)+CHOOSE(WEEKDAY(F46+7,2),0,0,0,0,0,2,1))),IF(J46="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F46),MAX(DATE(2026,6,6),F46+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F46" s="5" t="n">
@@ -17829,11 +17829,11 @@
         </is>
       </c>
       <c r="D47" s="5">
-        <f>IF(A47="","",MAX(E47,IF(ISNUMBER(I47),I47,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S47,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S47,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S47,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A47="","",MAX(E47,IF(ISNUMBER(I47),I47,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S47,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S47,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E47" s="5">
-        <f>IF(ISNUMBER(F47),IF(AND(J47="legacy",F47&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F47+7)+CHOOSE(WEEKDAY(F47+7,2),0,0,0,0,0,2,1))),IF(J47="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F47),MAX(DATE(2026,6,6),F47+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -17925,11 +17925,11 @@
         </is>
       </c>
       <c r="D48" s="5">
-        <f>IF(A48="","",MAX(E48,IF(ISNUMBER(I48),I48,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S48,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S48,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S48,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A48="","",MAX(E48,IF(ISNUMBER(I48),I48,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S48,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S48,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E48" s="5">
-        <f>IF(ISNUMBER(F48),IF(AND(J48="legacy",F48&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F48+7)+CHOOSE(WEEKDAY(F48+7,2),0,0,0,0,0,2,1))),IF(J48="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F48),MAX(DATE(2026,6,6),F48+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F48" s="5" t="n">
@@ -18019,11 +18019,11 @@
         </is>
       </c>
       <c r="D49" s="5">
-        <f>IF(A49="","",MAX(E49,IF(ISNUMBER(I49),I49,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S49,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S49,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S49,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A49="","",MAX(E49,IF(ISNUMBER(I49),I49,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S49,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S49,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E49" s="5">
-        <f>IF(ISNUMBER(F49),IF(AND(J49="legacy",F49&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F49+7)+CHOOSE(WEEKDAY(F49+7,2),0,0,0,0,0,2,1))),IF(J49="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F49),MAX(DATE(2026,6,6),F49+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F49" s="5" t="n">
@@ -18113,11 +18113,11 @@
         </is>
       </c>
       <c r="D50" s="5">
-        <f>IF(A50="","",MAX(E50,IF(ISNUMBER(I50),I50,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S50,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S50,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S50,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A50="","",MAX(E50,IF(ISNUMBER(I50),I50,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S50,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S50,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E50" s="5">
-        <f>IF(ISNUMBER(F50),IF(AND(J50="legacy",F50&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F50+7)+CHOOSE(WEEKDAY(F50+7,2),0,0,0,0,0,2,1))),IF(J50="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F50),MAX(DATE(2026,6,6),F50+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F50" s="5" t="n">
@@ -18207,11 +18207,11 @@
         </is>
       </c>
       <c r="D51" s="5">
-        <f>IF(A51="","",MAX(E51,IF(ISNUMBER(I51),I51,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S51,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S51,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S51,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A51="","",MAX(E51,IF(ISNUMBER(I51),I51,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S51,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S51,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E51" s="5">
-        <f>IF(ISNUMBER(F51),IF(AND(J51="legacy",F51&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F51+7)+CHOOSE(WEEKDAY(F51+7,2),0,0,0,0,0,2,1))),IF(J51="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F51),MAX(DATE(2026,6,6),F51+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F51" s="5" t="n">
@@ -18301,11 +18301,11 @@
         </is>
       </c>
       <c r="D52" s="5">
-        <f>IF(A52="","",MAX(E52,IF(ISNUMBER(I52),I52,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S52,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S52,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S52,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A52="","",MAX(E52,IF(ISNUMBER(I52),I52,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S52,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S52,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E52" s="5">
-        <f>IF(ISNUMBER(F52),IF(AND(J52="legacy",F52&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F52+7)+CHOOSE(WEEKDAY(F52+7,2),0,0,0,0,0,2,1))),IF(J52="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F52),MAX(DATE(2026,6,6),F52+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F52" s="5" t="n">
@@ -18395,11 +18395,11 @@
         </is>
       </c>
       <c r="D53" s="5">
-        <f>IF(A53="","",MAX(E53,IF(ISNUMBER(I53),I53,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S53,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S53,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S53,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A53="","",MAX(E53,IF(ISNUMBER(I53),I53,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S53,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S53,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E53" s="5">
-        <f>IF(ISNUMBER(F53),IF(AND(J53="legacy",F53&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F53+7)+CHOOSE(WEEKDAY(F53+7,2),0,0,0,0,0,2,1))),IF(J53="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F53),MAX(DATE(2026,6,6),F53+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F53" s="5" t="n">
@@ -18489,11 +18489,11 @@
         </is>
       </c>
       <c r="D54" s="5">
-        <f>IF(A54="","",MAX(E54,IF(ISNUMBER(I54),I54,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S54,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S54,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S54,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A54="","",MAX(E54,IF(ISNUMBER(I54),I54,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S54,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S54,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E54" s="5">
-        <f>IF(ISNUMBER(F54),IF(AND(J54="legacy",F54&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F54+7)+CHOOSE(WEEKDAY(F54+7,2),0,0,0,0,0,2,1))),IF(J54="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F54),MAX(DATE(2026,6,6),F54+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F54" s="5" t="n">
@@ -18583,11 +18583,11 @@
         </is>
       </c>
       <c r="D55" s="5">
-        <f>IF(A55="","",MAX(E55,IF(ISNUMBER(I55),I55,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S55,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S55,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S55,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A55="","",MAX(E55,IF(ISNUMBER(I55),I55,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S55,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S55,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E55" s="5">
-        <f>IF(ISNUMBER(F55),IF(AND(J55="legacy",F55&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F55+7)+CHOOSE(WEEKDAY(F55+7,2),0,0,0,0,0,2,1))),IF(J55="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F55),MAX(DATE(2026,6,6),F55+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F55" s="5" t="n">
@@ -18677,11 +18677,11 @@
         </is>
       </c>
       <c r="D56" s="5">
-        <f>IF(A56="","",MAX(E56,IF(ISNUMBER(I56),I56,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S56,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S56,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S56,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A56="","",MAX(E56,IF(ISNUMBER(I56),I56,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S56,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S56,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E56" s="5">
-        <f>IF(ISNUMBER(F56),IF(AND(J56="legacy",F56&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F56+7)+CHOOSE(WEEKDAY(F56+7,2),0,0,0,0,0,2,1))),IF(J56="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F56),MAX(DATE(2026,6,6),F56+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F56" s="5" t="n">
@@ -18771,11 +18771,11 @@
         </is>
       </c>
       <c r="D57" s="5">
-        <f>IF(A57="","",MAX(E57,IF(ISNUMBER(I57),I57,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S57,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S57,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S57,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A57="","",MAX(E57,IF(ISNUMBER(I57),I57,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S57,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S57,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E57" s="5">
-        <f>IF(ISNUMBER(F57),IF(AND(J57="legacy",F57&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F57+7)+CHOOSE(WEEKDAY(F57+7,2),0,0,0,0,0,2,1))),IF(J57="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F57),MAX(DATE(2026,6,6),F57+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F57" s="5" t="n">
@@ -18865,11 +18865,11 @@
         </is>
       </c>
       <c r="D58" s="5">
-        <f>IF(A58="","",MAX(E58,IF(ISNUMBER(I58),I58,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S58,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S58,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S58,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A58="","",MAX(E58,IF(ISNUMBER(I58),I58,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S58,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S58,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E58" s="5">
-        <f>IF(ISNUMBER(F58),IF(AND(J58="legacy",F58&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F58+7)+CHOOSE(WEEKDAY(F58+7,2),0,0,0,0,0,2,1))),IF(J58="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F58),MAX(DATE(2026,6,6),F58+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F58" s="5" t="n">
@@ -18959,11 +18959,11 @@
         </is>
       </c>
       <c r="D59" s="5">
-        <f>IF(A59="","",MAX(E59,IF(ISNUMBER(I59),I59,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S59,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S59,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S59,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A59="","",MAX(E59,IF(ISNUMBER(I59),I59,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S59,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S59,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E59" s="5">
-        <f>IF(ISNUMBER(F59),IF(AND(J59="legacy",F59&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F59+7)+CHOOSE(WEEKDAY(F59+7,2),0,0,0,0,0,2,1))),IF(J59="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F59),MAX(DATE(2026,6,6),F59+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F59" s="5" t="n">
@@ -19053,11 +19053,11 @@
         </is>
       </c>
       <c r="D60" s="5">
-        <f>IF(A60="","",MAX(E60,IF(ISNUMBER(I60),I60,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S60,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S60,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S60,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A60="","",MAX(E60,IF(ISNUMBER(I60),I60,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S60,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S60,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E60" s="5">
-        <f>IF(ISNUMBER(F60),IF(AND(J60="legacy",F60&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F60+7)+CHOOSE(WEEKDAY(F60+7,2),0,0,0,0,0,2,1))),IF(J60="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F60),MAX(DATE(2026,6,6),F60+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F60" s="5" t="n">
@@ -19147,11 +19147,11 @@
         </is>
       </c>
       <c r="D61" s="5">
-        <f>IF(A61="","",MAX(E61,IF(ISNUMBER(I61),I61,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S61,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S61,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S61,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A61="","",MAX(E61,IF(ISNUMBER(I61),I61,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S61,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S61,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E61" s="5">
-        <f>IF(ISNUMBER(F61),IF(AND(J61="legacy",F61&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F61+7)+CHOOSE(WEEKDAY(F61+7,2),0,0,0,0,0,2,1))),IF(J61="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F61),MAX(DATE(2026,6,6),F61+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F61" s="5" t="n">
@@ -19241,11 +19241,11 @@
         </is>
       </c>
       <c r="D62" s="5">
-        <f>IF(A62="","",MAX(E62,IF(ISNUMBER(I62),I62,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S62,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S62,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S62,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A62="","",MAX(E62,IF(ISNUMBER(I62),I62,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S62,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S62,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E62" s="5">
-        <f>IF(ISNUMBER(F62),IF(AND(J62="legacy",F62&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F62+7)+CHOOSE(WEEKDAY(F62+7,2),0,0,0,0,0,2,1))),IF(J62="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F62),MAX(DATE(2026,6,6),F62+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F62" s="5" t="n">
@@ -19335,11 +19335,11 @@
         </is>
       </c>
       <c r="D63" s="5">
-        <f>IF(A63="","",MAX(E63,IF(ISNUMBER(I63),I63,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S63,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S63,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S63,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A63="","",MAX(E63,IF(ISNUMBER(I63),I63,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S63,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S63,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E63" s="5">
-        <f>IF(ISNUMBER(F63),IF(AND(J63="legacy",F63&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F63+7)+CHOOSE(WEEKDAY(F63+7,2),0,0,0,0,0,2,1))),IF(J63="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F63),MAX(DATE(2026,6,6),F63+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F63" s="5" t="n">
@@ -19429,11 +19429,11 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <f>IF(A64="","",MAX(E64,IF(ISNUMBER(I64),I64,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S64,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S64,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S64,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A64="","",MAX(E64,IF(ISNUMBER(I64),I64,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S64,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S64,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E64" s="5">
-        <f>IF(ISNUMBER(F64),IF(AND(J64="legacy",F64&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F64+7)+CHOOSE(WEEKDAY(F64+7,2),0,0,0,0,0,2,1))),IF(J64="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F64),MAX(DATE(2026,6,6),F64+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F64" s="5" t="n">
@@ -19523,11 +19523,11 @@
         </is>
       </c>
       <c r="D65" s="5">
-        <f>IF(A65="","",MAX(E65,IF(ISNUMBER(I65),I65,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S65,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S65,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S65,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A65="","",MAX(E65,IF(ISNUMBER(I65),I65,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S65,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S65,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E65" s="5">
-        <f>IF(ISNUMBER(F65),IF(AND(J65="legacy",F65&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F65+7)+CHOOSE(WEEKDAY(F65+7,2),0,0,0,0,0,2,1))),IF(J65="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F65),MAX(DATE(2026,6,6),F65+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F65" s="5" t="n">
@@ -19617,11 +19617,11 @@
         </is>
       </c>
       <c r="D66" s="5">
-        <f>IF(A66="","",MAX(E66,IF(ISNUMBER(I66),I66,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S66,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S66,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S66,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A66="","",MAX(E66,IF(ISNUMBER(I66),I66,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S66,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S66,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E66" s="5">
-        <f>IF(ISNUMBER(F66),IF(AND(J66="legacy",F66&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F66+7)+CHOOSE(WEEKDAY(F66+7,2),0,0,0,0,0,2,1))),IF(J66="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F66),MAX(DATE(2026,6,6),F66+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -19709,11 +19709,11 @@
         </is>
       </c>
       <c r="D67" s="5">
-        <f>IF(A67="","",MAX(E67,IF(ISNUMBER(I67),I67,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S67,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S67,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S67,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A67="","",MAX(E67,IF(ISNUMBER(I67),I67,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S67,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S67,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E67" s="5">
-        <f>IF(ISNUMBER(F67),IF(AND(J67="legacy",F67&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F67+7)+CHOOSE(WEEKDAY(F67+7,2),0,0,0,0,0,2,1))),IF(J67="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F67),MAX(DATE(2026,6,6),F67+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F67" s="5" t="n">
@@ -19803,11 +19803,11 @@
         </is>
       </c>
       <c r="D68" s="5">
-        <f>IF(A68="","",MAX(E68,IF(ISNUMBER(I68),I68,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S68,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S68,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S68,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A68="","",MAX(E68,IF(ISNUMBER(I68),I68,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S68,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S68,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E68" s="5">
-        <f>IF(ISNUMBER(F68),IF(AND(J68="legacy",F68&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F68+7)+CHOOSE(WEEKDAY(F68+7,2),0,0,0,0,0,2,1))),IF(J68="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F68),MAX(DATE(2026,6,6),F68+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -19899,11 +19899,11 @@
         </is>
       </c>
       <c r="D69" s="5">
-        <f>IF(A69="","",MAX(E69,IF(ISNUMBER(I69),I69,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S69,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S69,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S69,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A69="","",MAX(E69,IF(ISNUMBER(I69),I69,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S69,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S69,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E69" s="5">
-        <f>IF(ISNUMBER(F69),IF(AND(J69="legacy",F69&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F69+7)+CHOOSE(WEEKDAY(F69+7,2),0,0,0,0,0,2,1))),IF(J69="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F69),MAX(DATE(2026,6,6),F69+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -19995,11 +19995,11 @@
         </is>
       </c>
       <c r="D70" s="5">
-        <f>IF(A70="","",MAX(E70,IF(ISNUMBER(I70),I70,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S70,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S70,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S70,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A70="","",MAX(E70,IF(ISNUMBER(I70),I70,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S70,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S70,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E70" s="5">
-        <f>IF(ISNUMBER(F70),IF(AND(J70="legacy",F70&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F70+7)+CHOOSE(WEEKDAY(F70+7,2),0,0,0,0,0,2,1))),IF(J70="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F70),MAX(DATE(2026,6,6),F70+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -20091,11 +20091,11 @@
         </is>
       </c>
       <c r="D71" s="5">
-        <f>IF(A71="","",MAX(E71,IF(ISNUMBER(I71),I71,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S71,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S71,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S71,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A71="","",MAX(E71,IF(ISNUMBER(I71),I71,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S71,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S71,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E71" s="5">
-        <f>IF(ISNUMBER(F71),IF(AND(J71="legacy",F71&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F71+7)+CHOOSE(WEEKDAY(F71+7,2),0,0,0,0,0,2,1))),IF(J71="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F71),MAX(DATE(2026,6,6),F71+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F71" s="5" t="n">
@@ -20185,11 +20185,11 @@
         </is>
       </c>
       <c r="D72" s="5">
-        <f>IF(A72="","",MAX(E72,IF(ISNUMBER(I72),I72,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S72,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S72,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S72,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A72="","",MAX(E72,IF(ISNUMBER(I72),I72,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S72,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S72,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E72" s="5">
-        <f>IF(ISNUMBER(F72),IF(AND(J72="legacy",F72&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F72+7)+CHOOSE(WEEKDAY(F72+7,2),0,0,0,0,0,2,1))),IF(J72="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F72),MAX(DATE(2026,6,6),F72+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F72" s="5" t="n">
@@ -20275,11 +20275,11 @@
         </is>
       </c>
       <c r="D73" s="5">
-        <f>IF(A73="","",MAX(E73,IF(ISNUMBER(I73),I73,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S73,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S73,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S73,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A73="","",MAX(E73,IF(ISNUMBER(I73),I73,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S73,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S73,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E73" s="5">
-        <f>IF(ISNUMBER(F73),IF(AND(J73="legacy",F73&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F73+7)+CHOOSE(WEEKDAY(F73+7,2),0,0,0,0,0,2,1))),IF(J73="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F73),MAX(DATE(2026,6,6),F73+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F73" s="5" t="n">
@@ -20365,11 +20365,11 @@
         </is>
       </c>
       <c r="D74" s="5">
-        <f>IF(A74="","",MAX(E74,IF(ISNUMBER(I74),I74,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S74,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S74,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S74,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A74="","",MAX(E74,IF(ISNUMBER(I74),I74,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S74,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S74,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E74" s="5">
-        <f>IF(ISNUMBER(F74),IF(AND(J74="legacy",F74&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F74+7)+CHOOSE(WEEKDAY(F74+7,2),0,0,0,0,0,2,1))),IF(J74="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F74),MAX(DATE(2026,6,6),F74+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F74" s="5" t="n">
@@ -20459,11 +20459,11 @@
         </is>
       </c>
       <c r="D75" s="5">
-        <f>IF(A75="","",MAX(E75,IF(ISNUMBER(I75),I75,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S75,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S75,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S75,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A75="","",MAX(E75,IF(ISNUMBER(I75),I75,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S75,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S75,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E75" s="5">
-        <f>IF(ISNUMBER(F75),IF(AND(J75="legacy",F75&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F75+7)+CHOOSE(WEEKDAY(F75+7,2),0,0,0,0,0,2,1))),IF(J75="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F75),MAX(DATE(2026,6,6),F75+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F75" s="5" t="n">
@@ -20549,11 +20549,11 @@
         </is>
       </c>
       <c r="D76" s="5">
-        <f>IF(A76="","",MAX(E76,IF(ISNUMBER(I76),I76,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S76,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S76,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S76,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A76="","",MAX(E76,IF(ISNUMBER(I76),I76,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S76,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S76,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E76" s="5">
-        <f>IF(ISNUMBER(F76),IF(AND(J76="legacy",F76&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F76+7)+CHOOSE(WEEKDAY(F76+7,2),0,0,0,0,0,2,1))),IF(J76="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F76),MAX(DATE(2026,6,6),F76+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F76" s="5" t="n">
@@ -20643,11 +20643,11 @@
         </is>
       </c>
       <c r="D77" s="5">
-        <f>IF(A77="","",MAX(E77,IF(ISNUMBER(I77),I77,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S77,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S77,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S77,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A77="","",MAX(E77,IF(ISNUMBER(I77),I77,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S77,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S77,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E77" s="5">
-        <f>IF(ISNUMBER(F77),IF(AND(J77="legacy",F77&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F77+7)+CHOOSE(WEEKDAY(F77+7,2),0,0,0,0,0,2,1))),IF(J77="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F77),MAX(DATE(2026,6,6),F77+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F77" s="5" t="n">
@@ -20737,11 +20737,11 @@
         </is>
       </c>
       <c r="D78" s="5">
-        <f>IF(A78="","",MAX(E78,IF(ISNUMBER(I78),I78,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S78,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S78,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S78,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A78="","",MAX(E78,IF(ISNUMBER(I78),I78,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S78,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S78,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E78" s="5">
-        <f>IF(ISNUMBER(F78),IF(AND(J78="legacy",F78&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F78+7)+CHOOSE(WEEKDAY(F78+7,2),0,0,0,0,0,2,1))),IF(J78="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F78),MAX(DATE(2026,6,6),F78+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F78" s="5" t="n">
@@ -20831,11 +20831,11 @@
         </is>
       </c>
       <c r="D79" s="5">
-        <f>IF(A79="","",MAX(E79,IF(ISNUMBER(I79),I79,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S79,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S79,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S79,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A79="","",MAX(E79,IF(ISNUMBER(I79),I79,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S79,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S79,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E79" s="5">
-        <f>IF(ISNUMBER(F79),IF(AND(J79="legacy",F79&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F79+7)+CHOOSE(WEEKDAY(F79+7,2),0,0,0,0,0,2,1))),IF(J79="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F79),MAX(DATE(2026,6,6),F79+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F79" s="5" t="n">
@@ -20925,11 +20925,11 @@
         </is>
       </c>
       <c r="D80" s="5">
-        <f>IF(A80="","",MAX(E80,IF(ISNUMBER(I80),I80,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S80,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S80,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S80,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A80="","",MAX(E80,IF(ISNUMBER(I80),I80,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S80,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S80,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E80" s="5">
-        <f>IF(ISNUMBER(F80),IF(AND(J80="legacy",F80&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F80+7)+CHOOSE(WEEKDAY(F80+7,2),0,0,0,0,0,2,1))),IF(J80="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F80),MAX(DATE(2026,6,6),F80+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F80" s="5" t="n">
@@ -21019,11 +21019,11 @@
         </is>
       </c>
       <c r="D81" s="5">
-        <f>IF(A81="","",MAX(E81,IF(ISNUMBER(I81),I81,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S81,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S81,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S81,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A81="","",MAX(E81,IF(ISNUMBER(I81),I81,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S81,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S81,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E81" s="5">
-        <f>IF(ISNUMBER(F81),IF(AND(J81="legacy",F81&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F81+7)+CHOOSE(WEEKDAY(F81+7,2),0,0,0,0,0,2,1))),IF(J81="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F81),MAX(DATE(2026,6,6),F81+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F81" s="5" t="n">
@@ -21113,11 +21113,11 @@
         </is>
       </c>
       <c r="D82" s="5">
-        <f>IF(A82="","",MAX(E82,IF(ISNUMBER(I82),I82,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S82,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S82,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S82,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A82="","",MAX(E82,IF(ISNUMBER(I82),I82,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S82,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S82,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E82" s="5">
-        <f>IF(ISNUMBER(F82),IF(AND(J82="legacy",F82&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F82+7)+CHOOSE(WEEKDAY(F82+7,2),0,0,0,0,0,2,1))),IF(J82="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F82),MAX(DATE(2026,6,6),F82+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F82" s="5" t="n">
@@ -21203,11 +21203,11 @@
         </is>
       </c>
       <c r="D83" s="5">
-        <f>IF(A83="","",MAX(E83,IF(ISNUMBER(I83),I83,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S83,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S83,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S83,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A83="","",MAX(E83,IF(ISNUMBER(I83),I83,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S83,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S83,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E83" s="5">
-        <f>IF(ISNUMBER(F83),IF(AND(J83="legacy",F83&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F83+7)+CHOOSE(WEEKDAY(F83+7,2),0,0,0,0,0,2,1))),IF(J83="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F83),MAX(DATE(2026,6,6),F83+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F83" s="5" t="n">
@@ -21293,11 +21293,11 @@
         </is>
       </c>
       <c r="D84" s="5">
-        <f>IF(A84="","",MAX(E84,IF(ISNUMBER(I84),I84,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S84,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S84,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S84,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A84="","",MAX(E84,IF(ISNUMBER(I84),I84,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S84,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S84,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E84" s="5">
-        <f>IF(ISNUMBER(F84),IF(AND(J84="legacy",F84&lt;=DATE(2026,5,27)),DATE(2026,5,27),MAX(DATE(2026,5,27),(F84+7)+CHOOSE(WEEKDAY(F84+7,2),0,0,0,0,0,2,1))),IF(J84="legacy",DATE(2026,5,27),""))</f>
+        <f>IF(ISNUMBER(F84),MAX(DATE(2026,6,6),F84+7),DATE(2026,6,6))</f>
         <v/>
       </c>
       <c r="F84" s="5" t="n">
@@ -21383,11 +21383,11 @@
         </is>
       </c>
       <c r="D85" s="5">
-        <f>IF(A85="","",MAX(E85,IF(ISNUMBER(I85),I85,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S85,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S85,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S85,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A85="","",MAX(E85,IF(ISNUMBER(I85),I85,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S85,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S85,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E85" s="5">
-        <f>IF(ISNUMBER(F85),MAX(DATE(2026,5,27),(F85+7)+CHOOSE(WEEKDAY(F85+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F85),MAX(DATE(2026,6,6),F85+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F85" s="5" t="n">
@@ -21477,11 +21477,11 @@
         </is>
       </c>
       <c r="D86" s="5">
-        <f>IF(A86="","",MAX(E86,IF(ISNUMBER(I86),I86,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S86,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S86,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S86,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A86="","",MAX(E86,IF(ISNUMBER(I86),I86,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S86,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S86,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E86" s="5">
-        <f>IF(ISNUMBER(F86),MAX(DATE(2026,5,27),(F86+7)+CHOOSE(WEEKDAY(F86+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F86),MAX(DATE(2026,6,6),F86+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F86" s="5" t="n">
@@ -21571,11 +21571,11 @@
         </is>
       </c>
       <c r="D87" s="5">
-        <f>IF(A87="","",MAX(E87,IF(ISNUMBER(I87),I87,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S87,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S87,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S87,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A87="","",MAX(E87,IF(ISNUMBER(I87),I87,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S87,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S87,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E87" s="5">
-        <f>IF(ISNUMBER(F87),MAX(DATE(2026,5,27),(F87+7)+CHOOSE(WEEKDAY(F87+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F87),MAX(DATE(2026,6,6),F87+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F87" s="5" t="n">
@@ -21665,11 +21665,11 @@
         </is>
       </c>
       <c r="D88" s="5">
-        <f>IF(A88="","",MAX(E88,IF(ISNUMBER(I88),I88,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S88,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S88,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S88,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A88="","",MAX(E88,IF(ISNUMBER(I88),I88,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S88,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S88,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E88" s="5">
-        <f>IF(ISNUMBER(F88),MAX(DATE(2026,5,27),(F88+7)+CHOOSE(WEEKDAY(F88+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F88),MAX(DATE(2026,6,6),F88+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -21761,11 +21761,11 @@
         </is>
       </c>
       <c r="D89" s="5">
-        <f>IF(A89="","",MAX(E89,IF(ISNUMBER(I89),I89,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S89,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S89,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S89,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A89="","",MAX(E89,IF(ISNUMBER(I89),I89,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S89,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S89,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E89" s="5">
-        <f>IF(ISNUMBER(F89),MAX(DATE(2026,5,27),(F89+7)+CHOOSE(WEEKDAY(F89+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F89),MAX(DATE(2026,6,6),F89+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F89" s="5" t="n">
@@ -21855,11 +21855,11 @@
         </is>
       </c>
       <c r="D90" s="5">
-        <f>IF(A90="","",MAX(E90,IF(ISNUMBER(I90),I90,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S90,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S90,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S90,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A90="","",MAX(E90,IF(ISNUMBER(I90),I90,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S90,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S90,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E90" s="5">
-        <f>IF(ISNUMBER(F90),MAX(DATE(2026,5,27),(F90+7)+CHOOSE(WEEKDAY(F90+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F90),MAX(DATE(2026,6,6),F90+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F90" s="5" t="n">
@@ -21949,11 +21949,11 @@
         </is>
       </c>
       <c r="D91" s="5">
-        <f>IF(A91="","",MAX(E91,IF(ISNUMBER(I91),I91,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S91,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S91,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S91,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A91="","",MAX(E91,IF(ISNUMBER(I91),I91,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S91,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S91,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E91" s="5">
-        <f>IF(ISNUMBER(F91),MAX(DATE(2026,5,27),(F91+7)+CHOOSE(WEEKDAY(F91+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F91),MAX(DATE(2026,6,6),F91+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F91" s="5" t="n">
@@ -22043,11 +22043,11 @@
         </is>
       </c>
       <c r="D92" s="5">
-        <f>IF(A92="","",MAX(E92,IF(ISNUMBER(I92),I92,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S92,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S92,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S92,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A92="","",MAX(E92,IF(ISNUMBER(I92),I92,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S92,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S92,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E92" s="5">
-        <f>IF(ISNUMBER(F92),MAX(DATE(2026,5,27),(F92+7)+CHOOSE(WEEKDAY(F92+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F92),MAX(DATE(2026,6,6),F92+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F92" s="5" t="n">
@@ -22137,11 +22137,11 @@
         </is>
       </c>
       <c r="D93" s="5">
-        <f>IF(A93="","",MAX(E93,IF(ISNUMBER(I93),I93,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S93,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S93,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S93,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A93="","",MAX(E93,IF(ISNUMBER(I93),I93,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S93,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S93,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E93" s="5">
-        <f>IF(ISNUMBER(F93),MAX(DATE(2026,5,27),(F93+7)+CHOOSE(WEEKDAY(F93+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F93),MAX(DATE(2026,6,6),F93+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F93" s="5" t="n">
@@ -22231,11 +22231,11 @@
         </is>
       </c>
       <c r="D94" s="5">
-        <f>IF(A94="","",MAX(E94,IF(ISNUMBER(I94),I94,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S94,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S94,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S94,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A94="","",MAX(E94,IF(ISNUMBER(I94),I94,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S94,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S94,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E94" s="5">
-        <f>IF(ISNUMBER(F94),MAX(DATE(2026,5,27),(F94+7)+CHOOSE(WEEKDAY(F94+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F94),MAX(DATE(2026,6,6),F94+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F94" s="5" t="n">
@@ -22325,11 +22325,11 @@
         </is>
       </c>
       <c r="D95" s="5">
-        <f>IF(A95="","",MAX(E95,IF(ISNUMBER(I95),I95,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S95,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S95,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S95,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A95="","",MAX(E95,IF(ISNUMBER(I95),I95,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S95,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S95,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E95" s="5">
-        <f>IF(ISNUMBER(F95),MAX(DATE(2026,5,27),(F95+7)+CHOOSE(WEEKDAY(F95+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F95),MAX(DATE(2026,6,6),F95+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -22421,11 +22421,11 @@
         </is>
       </c>
       <c r="D96" s="5">
-        <f>IF(A96="","",MAX(E96,IF(ISNUMBER(I96),I96,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S96,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S96,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S96,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A96="","",MAX(E96,IF(ISNUMBER(I96),I96,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S96,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S96,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E96" s="5">
-        <f>IF(ISNUMBER(F96),MAX(DATE(2026,5,27),(F96+7)+CHOOSE(WEEKDAY(F96+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F96),MAX(DATE(2026,6,6),F96+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F96" s="5" t="n">
@@ -22515,11 +22515,11 @@
         </is>
       </c>
       <c r="D97" s="5">
-        <f>IF(A97="","",MAX(E97,IF(ISNUMBER(I97),I97,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S97,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S97,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S97,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A97="","",MAX(E97,IF(ISNUMBER(I97),I97,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S97,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S97,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E97" s="5">
-        <f>IF(ISNUMBER(F97),MAX(DATE(2026,5,27),(F97+7)+CHOOSE(WEEKDAY(F97+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F97),MAX(DATE(2026,6,6),F97+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F97" s="5" t="n">
@@ -22609,11 +22609,11 @@
         </is>
       </c>
       <c r="D98" s="5">
-        <f>IF(A98="","",MAX(E98,IF(ISNUMBER(I98),I98,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S98,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S98,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S98,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A98="","",MAX(E98,IF(ISNUMBER(I98),I98,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S98,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S98,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E98" s="5">
-        <f>IF(ISNUMBER(F98),MAX(DATE(2026,5,27),(F98+7)+CHOOSE(WEEKDAY(F98+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F98),MAX(DATE(2026,6,6),F98+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -22705,11 +22705,11 @@
         </is>
       </c>
       <c r="D99" s="5">
-        <f>IF(A99="","",MAX(E99,IF(ISNUMBER(I99),I99,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S99,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S99,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S99,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A99="","",MAX(E99,IF(ISNUMBER(I99),I99,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S99,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S99,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E99" s="5">
-        <f>IF(ISNUMBER(F99),MAX(DATE(2026,5,27),(F99+7)+CHOOSE(WEEKDAY(F99+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F99),MAX(DATE(2026,6,6),F99+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -22801,11 +22801,11 @@
         </is>
       </c>
       <c r="D100" s="5">
-        <f>IF(A100="","",MAX(E100,IF(ISNUMBER(I100),I100,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S100,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S100,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S100,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A100="","",MAX(E100,IF(ISNUMBER(I100),I100,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S100,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S100,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E100" s="5">
-        <f>IF(ISNUMBER(F100),MAX(DATE(2026,5,27),(F100+7)+CHOOSE(WEEKDAY(F100+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F100),MAX(DATE(2026,6,6),F100+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F100" s="5" t="n">
@@ -22895,11 +22895,11 @@
         </is>
       </c>
       <c r="D101" s="5">
-        <f>IF(A101="","",MAX(E101,IF(ISNUMBER(I101),I101,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S101,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S101,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S101,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A101="","",MAX(E101,IF(ISNUMBER(I101),I101,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S101,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S101,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E101" s="5">
-        <f>IF(ISNUMBER(F101),MAX(DATE(2026,5,27),(F101+7)+CHOOSE(WEEKDAY(F101+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F101),MAX(DATE(2026,6,6),F101+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -22991,11 +22991,11 @@
         </is>
       </c>
       <c r="D102" s="5">
-        <f>IF(A102="","",MAX(E102,IF(ISNUMBER(I102),I102,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S102,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S102,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S102,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A102="","",MAX(E102,IF(ISNUMBER(I102),I102,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S102,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S102,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E102" s="5">
-        <f>IF(ISNUMBER(F102),MAX(DATE(2026,5,27),(F102+7)+CHOOSE(WEEKDAY(F102+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F102),MAX(DATE(2026,6,6),F102+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F102" s="5" t="n">
@@ -23085,11 +23085,11 @@
         </is>
       </c>
       <c r="D103" s="5">
-        <f>IF(A103="","",MAX(E103,IF(ISNUMBER(I103),I103,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S103,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S103,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S103,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A103="","",MAX(E103,IF(ISNUMBER(I103),I103,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S103,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S103,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E103" s="5">
-        <f>IF(ISNUMBER(F103),MAX(DATE(2026,5,27),(F103+7)+CHOOSE(WEEKDAY(F103+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F103),MAX(DATE(2026,6,6),F103+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F103" s="5" t="n">
@@ -23179,11 +23179,11 @@
         </is>
       </c>
       <c r="D104" s="5">
-        <f>IF(A104="","",MAX(E104,IF(ISNUMBER(I104),I104,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S104,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S104,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S104,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A104="","",MAX(E104,IF(ISNUMBER(I104),I104,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S104,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S104,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E104" s="5">
-        <f>IF(ISNUMBER(F104),MAX(DATE(2026,5,27),(F104+7)+CHOOSE(WEEKDAY(F104+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F104),MAX(DATE(2026,6,6),F104+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F104" s="5" t="n">
@@ -23273,11 +23273,11 @@
         </is>
       </c>
       <c r="D105" s="5">
-        <f>IF(A105="","",MAX(E105,IF(ISNUMBER(I105),I105,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S105,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S105,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S105,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A105="","",MAX(E105,IF(ISNUMBER(I105),I105,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S105,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S105,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E105" s="5">
-        <f>IF(ISNUMBER(F105),MAX(DATE(2026,5,27),(F105+7)+CHOOSE(WEEKDAY(F105+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F105),MAX(DATE(2026,6,6),F105+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F105" s="5" t="n">
@@ -23367,11 +23367,11 @@
         </is>
       </c>
       <c r="D106" s="5">
-        <f>IF(A106="","",MAX(E106,IF(ISNUMBER(I106),I106,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S106,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S106,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S106,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A106="","",MAX(E106,IF(ISNUMBER(I106),I106,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S106,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S106,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E106" s="5">
-        <f>IF(ISNUMBER(F106),MAX(DATE(2026,5,27),(F106+7)+CHOOSE(WEEKDAY(F106+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F106),MAX(DATE(2026,6,6),F106+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -23463,11 +23463,11 @@
         </is>
       </c>
       <c r="D107" s="5">
-        <f>IF(A107="","",MAX(E107,IF(ISNUMBER(I107),I107,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S107,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S107,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S107,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A107="","",MAX(E107,IF(ISNUMBER(I107),I107,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S107,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S107,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E107" s="5">
-        <f>IF(ISNUMBER(F107),MAX(DATE(2026,5,27),(F107+7)+CHOOSE(WEEKDAY(F107+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F107),MAX(DATE(2026,6,6),F107+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F107" s="5" t="n">
@@ -23557,11 +23557,11 @@
         </is>
       </c>
       <c r="D108" s="5">
-        <f>IF(A108="","",MAX(E108,IF(ISNUMBER(I108),I108,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S108,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S108,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S108,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A108="","",MAX(E108,IF(ISNUMBER(I108),I108,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S108,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S108,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E108" s="5">
-        <f>IF(ISNUMBER(F108),MAX(DATE(2026,5,27),(F108+7)+CHOOSE(WEEKDAY(F108+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F108),MAX(DATE(2026,6,6),F108+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -23653,11 +23653,11 @@
         </is>
       </c>
       <c r="D109" s="5">
-        <f>IF(A109="","",MAX(E109,IF(ISNUMBER(I109),I109,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S109,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S109,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S109,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A109="","",MAX(E109,IF(ISNUMBER(I109),I109,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S109,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S109,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E109" s="5">
-        <f>IF(ISNUMBER(F109),MAX(DATE(2026,5,27),(F109+7)+CHOOSE(WEEKDAY(F109+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F109),MAX(DATE(2026,6,6),F109+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F109" s="5" t="n">
@@ -23747,11 +23747,11 @@
         </is>
       </c>
       <c r="D110" s="5">
-        <f>IF(A110="","",MAX(E110,IF(ISNUMBER(I110),I110,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S110,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S110,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S110,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A110="","",MAX(E110,IF(ISNUMBER(I110),I110,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S110,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S110,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E110" s="5">
-        <f>IF(ISNUMBER(F110),MAX(DATE(2026,5,27),(F110+7)+CHOOSE(WEEKDAY(F110+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F110),MAX(DATE(2026,6,6),F110+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F110" s="5" t="n">
@@ -23841,11 +23841,11 @@
         </is>
       </c>
       <c r="D111" s="5">
-        <f>IF(A111="","",MAX(E111,IF(ISNUMBER(I111),I111,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S111,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S111,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S111,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A111="","",MAX(E111,IF(ISNUMBER(I111),I111,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S111,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S111,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E111" s="5">
-        <f>IF(ISNUMBER(F111),MAX(DATE(2026,5,27),(F111+7)+CHOOSE(WEEKDAY(F111+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F111),MAX(DATE(2026,6,6),F111+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -23937,11 +23937,11 @@
         </is>
       </c>
       <c r="D112" s="5">
-        <f>IF(A112="","",MAX(E112,IF(ISNUMBER(I112),I112,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S112,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S112,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S112,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A112="","",MAX(E112,IF(ISNUMBER(I112),I112,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S112,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S112,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E112" s="5">
-        <f>IF(ISNUMBER(F112),MAX(DATE(2026,5,27),(F112+7)+CHOOSE(WEEKDAY(F112+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F112),MAX(DATE(2026,6,6),F112+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F112" s="5" t="inlineStr">
@@ -24033,11 +24033,11 @@
         </is>
       </c>
       <c r="D113" s="5">
-        <f>IF(A113="","",MAX(E113,IF(ISNUMBER(I113),I113,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S113,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S113,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S113,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A113="","",MAX(E113,IF(ISNUMBER(I113),I113,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S113,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S113,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E113" s="5">
-        <f>IF(ISNUMBER(F113),MAX(DATE(2026,5,27),(F113+7)+CHOOSE(WEEKDAY(F113+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F113),MAX(DATE(2026,6,6),F113+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -24129,11 +24129,11 @@
         </is>
       </c>
       <c r="D114" s="5">
-        <f>IF(A114="","",MAX(E114,IF(ISNUMBER(I114),I114,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S114,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S114,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S114,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A114="","",MAX(E114,IF(ISNUMBER(I114),I114,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S114,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S114,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E114" s="5">
-        <f>IF(ISNUMBER(F114),MAX(DATE(2026,5,27),(F114+7)+CHOOSE(WEEKDAY(F114+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F114),MAX(DATE(2026,6,6),F114+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F114" s="5" t="n">
@@ -24223,11 +24223,11 @@
         </is>
       </c>
       <c r="D115" s="5">
-        <f>IF(A115="","",MAX(E115,IF(ISNUMBER(I115),I115,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S115,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S115,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S115,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A115="","",MAX(E115,IF(ISNUMBER(I115),I115,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S115,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S115,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E115" s="5">
-        <f>IF(ISNUMBER(F115),MAX(DATE(2026,5,27),(F115+7)+CHOOSE(WEEKDAY(F115+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F115),MAX(DATE(2026,6,6),F115+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F115" s="5" t="inlineStr">
@@ -24319,11 +24319,11 @@
         </is>
       </c>
       <c r="D116" s="5">
-        <f>IF(A116="","",MAX(E116,IF(ISNUMBER(I116),I116,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S116,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S116,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S116,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A116="","",MAX(E116,IF(ISNUMBER(I116),I116,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S116,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S116,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E116" s="5">
-        <f>IF(ISNUMBER(F116),MAX(DATE(2026,5,27),(F116+7)+CHOOSE(WEEKDAY(F116+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F116),MAX(DATE(2026,6,6),F116+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -24415,11 +24415,11 @@
         </is>
       </c>
       <c r="D117" s="5">
-        <f>IF(A117="","",MAX(E117,IF(ISNUMBER(I117),I117,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S117,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S117,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S117,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A117="","",MAX(E117,IF(ISNUMBER(I117),I117,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S117,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S117,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E117" s="5">
-        <f>IF(ISNUMBER(F117),MAX(DATE(2026,5,27),(F117+7)+CHOOSE(WEEKDAY(F117+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F117),MAX(DATE(2026,6,6),F117+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F117" s="5" t="n">
@@ -24509,11 +24509,11 @@
         </is>
       </c>
       <c r="D118" s="5">
-        <f>IF(A118="","",MAX(E118,IF(ISNUMBER(I118),I118,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S118,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S118,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S118,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A118="","",MAX(E118,IF(ISNUMBER(I118),I118,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S118,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S118,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E118" s="5">
-        <f>IF(ISNUMBER(F118),MAX(DATE(2026,5,27),(F118+7)+CHOOSE(WEEKDAY(F118+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F118),MAX(DATE(2026,6,6),F118+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F118" s="5" t="n">
@@ -24603,11 +24603,11 @@
         </is>
       </c>
       <c r="D119" s="5">
-        <f>IF(A119="","",MAX(E119,IF(ISNUMBER(I119),I119,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S119,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S119,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S119,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A119="","",MAX(E119,IF(ISNUMBER(I119),I119,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S119,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S119,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E119" s="5">
-        <f>IF(ISNUMBER(F119),MAX(DATE(2026,5,27),(F119+7)+CHOOSE(WEEKDAY(F119+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F119),MAX(DATE(2026,6,6),F119+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F119" s="5" t="n">
@@ -24697,11 +24697,11 @@
         </is>
       </c>
       <c r="D120" s="5">
-        <f>IF(A120="","",MAX(E120,IF(ISNUMBER(I120),I120,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S120,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S120,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S120,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A120="","",MAX(E120,IF(ISNUMBER(I120),I120,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S120,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S120,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E120" s="5">
-        <f>IF(ISNUMBER(F120),MAX(DATE(2026,5,27),(F120+7)+CHOOSE(WEEKDAY(F120+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F120),MAX(DATE(2026,6,6),F120+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F120" s="5" t="n">
@@ -24791,11 +24791,11 @@
         </is>
       </c>
       <c r="D121" s="5">
-        <f>IF(A121="","",MAX(E121,IF(ISNUMBER(I121),I121,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S121,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S121,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S121,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A121="","",MAX(E121,IF(ISNUMBER(I121),I121,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S121,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S121,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E121" s="5">
-        <f>IF(ISNUMBER(F121),MAX(DATE(2026,5,27),(F121+7)+CHOOSE(WEEKDAY(F121+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F121),MAX(DATE(2026,6,6),F121+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -24887,11 +24887,11 @@
         </is>
       </c>
       <c r="D122" s="5">
-        <f>IF(A122="","",MAX(E122,IF(ISNUMBER(I122),I122,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S122,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S122,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S122,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A122="","",MAX(E122,IF(ISNUMBER(I122),I122,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S122,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S122,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E122" s="5">
-        <f>IF(ISNUMBER(F122),MAX(DATE(2026,5,27),(F122+7)+CHOOSE(WEEKDAY(F122+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F122),MAX(DATE(2026,6,6),F122+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F122" s="5" t="n">
@@ -24981,11 +24981,11 @@
         </is>
       </c>
       <c r="D123" s="5">
-        <f>IF(A123="","",MAX(E123,IF(ISNUMBER(I123),I123,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S123,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S123,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S123,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A123="","",MAX(E123,IF(ISNUMBER(I123),I123,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S123,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S123,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E123" s="5">
-        <f>IF(ISNUMBER(F123),MAX(DATE(2026,5,27),(F123+7)+CHOOSE(WEEKDAY(F123+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F123),MAX(DATE(2026,6,6),F123+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F123" s="5" t="inlineStr">
@@ -25077,11 +25077,11 @@
         </is>
       </c>
       <c r="D124" s="5">
-        <f>IF(A124="","",MAX(E124,IF(ISNUMBER(I124),I124,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S124,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S124,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S124,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A124="","",MAX(E124,IF(ISNUMBER(I124),I124,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S124,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S124,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E124" s="5">
-        <f>IF(ISNUMBER(F124),MAX(DATE(2026,5,27),(F124+7)+CHOOSE(WEEKDAY(F124+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F124),MAX(DATE(2026,6,6),F124+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -25169,11 +25169,11 @@
         </is>
       </c>
       <c r="D125" s="5">
-        <f>IF(A125="","",MAX(E125,IF(ISNUMBER(I125),I125,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S125,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S125,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S125,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A125="","",MAX(E125,IF(ISNUMBER(I125),I125,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S125,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S125,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E125" s="5">
-        <f>IF(ISNUMBER(F125),MAX(DATE(2026,5,27),(F125+7)+CHOOSE(WEEKDAY(F125+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F125),MAX(DATE(2026,6,6),F125+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -25265,11 +25265,11 @@
         </is>
       </c>
       <c r="D126" s="5">
-        <f>IF(A126="","",MAX(E126,IF(ISNUMBER(I126),I126,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S126,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S126,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S126,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A126="","",MAX(E126,IF(ISNUMBER(I126),I126,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S126,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S126,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E126" s="5">
-        <f>IF(ISNUMBER(F126),MAX(DATE(2026,5,27),(F126+7)+CHOOSE(WEEKDAY(F126+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F126),MAX(DATE(2026,6,6),F126+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F126" s="5" t="n">
@@ -25359,11 +25359,11 @@
         </is>
       </c>
       <c r="D127" s="5">
-        <f>IF(A127="","",MAX(E127,IF(ISNUMBER(I127),I127,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S127,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S127,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S127,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A127="","",MAX(E127,IF(ISNUMBER(I127),I127,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S127,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S127,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E127" s="5">
-        <f>IF(ISNUMBER(F127),MAX(DATE(2026,5,27),(F127+7)+CHOOSE(WEEKDAY(F127+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F127),MAX(DATE(2026,6,6),F127+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F127" s="5" t="n">
@@ -25453,11 +25453,11 @@
         </is>
       </c>
       <c r="D128" s="5">
-        <f>IF(A128="","",MAX(E128,IF(ISNUMBER(I128),I128,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S128,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S128,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S128,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A128="","",MAX(E128,IF(ISNUMBER(I128),I128,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S128,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S128,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E128" s="5">
-        <f>IF(ISNUMBER(F128),MAX(DATE(2026,5,27),(F128+7)+CHOOSE(WEEKDAY(F128+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F128),MAX(DATE(2026,6,6),F128+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -25549,11 +25549,11 @@
         </is>
       </c>
       <c r="D129" s="5">
-        <f>IF(A129="","",MAX(E129,IF(ISNUMBER(I129),I129,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S129,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S129,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S129,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A129="","",MAX(E129,IF(ISNUMBER(I129),I129,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S129,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S129,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E129" s="5">
-        <f>IF(ISNUMBER(F129),MAX(DATE(2026,5,27),(F129+7)+CHOOSE(WEEKDAY(F129+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F129),MAX(DATE(2026,6,6),F129+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F129" s="5" t="n">
@@ -25643,11 +25643,11 @@
         </is>
       </c>
       <c r="D130" s="5">
-        <f>IF(A130="","",MAX(E130,IF(ISNUMBER(I130),I130,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S130,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S130,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S130,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A130="","",MAX(E130,IF(ISNUMBER(I130),I130,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S130,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S130,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E130" s="5">
-        <f>IF(ISNUMBER(F130),MAX(DATE(2026,5,27),(F130+7)+CHOOSE(WEEKDAY(F130+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F130),MAX(DATE(2026,6,6),F130+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F130" s="5" t="n">
@@ -25737,11 +25737,11 @@
         </is>
       </c>
       <c r="D131" s="5">
-        <f>IF(A131="","",MAX(E131,IF(ISNUMBER(I131),I131,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S131,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S131,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S131,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A131="","",MAX(E131,IF(ISNUMBER(I131),I131,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S131,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S131,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E131" s="5">
-        <f>IF(ISNUMBER(F131),MAX(DATE(2026,5,27),(F131+7)+CHOOSE(WEEKDAY(F131+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F131),MAX(DATE(2026,6,6),F131+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F131" s="5" t="inlineStr">
@@ -25833,11 +25833,11 @@
         </is>
       </c>
       <c r="D132" s="5">
-        <f>IF(A132="","",MAX(E132,IF(ISNUMBER(I132),I132,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S132,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S132,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S132,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A132="","",MAX(E132,IF(ISNUMBER(I132),I132,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S132,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S132,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E132" s="5">
-        <f>IF(ISNUMBER(F132),MAX(DATE(2026,5,27),(F132+7)+CHOOSE(WEEKDAY(F132+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F132),MAX(DATE(2026,6,6),F132+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F132" s="5" t="n">
@@ -25927,11 +25927,11 @@
         </is>
       </c>
       <c r="D133" s="5">
-        <f>IF(A133="","",MAX(E133,IF(ISNUMBER(I133),I133,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S133,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S133,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S133,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A133="","",MAX(E133,IF(ISNUMBER(I133),I133,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S133,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S133,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E133" s="5">
-        <f>IF(ISNUMBER(F133),MAX(DATE(2026,5,27),(F133+7)+CHOOSE(WEEKDAY(F133+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F133),MAX(DATE(2026,6,6),F133+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F133" s="5" t="n">
@@ -26021,11 +26021,11 @@
         </is>
       </c>
       <c r="D134" s="5">
-        <f>IF(A134="","",MAX(E134,IF(ISNUMBER(I134),I134,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S134,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S134,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S134,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A134="","",MAX(E134,IF(ISNUMBER(I134),I134,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S134,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S134,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E134" s="5">
-        <f>IF(ISNUMBER(F134),MAX(DATE(2026,5,27),(F134+7)+CHOOSE(WEEKDAY(F134+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F134),MAX(DATE(2026,6,6),F134+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F134" s="5" t="n">
@@ -26115,11 +26115,11 @@
         </is>
       </c>
       <c r="D135" s="5">
-        <f>IF(A135="","",MAX(E135,IF(ISNUMBER(I135),I135,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S135,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S135,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S135,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A135="","",MAX(E135,IF(ISNUMBER(I135),I135,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S135,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S135,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E135" s="5">
-        <f>IF(ISNUMBER(F135),MAX(DATE(2026,5,27),(F135+7)+CHOOSE(WEEKDAY(F135+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F135),MAX(DATE(2026,6,6),F135+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F135" s="5" t="inlineStr">
@@ -26211,11 +26211,11 @@
         </is>
       </c>
       <c r="D136" s="5">
-        <f>IF(A136="","",MAX(E136,IF(ISNUMBER(I136),I136,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S136,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S136,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S136,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A136="","",MAX(E136,IF(ISNUMBER(I136),I136,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S136,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S136,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E136" s="5">
-        <f>IF(ISNUMBER(F136),MAX(DATE(2026,5,27),(F136+7)+CHOOSE(WEEKDAY(F136+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F136),MAX(DATE(2026,6,6),F136+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F136" s="5" t="n">
@@ -26305,11 +26305,11 @@
         </is>
       </c>
       <c r="D137" s="5">
-        <f>IF(A137="","",MAX(E137,IF(ISNUMBER(I137),I137,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S137,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S137,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S137,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A137="","",MAX(E137,IF(ISNUMBER(I137),I137,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S137,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S137,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E137" s="5">
-        <f>IF(ISNUMBER(F137),MAX(DATE(2026,5,27),(F137+7)+CHOOSE(WEEKDAY(F137+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F137),MAX(DATE(2026,6,6),F137+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F137" s="5" t="inlineStr">
@@ -26401,11 +26401,11 @@
         </is>
       </c>
       <c r="D138" s="5">
-        <f>IF(A138="","",MAX(E138,IF(ISNUMBER(I138),I138,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S138,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S138,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S138,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A138="","",MAX(E138,IF(ISNUMBER(I138),I138,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S138,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S138,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E138" s="5">
-        <f>IF(ISNUMBER(F138),MAX(DATE(2026,5,27),(F138+7)+CHOOSE(WEEKDAY(F138+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F138),MAX(DATE(2026,6,6),F138+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F138" s="5" t="n">
@@ -26495,11 +26495,11 @@
         </is>
       </c>
       <c r="D139" s="5">
-        <f>IF(A139="","",MAX(E139,IF(ISNUMBER(I139),I139,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S139,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S139,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S139,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A139="","",MAX(E139,IF(ISNUMBER(I139),I139,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S139,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S139,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E139" s="5">
-        <f>IF(ISNUMBER(F139),MAX(DATE(2026,5,27),(F139+7)+CHOOSE(WEEKDAY(F139+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F139),MAX(DATE(2026,6,6),F139+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F139" s="5" t="n">
@@ -26589,11 +26589,11 @@
         </is>
       </c>
       <c r="D140" s="5">
-        <f>IF(A140="","",MAX(E140,IF(ISNUMBER(I140),I140,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S140,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S140,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S140,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A140="","",MAX(E140,IF(ISNUMBER(I140),I140,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S140,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S140,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E140" s="5">
-        <f>IF(ISNUMBER(F140),MAX(DATE(2026,5,27),(F140+7)+CHOOSE(WEEKDAY(F140+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F140),MAX(DATE(2026,6,6),F140+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F140" s="5" t="n">
@@ -26683,11 +26683,11 @@
         </is>
       </c>
       <c r="D141" s="5">
-        <f>IF(A141="","",MAX(E141,IF(ISNUMBER(I141),I141,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S141,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S141,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S141,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A141="","",MAX(E141,IF(ISNUMBER(I141),I141,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S141,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S141,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E141" s="5">
-        <f>IF(ISNUMBER(F141),MAX(DATE(2026,5,27),(F141+7)+CHOOSE(WEEKDAY(F141+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F141),MAX(DATE(2026,6,6),F141+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F141" s="5" t="n">
@@ -26777,11 +26777,11 @@
         </is>
       </c>
       <c r="D142" s="5">
-        <f>IF(A142="","",MAX(E142,IF(ISNUMBER(I142),I142,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S142,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S142,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S142,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A142="","",MAX(E142,IF(ISNUMBER(I142),I142,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S142,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S142,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E142" s="5">
-        <f>IF(ISNUMBER(F142),MAX(DATE(2026,5,27),(F142+7)+CHOOSE(WEEKDAY(F142+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F142),MAX(DATE(2026,6,6),F142+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F142" s="5" t="n">
@@ -26871,11 +26871,11 @@
         </is>
       </c>
       <c r="D143" s="5">
-        <f>IF(A143="","",MAX(E143,IF(ISNUMBER(I143),I143,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S143,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S143,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S143,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A143="","",MAX(E143,IF(ISNUMBER(I143),I143,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S143,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S143,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E143" s="5">
-        <f>IF(ISNUMBER(F143),MAX(DATE(2026,5,27),(F143+7)+CHOOSE(WEEKDAY(F143+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F143),MAX(DATE(2026,6,6),F143+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F143" s="5" t="n">
@@ -26965,11 +26965,11 @@
         </is>
       </c>
       <c r="D144" s="5">
-        <f>IF(A144="","",MAX(E144,IF(ISNUMBER(I144),I144,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S144,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S144,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S144,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A144="","",MAX(E144,IF(ISNUMBER(I144),I144,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S144,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S144,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E144" s="5">
-        <f>IF(ISNUMBER(F144),MAX(DATE(2026,5,27),(F144+7)+CHOOSE(WEEKDAY(F144+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F144),MAX(DATE(2026,6,6),F144+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F144" s="5" t="n">
@@ -27059,11 +27059,11 @@
         </is>
       </c>
       <c r="D145" s="5">
-        <f>IF(A145="","",MAX(E145,IF(ISNUMBER(I145),I145,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S145,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S145,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S145,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A145="","",MAX(E145,IF(ISNUMBER(I145),I145,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S145,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S145,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E145" s="5">
-        <f>IF(ISNUMBER(F145),MAX(DATE(2026,5,27),(F145+7)+CHOOSE(WEEKDAY(F145+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F145),MAX(DATE(2026,6,6),F145+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F145" s="5" t="inlineStr">
@@ -27155,11 +27155,11 @@
         </is>
       </c>
       <c r="D146" s="5">
-        <f>IF(A146="","",MAX(E146,IF(ISNUMBER(I146),I146,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S146,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S146,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S146,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A146="","",MAX(E146,IF(ISNUMBER(I146),I146,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S146,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S146,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E146" s="5">
-        <f>IF(ISNUMBER(F146),MAX(DATE(2026,5,27),(F146+7)+CHOOSE(WEEKDAY(F146+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F146),MAX(DATE(2026,6,6),F146+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F146" s="5" t="inlineStr">
@@ -27251,11 +27251,11 @@
         </is>
       </c>
       <c r="D147" s="5">
-        <f>IF(A147="","",MAX(E147,IF(ISNUMBER(I147),I147,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S147,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S147,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S147,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A147="","",MAX(E147,IF(ISNUMBER(I147),I147,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S147,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S147,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E147" s="5">
-        <f>IF(ISNUMBER(F147),MAX(DATE(2026,5,27),(F147+7)+CHOOSE(WEEKDAY(F147+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F147),MAX(DATE(2026,6,6),F147+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F147" s="5" t="n">
@@ -27345,11 +27345,11 @@
         </is>
       </c>
       <c r="D148" s="5">
-        <f>IF(A148="","",MAX(E148,IF(ISNUMBER(I148),I148,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S148,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S148,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S148,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A148="","",MAX(E148,IF(ISNUMBER(I148),I148,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S148,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S148,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E148" s="5">
-        <f>IF(ISNUMBER(F148),MAX(DATE(2026,5,27),(F148+7)+CHOOSE(WEEKDAY(F148+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F148),MAX(DATE(2026,6,6),F148+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F148" s="5" t="n">
@@ -27435,11 +27435,11 @@
         </is>
       </c>
       <c r="D149" s="5">
-        <f>IF(A149="","",MAX(E149,IF(ISNUMBER(I149),I149,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S149,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S149,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S149,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A149="","",MAX(E149,IF(ISNUMBER(I149),I149,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S149,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S149,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E149" s="5">
-        <f>IF(ISNUMBER(F149),MAX(DATE(2026,5,27),(F149+7)+CHOOSE(WEEKDAY(F149+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F149),MAX(DATE(2026,6,6),F149+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F149" s="5" t="n">
@@ -27525,11 +27525,11 @@
         </is>
       </c>
       <c r="D150" s="5">
-        <f>IF(A150="","",MAX(E150,IF(ISNUMBER(I150),I150,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S150,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S150,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S150,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A150="","",MAX(E150,IF(ISNUMBER(I150),I150,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S150,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S150,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E150" s="5">
-        <f>IF(ISNUMBER(F150),MAX(DATE(2026,5,27),(F150+7)+CHOOSE(WEEKDAY(F150+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F150),MAX(DATE(2026,6,6),F150+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F150" s="5" t="n">
@@ -27619,11 +27619,11 @@
         </is>
       </c>
       <c r="D151" s="5">
-        <f>IF(A151="","",MAX(E151,IF(ISNUMBER(I151),I151,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S151,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S151,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S151,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A151="","",MAX(E151,IF(ISNUMBER(I151),I151,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S151,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S151,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E151" s="5">
-        <f>IF(ISNUMBER(F151),MAX(DATE(2026,5,27),(F151+7)+CHOOSE(WEEKDAY(F151+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F151),MAX(DATE(2026,6,6),F151+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F151" s="5" t="n">
@@ -27709,11 +27709,11 @@
         </is>
       </c>
       <c r="D152" s="5">
-        <f>IF(A152="","",MAX(E152,IF(ISNUMBER(I152),I152,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S152,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S152,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S152,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A152="","",MAX(E152,IF(ISNUMBER(I152),I152,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S152,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S152,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E152" s="5">
-        <f>IF(ISNUMBER(F152),MAX(DATE(2026,5,27),(F152+7)+CHOOSE(WEEKDAY(F152+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F152),MAX(DATE(2026,6,6),F152+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F152" s="5" t="n">
@@ -27803,11 +27803,11 @@
         </is>
       </c>
       <c r="D153" s="5">
-        <f>IF(A153="","",MAX(E153,IF(ISNUMBER(I153),I153,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S153,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S153,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S153,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A153="","",MAX(E153,IF(ISNUMBER(I153),I153,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S153,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S153,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E153" s="5">
-        <f>IF(ISNUMBER(F153),MAX(DATE(2026,5,27),(F153+7)+CHOOSE(WEEKDAY(F153+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F153),MAX(DATE(2026,6,6),F153+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F153" s="5" t="n">
@@ -27897,11 +27897,11 @@
         </is>
       </c>
       <c r="D154" s="5">
-        <f>IF(A154="","",MAX(E154,IF(ISNUMBER(I154),I154,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S154,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S154,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S154,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A154="","",MAX(E154,IF(ISNUMBER(I154),I154,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S154,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S154,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E154" s="5">
-        <f>IF(ISNUMBER(F154),MAX(DATE(2026,5,27),(F154+7)+CHOOSE(WEEKDAY(F154+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F154),MAX(DATE(2026,6,6),F154+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F154" s="5" t="n">
@@ -27991,11 +27991,11 @@
         </is>
       </c>
       <c r="D155" s="5">
-        <f>IF(A155="","",MAX(E155,IF(ISNUMBER(I155),I155,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S155,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S155,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S155,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A155="","",MAX(E155,IF(ISNUMBER(I155),I155,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S155,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S155,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E155" s="5">
-        <f>IF(ISNUMBER(F155),MAX(DATE(2026,5,27),(F155+7)+CHOOSE(WEEKDAY(F155+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F155),MAX(DATE(2026,6,6),F155+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F155" s="5" t="inlineStr">
@@ -28087,11 +28087,11 @@
         </is>
       </c>
       <c r="D156" s="5">
-        <f>IF(A156="","",MAX(E156,IF(ISNUMBER(I156),I156,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S156,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S156,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S156,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A156="","",MAX(E156,IF(ISNUMBER(I156),I156,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S156,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S156,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E156" s="5">
-        <f>IF(ISNUMBER(F156),MAX(DATE(2026,5,27),(F156+7)+CHOOSE(WEEKDAY(F156+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F156),MAX(DATE(2026,6,6),F156+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F156" s="5" t="n">
@@ -28181,11 +28181,11 @@
         </is>
       </c>
       <c r="D157" s="5">
-        <f>IF(A157="","",MAX(E157,IF(ISNUMBER(I157),I157,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S157,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S157,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S157,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A157="","",MAX(E157,IF(ISNUMBER(I157),I157,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S157,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S157,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E157" s="5">
-        <f>IF(ISNUMBER(F157),MAX(DATE(2026,5,27),(F157+7)+CHOOSE(WEEKDAY(F157+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F157),MAX(DATE(2026,6,6),F157+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F157" s="5" t="inlineStr">
@@ -28277,11 +28277,11 @@
         </is>
       </c>
       <c r="D158" s="5">
-        <f>IF(A158="","",MAX(E158,IF(ISNUMBER(I158),I158,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S158,'iCoA Register'!$P:$P,0))),(INDEX('iCoA Register'!$F:$F,MATCH(S158,'iCoA Register'!$P:$P,0)))+CHOOSE(WEEKDAY(INDEX('iCoA Register'!$F:$F,MATCH(S158,'iCoA Register'!$P:$P,0)),2),0,0,0,0,0,2,1),0),0)))</f>
+        <f>IF(A158="","",MAX(E158,IF(ISNUMBER(I158),I158,0),IFERROR(IF(ISNUMBER(INDEX('iCoA Register'!$F:$F,MATCH(S158,'iCoA Register'!$P:$P,0))),INDEX('iCoA Register'!$F:$F,MATCH(S158,'iCoA Register'!$P:$P,0)),0),0)))</f>
         <v/>
       </c>
       <c r="E158" s="5">
-        <f>IF(ISNUMBER(F158),MAX(DATE(2026,5,27),(F158+7)+CHOOSE(WEEKDAY(F158+7,2),0,0,0,0,0,2,1)),"at retest sampling")</f>
+        <f>IF(ISNUMBER(F158),MAX(DATE(2026,6,6),F158+7),"at retest sampling")</f>
         <v/>
       </c>
       <c r="F158" s="5" t="inlineStr">
@@ -28361,7 +28361,7 @@
     <row r="160" ht="150" customHeight="1">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins, microbiology by IJZ-MB) and the initial certificates for the rest; its rule date is the first working day 7 days after the latest retest certificate, and it is issued once the in-house retest iCoA exists. FORMULAS: No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 28.05.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 01.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #9 — only the retest 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 01.06.2026 | P060342: no initial certificate for #9 — only the retest 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins, microbiology by IJZ-MB) and the initial certificates for the rest; its rule date is the first working day 7 days after the latest retest certificate, and it is issued once the in-house retest iCoA exists. FORMULAS: No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #9 — only the retest 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #9 — only the retest 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
@@ -31732,7 +31732,7 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v21 on 05.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v22 on 05.09.2026</t>
         </is>
       </c>
     </row>
@@ -31746,14 +31746,14 @@
     <row r="3" ht="190" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins, microbiology by IJZ-MB) and the initial certificates for the rest; its rule date is the first working day 7 days after the latest retest certificate, and it is issued once the in-house retest iCoA exists. FORMULAS: No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 27.05.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 28.05.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 01.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 27.05.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #9 — only the retest 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 01.06.2026 | P060342: no initial certificate for #9 — only the retest 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
+          <t>Head of QC, 05.09.2026: preliminary CoQ issuance register — codes CoQ-PP_26-nnn (nnn = 001 … 999), one series for the year of issue, in the order of issue. LEGACY lots (packed before the SOP floor of 11.05.2026, or holding an old in-house QCCoA 001 certificate, which the CoQ supersedes) are all issued on 27.05.2026, in chronological order of packaging; POST-SOP lots follow, each on the first working day 7 days after the latest eCoA the CoQ cites and never before 27.05.2026, so the legacy series keeps 001 onward. Every CoQ cites its lot's iCoA (identification A, B, foreign matter) and reports identification C as 'Conforms', referenced to the eCoA that covers Total THC. ADHERENCE (ISSUE_COQ_CONVENTIONS): a CoQ never precedes a document it cites — a legacy lot whose latest eCoA is dated after 27.05.2026 takes the post-SOP rule and is flagged in Status; a CoQ never precedes its iCoA; Head of QC, 05.09.2026 (evening): a production lot whose initial certificate for a determination is not on file keeps its planned CoQ and number — the initial testing exists at the Faculty of Pharmacy's Center for Natural Products (microbiology: IJZ) and the certificate is to be located (Work Order; Status names the determination); a certificate dated on or after 01.07.2026 is a retest document (the QP's campaign: Tranche 1, the first 21 lots, sampled July 2026; then Tranches 2 and 3) and never certifies the initial CoQ — a determination whose only certificate is a retest one is uncertified for the legacy CoQ and flagged; the IJZ-MB delivery of 25/26.08.2026 (certificates of 31.08 and 01.09.2026, 68 to 436 days after packaging) is one campaign sampling and every certificate in it is a retest document, for the post-SOP lots too; nothing is dated on a weekend. RETEST ROWS: the reissued CoQ carries the retest results (cannabinoids with identification C by Farmahem, mycotoxins, microbiology by IJZ-MB) and the initial certificates for the rest; its rule date is the first working day 7 days after the latest retest certificate, and it is issued once the in-house retest iCoA exists. FORMULAS: No. and the code as on the iCoA Register; Rule date is 27.05.2026 for a legacy row whose latest eCoA is on or before it, else the first working day 7 days after the latest eCoA (not before 27.05.2026); the planned date is the latest of the rule date, the iCoA's date and the lot's last day of packaging; iCoA (register) and its date are looked up on the iCoA Register by Key. The latest eCoA cited is a value (the first credited certificate per determination dated before the retest campaign; for a retest row, the latest retest certificate), recomputed by the builder. Working days are Monday to Friday; public holidays are not applied. FLAGS: the legacy CoQ day 06.06.2026 is a Saturday — the owner's date, kept as given | P060272: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060322: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060432: no initial certificate for #9 — only the retest 537-1068-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060392: no initial certificate for #9 — only the retest 538-1069-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060292: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060302: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060402: no initial certificate for #10 — only the retest 197-8-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060142: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060182: no initial certificate for #9 — only the retest 550-1081-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | HPA1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-13-K-26 of 07.08.2026 / 197-13-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060152: no initial certificate for #10 — only the retest 197-16-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060202: no initial certificate for #9 — only the retest 547-1078-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060262: post-SOP CoQ rule date 30.04.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060312: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060482: CoQ rule date 07.07.2026 precedes the packaging of the lot (05.08.2026) — held to the packaging date | OPM1024: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-17-K-26 of 07.08.2026 / 197-17-M-26 of 10.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060222: no initial certificate for #9 — only the retest 546-1077-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060332: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060332: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-6-K-26 of 07.08.2026 / 197-6-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060352: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060352: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-7-K-26 of 07.08.2026 / 197-7-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060382: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060382: no initial certificate for #3, #4, #5, #6, #8, #10 — only the retest 197-21-K-26 of 07.08.2026 / 197-21-M-26 of 10.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060442: no initial certificate for #9 — only the retest 536-1067-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060282: post-SOP CoQ rule date 18.05.2026 precedes the legacy series day 06.06.2026 — held to it, so the legacy CoQs keep 001 onward | P060162: no initial certificate for #9 — only the retest 549-1080-26 of 31.08.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P050142: no initial certificate for #9 — only the retest 559-1090-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060102: no initial certificate for #9 — only the retest 551-1082-26 of 01.09.2026; the legacy CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue) | P060342: no initial certificate on file — the CoQ keeps its planned number with a provisional date 06.06.2026 | P060342: no initial certificate for #9 — only the retest 539-1070-26 of 31.08.2026; the post-SOP CoQ cannot cite it (Head of QC to rule: report as not tested at initial testing, or wait for the reissue)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v21.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v22.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -7103,7 +7103,7 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>— not recorded —</t>
+          <t>— not recorded — (P160012)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>— not recorded —</t>
+          <t>— not recorded — (P160022)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>— not recorded —</t>
+          <t>— not recorded — (P160032)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -21148,7 +21148,7 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>— not recorded —</t>
+          <t>— not recorded — (P160012)</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>— not recorded —</t>
+          <t>— not recorded — (P160022)</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>— not recorded —</t>
+          <t>— not recorded — (P160032)</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v22 on 05.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v23 on 05.09.2026</t>
         </is>
       </c>
     </row>
@@ -31753,7 +31753,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v22.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v23.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/Issuance_Registers_prelim.xlsx
@@ -32278,7 +32278,7 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v24 on 05.09.2026</t>
+          <t>iCoA and CoQ Issuance Registers — preliminary — built with CoQ Analysis Master v25 on 05.09.2026</t>
         </is>
       </c>
     </row>
@@ -32299,7 +32299,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Source: CoQ_Analysis_Master_v24.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
+          <t>Source: CoQ_Analysis_Master_v25.xlsx, sheets iCoA Issuance and Batch Dates; dates from the Head of QC's list of 04.09.2026; the issuance plan of 31.08.2026 for the plan references.</t>
         </is>
       </c>
     </row>
